--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-17T15:32:01+00:00</t>
+    <t>2023-10-31T15:37:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>JPSys</t>
+    <t>VA</t>
   </si>
   <si>
     <t>Contact</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31T15:37:13+00:00</t>
+    <t>2023-11-01T18:52:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for Use Case Organization</t>
+    <t>This StructureDefinition contains the maps for VistA INSTITUTION (file 4) to FHIR Organization</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-01T18:52:48+00:00</t>
+    <t>2023-11-08T21:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-08T21:21:15+00:00</t>
+    <t>2023-11-08T21:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-09T22:38:39+00:00</t>
+    <t>2023-11-14T14:54:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T14:54:31+00:00</t>
+    <t>2023-11-14T17:25:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="504">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.3.0</t>
+    <t>0.4.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-14T17:25:19+00:00</t>
+    <t>2023-11-15T12:04:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -243,10 +243,10 @@
     <t>Mapping: FiveWs Pattern Mapping</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
     <t>Mapping: Clinical Data Warehouse (CDW)</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
   </si>
   <si>
     <t/>
@@ -663,10 +663,10 @@
     <t>./Value</t>
   </si>
   <si>
+    <t>1252: source value from INSTITUTION - NPI (#4-41.99) case NPI slice</t>
+  </si>
+  <si>
     <t>Dim.Institution.NPI</t>
-  </si>
-  <si>
-    <t>1252: source value from INSTITUTION - NPI (#4-41.99) case NPI slice</t>
   </si>
   <si>
     <t>Organization.identifier.period</t>
@@ -773,6 +773,10 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-16:1253: fixed value "true" {null}</t>
+  </si>
+  <si>
     <t>No equivalent in HL7 v2</t>
   </si>
   <si>
@@ -814,6 +818,10 @@
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-17:1254: fixed value "prov" {null}</t>
+  </si>
+  <si>
     <t>No equivalent in v2</t>
   </si>
   <si>
@@ -848,6 +856,9 @@
   </si>
   <si>
     <t>.PreferredName/Name</t>
+  </si>
+  <si>
+    <t>1251: source value from INSTITUTION - NAME (#4-.01)</t>
   </si>
   <si>
     <t>Dim.AutoDiscontinuedRule.InstitutionName
@@ -855,9 +866,6 @@
 Dim.RequestService.IFCRoutingInstitution</t>
   </si>
   <si>
-    <t>1251: source value from INSTITUTION - NAME (#4-.01)</t>
-  </si>
-  <si>
     <t>Organization.alias</t>
   </si>
   <si>
@@ -874,10 +882,10 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
+    <t>1255: source value from INSTITUTION - SHORT NAME (#4-.05)</t>
+  </si>
+  <si>
     <t>Dim.Institution.InstitutionShortName</t>
-  </si>
-  <si>
-    <t>1255: source value from INSTITUTION - SHORT NAME (#4-.05)</t>
   </si>
   <si>
     <t>Organization.telecom</t>
@@ -1143,6 +1151,10 @@
     <t>Address.type</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-18:1257: fixed value "physical" {null}inv-19:1268: fixed value "postal" {null}</t>
+  </si>
+  <si>
     <t>XAD.18</t>
   </si>
   <si>
@@ -1203,10 +1215,10 @@
     <t>./StreetAddress (newline delimitted)</t>
   </si>
   <si>
+    <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (#4-4.02)</t>
+  </si>
+  <si>
     <t>Dim.Institution.StreetAddress2</t>
-  </si>
-  <si>
-    <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (#4-4.02)</t>
   </si>
   <si>
     <t>Organization.address.city</t>
@@ -1237,10 +1249,10 @@
     <t>./Jurisdiction</t>
   </si>
   <si>
+    <t>1271: source value from INSTITUTION - CITY (MAILING) (#4-4.03)</t>
+  </si>
+  <si>
     <t>Dim.Institution.City</t>
-  </si>
-  <si>
-    <t>1271: source value from INSTITUTION - CITY (MAILING) (#4-4.03)</t>
   </si>
   <si>
     <t>Organization.address.district</t>
@@ -1271,10 +1283,10 @@
     <t>AD.part[parttype = CNT | CPA]</t>
   </si>
   <si>
+    <t>1261: source value from INSTITUTION - DISTRICT (#4-.03)</t>
+  </si>
+  <si>
     <t>Dim.Institution.MedicalDistrict</t>
-  </si>
-  <si>
-    <t>1261: source value from INSTITUTION - DISTRICT (#4-.03)</t>
   </si>
   <si>
     <t>Organization.address.state</t>
@@ -1308,13 +1320,13 @@
     <t>./Region</t>
   </si>
   <si>
+    <t>1272: source value from INSTITUTION - STATE (MAILING) (#4-4.04)</t>
+  </si>
+  <si>
     <t>Dim.State.StateAbbrev
 Dim.State.StateAbbrev</t>
   </si>
   <si>
-    <t>1272: source value from INSTITUTION - STATE (MAILING) (#4-4.04)</t>
-  </si>
-  <si>
     <t>Organization.address.postalCode</t>
   </si>
   <si>
@@ -1343,12 +1355,12 @@
     <t>./PostalIdentificationCode</t>
   </si>
   <si>
+    <t>1273: source value from INSTITUTION - ZIP (MAILING) (#4-4.05)</t>
+  </si>
+  <si>
     <t>Dim.Institution.Zip</t>
   </si>
   <si>
-    <t>1273: source value from INSTITUTION - ZIP (MAILING) (#4-4.05)</t>
-  </si>
-  <si>
     <t>Organization.address.country</t>
   </si>
   <si>
@@ -1373,10 +1385,10 @@
     <t>./Country</t>
   </si>
   <si>
+    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (#4-801 &gt; 779.004-.01)</t>
+  </si>
+  <si>
     <t>Dim.Country.CountryCode</t>
-  </si>
-  <si>
-    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (#4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>Organization.address.period</t>
@@ -1941,8 +1953,8 @@
     <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="218.1953125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="43.94140625" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4582,33 +4594,33 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>99</v>
+        <v>242</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>246</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4634,16 +4646,16 @@
         <v>179</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4668,13 +4680,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4692,7 +4704,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4704,33 +4716,33 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>256</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>162</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>77</v>
+        <v>260</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>258</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4756,16 +4768,16 @@
         <v>158</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4814,7 +4826,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4829,30 +4841,30 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4878,16 +4890,16 @@
         <v>158</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4936,7 +4948,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4954,7 +4966,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -4963,18 +4975,18 @@
         <v>77</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4997,19 +5009,19 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5058,7 +5070,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5067,19 +5079,19 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -5093,10 +5105,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5211,10 +5223,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5331,10 +5343,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5360,10 +5372,10 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5393,10 +5405,10 @@
         <v>173</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5414,7 +5426,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5423,19 +5435,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5449,10 +5461,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5478,16 +5490,16 @@
         <v>158</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5536,7 +5548,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5551,10 +5563,10 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>207</v>
@@ -5571,10 +5583,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5600,16 +5612,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5637,10 +5649,10 @@
         <v>173</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5658,7 +5670,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5673,13 +5685,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5693,10 +5705,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5719,16 +5731,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5778,7 +5790,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5813,10 +5825,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5842,10 +5854,10 @@
         <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5896,7 +5908,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5914,7 +5926,7 @@
         <v>130</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>217</v>
@@ -5931,10 +5943,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5957,19 +5969,19 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6018,7 +6030,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6027,19 +6039,19 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -6053,10 +6065,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6171,10 +6183,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6291,10 +6303,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6320,16 +6332,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6342,7 +6354,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6357,10 +6369,10 @@
         <v>173</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6378,7 +6390,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6393,13 +6405,13 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6413,10 +6425,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6442,13 +6454,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6462,7 +6474,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6477,10 +6489,10 @@
         <v>173</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6498,7 +6510,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6510,13 +6522,13 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>99</v>
+        <v>363</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6525,18 +6537,18 @@
         <v>77</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AP38" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6562,16 +6574,16 @@
         <v>158</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6584,7 +6596,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6620,7 +6632,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6635,10 +6647,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6655,10 +6667,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6669,7 +6681,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -6684,10 +6696,10 @@
         <v>158</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6702,7 +6714,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -6738,7 +6750,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6753,34 +6765,34 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6802,10 +6814,10 @@
         <v>158</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6820,7 +6832,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -6856,7 +6868,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6871,34 +6883,34 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6920,13 +6932,13 @@
         <v>158</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6940,7 +6952,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -6976,7 +6988,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6991,10 +7003,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7003,22 +7015,22 @@
         <v>77</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7040,10 +7052,10 @@
         <v>158</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7073,10 +7085,10 @@
         <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7094,7 +7106,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7109,34 +7121,34 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7158,10 +7170,10 @@
         <v>158</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7176,7 +7188,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7212,7 +7224,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7227,30 +7239,30 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7276,13 +7288,13 @@
         <v>158</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7332,7 +7344,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7347,30 +7359,30 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7396,14 +7408,14 @@
         <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7416,7 +7428,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7452,7 +7464,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7467,10 +7479,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>217</v>
@@ -7487,10 +7499,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7516,14 +7528,14 @@
         <v>219</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7572,7 +7584,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7587,10 +7599,10 @@
         <v>99</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>162</v>
@@ -7607,10 +7619,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7633,19 +7645,19 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7694,7 +7706,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7712,7 +7724,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7729,10 +7741,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7847,10 +7859,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7967,14 +7979,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7996,10 +8008,10 @@
         <v>133</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="N51" t="s" s="2">
         <v>136</v>
@@ -8054,7 +8066,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8089,10 +8101,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8118,14 +8130,14 @@
         <v>179</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8153,10 +8165,10 @@
         <v>184</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -8174,7 +8186,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8192,7 +8204,7 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8209,10 +8221,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8235,17 +8247,17 @@
         <v>77</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -8294,7 +8306,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8309,10 +8321,10 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
@@ -8321,18 +8333,18 @@
         <v>77</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>478</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8355,17 +8367,17 @@
         <v>77</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -8414,7 +8426,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8429,10 +8441,10 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
@@ -8449,10 +8461,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8567,10 +8579,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8687,10 +8699,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8716,10 +8728,10 @@
         <v>107</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8749,10 +8761,10 @@
         <v>173</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8770,7 +8782,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8779,19 +8791,19 @@
         <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8805,10 +8817,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8834,16 +8846,16 @@
         <v>158</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>77</v>
@@ -8892,7 +8904,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8907,10 +8919,10 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>207</v>
@@ -8919,18 +8931,18 @@
         <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>77</v>
+        <v>492</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>489</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8956,16 +8968,16 @@
         <v>107</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8993,10 +9005,10 @@
         <v>173</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -9014,7 +9026,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9029,13 +9041,13 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -9049,10 +9061,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9075,16 +9087,16 @@
         <v>88</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9134,7 +9146,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9169,10 +9181,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9198,10 +9210,10 @@
         <v>211</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9252,7 +9264,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9270,7 +9282,7 @@
         <v>130</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>217</v>
@@ -9287,10 +9299,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9313,17 +9325,17 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -9372,7 +9384,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9387,10 +9399,10 @@
         <v>99</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9407,10 +9419,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9433,17 +9445,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9492,7 +9504,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.0</t>
+    <t>0.5.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T12:04:59+00:00</t>
+    <t>2023-11-15T19:14:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -774,7 +774,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-16:1253: fixed value "true" {null}</t>
+inv-22:1253: fixed value = true {null}</t>
   </si>
   <si>
     <t>No equivalent in HL7 v2</t>
@@ -819,7 +819,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-17:1254: fixed value "prov" {null}</t>
+inv-23:1254: fixed value = prov {null}</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1152,7 +1152,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-18:1257: fixed value "physical" {null}inv-19:1268: fixed value "postal" {null}</t>
+inv-24:1257: fixed value = physical {null}inv-25:1268: fixed value = postal {null}</t>
   </si>
   <si>
     <t>XAD.18</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$63</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$89</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2441" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="543">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T19:14:31+00:00</t>
+    <t>2023-11-15T20:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1071,6 +1071,10 @@
     <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
   </si>
   <si>
+    <t xml:space="preserve">value:type}
+</t>
+  </si>
+  <si>
     <t xml:space="preserve">org-2
 </t>
   </si>
@@ -1151,16 +1155,9 @@
     <t>Address.type</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-24:1257: fixed value = physical {null}inv-25:1268: fixed value = postal {null}</t>
-  </si>
-  <si>
     <t>XAD.18</t>
   </si>
   <si>
-    <t>1268: fixed value = postal</t>
-  </si>
-  <si>
     <t>Organization.address.text</t>
   </si>
   <si>
@@ -1213,12 +1210,6 @@
   </si>
   <si>
     <t>./StreetAddress (newline delimitted)</t>
-  </si>
-  <si>
-    <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (#4-4.02)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.StreetAddress2</t>
   </si>
   <si>
     <t>Organization.address.city</t>
@@ -1249,12 +1240,6 @@
     <t>./Jurisdiction</t>
   </si>
   <si>
-    <t>1271: source value from INSTITUTION - CITY (MAILING) (#4-4.03)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.City</t>
-  </si>
-  <si>
     <t>Organization.address.district</t>
   </si>
   <si>
@@ -1283,12 +1268,6 @@
     <t>AD.part[parttype = CNT | CPA]</t>
   </si>
   <si>
-    <t>1261: source value from INSTITUTION - DISTRICT (#4-.03)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.MedicalDistrict</t>
-  </si>
-  <si>
     <t>Organization.address.state</t>
   </si>
   <si>
@@ -1320,13 +1299,6 @@
     <t>./Region</t>
   </si>
   <si>
-    <t>1272: source value from INSTITUTION - STATE (MAILING) (#4-4.04)</t>
-  </si>
-  <si>
-    <t>Dim.State.StateAbbrev
-Dim.State.StateAbbrev</t>
-  </si>
-  <si>
     <t>Organization.address.postalCode</t>
   </si>
   <si>
@@ -1355,12 +1327,6 @@
     <t>./PostalIdentificationCode</t>
   </si>
   <si>
-    <t>1273: source value from INSTITUTION - ZIP (MAILING) (#4-4.05)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.Zip</t>
-  </si>
-  <si>
     <t>Organization.address.country</t>
   </si>
   <si>
@@ -1383,12 +1349,6 @@
   </si>
   <si>
     <t>./Country</t>
-  </si>
-  <si>
-    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (#4-801 &gt; 779.004-.01)</t>
-  </si>
-  <si>
-    <t>Dim.Country.CountryCode</t>
   </si>
   <si>
     <t>Organization.address.period</t>
@@ -1413,6 +1373,156 @@
   </si>
   <si>
     <t>XAD.12 / XAD.13 + XAD.14</t>
+  </si>
+  <si>
+    <t>Organization.address:physical</t>
+  </si>
+  <si>
+    <t>physical</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.id</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.extension</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.use</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.type</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-24:1257: fixed value = physical {null}</t>
+  </si>
+  <si>
+    <t>1257: fixed value = physical</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.text</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.line</t>
+  </si>
+  <si>
+    <t>1259: source value from INSTITUTION - STREET ADDR. 2 (#4-1.02)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.StreetAddress2</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.city</t>
+  </si>
+  <si>
+    <t>1260: source value from INSTITUTION - CITY (#4-1.03)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.City</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.district</t>
+  </si>
+  <si>
+    <t>1261: source value from INSTITUTION - DISTRICT (#4-.03)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.MedicalDistrict</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.state</t>
+  </si>
+  <si>
+    <t>1262: source value from INSTITUTION - STATE &gt; STATE - ABBREVIATION (#4-.02 &gt; 5-1)</t>
+  </si>
+  <si>
+    <t>Dim.State.StateAbbrev
+Dim.State.StateAbbrev</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.postalCode</t>
+  </si>
+  <si>
+    <t>1263: source value from INSTITUTION - ZIP (#4-1.04)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.Zip</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.country</t>
+  </si>
+  <si>
+    <t>1264: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (#4-801 &gt; 779.004-.01)</t>
+  </si>
+  <si>
+    <t>Dim.Country.CountryCode</t>
+  </si>
+  <si>
+    <t>Organization.address:physical.period</t>
+  </si>
+  <si>
+    <t>Organization.address:postal</t>
+  </si>
+  <si>
+    <t>postal</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.id</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.extension</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.use</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.type</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+inv-25:1268: fixed value = postal {null}</t>
+  </si>
+  <si>
+    <t>1268: fixed value = postal</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.text</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.line</t>
+  </si>
+  <si>
+    <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (#4-4.02)</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.city</t>
+  </si>
+  <si>
+    <t>1271: source value from INSTITUTION - CITY (MAILING) (#4-4.03)</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.district</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.state</t>
+  </si>
+  <si>
+    <t>1272: source value from INSTITUTION - STATE (MAILING) (#4-4.04)</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.postalCode</t>
+  </si>
+  <si>
+    <t>1273: source value from INSTITUTION - ZIP (MAILING) (#4-4.05)</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.country</t>
+  </si>
+  <si>
+    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (#4-801 &gt; 779.004-.01)</t>
+  </si>
+  <si>
+    <t>Organization.address:postal.period</t>
   </si>
   <si>
     <t>Organization.partOf</t>
@@ -1911,10 +2021,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP63"/>
+  <dimension ref="A1:AP89"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="37.77734375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="39.625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.77734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -6018,16 +6128,14 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC34" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>337</v>
+      </c>
+      <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE34" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF34" t="s" s="2">
         <v>331</v>
@@ -6039,19 +6147,19 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -6065,10 +6173,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6183,10 +6291,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6303,10 +6411,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6332,16 +6440,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6354,7 +6462,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6369,10 +6477,10 @@
         <v>173</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6390,7 +6498,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6405,13 +6513,13 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>318</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6425,10 +6533,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6454,13 +6562,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6474,7 +6582,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6489,10 +6597,10 @@
         <v>173</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6510,7 +6618,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6522,7 +6630,7 @@
         <v>77</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>363</v>
+        <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>364</v>
@@ -6537,7 +6645,7 @@
         <v>77</v>
       </c>
       <c r="AO38" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="AP38" t="s" s="2">
         <v>77</v>
@@ -6545,10 +6653,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6574,16 +6682,16 @@
         <v>158</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M39" t="s" s="2">
         <v>367</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="N39" t="s" s="2">
         <v>368</v>
       </c>
-      <c r="N39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>369</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6596,43 +6704,43 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF39" t="s" s="2">
         <v>371</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>372</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6647,10 +6755,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AL39" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6667,10 +6775,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6681,7 +6789,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -6696,10 +6804,10 @@
         <v>158</v>
       </c>
       <c r="L40" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M40" t="s" s="2">
         <v>377</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>378</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6714,43 +6822,43 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="U40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF40" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6765,34 +6873,34 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL40" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AM40" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AM40" t="s" s="2">
-        <v>383</v>
-      </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>385</v>
+        <v>77</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6814,10 +6922,10 @@
         <v>158</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6832,7 +6940,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -6868,7 +6976,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6883,34 +6991,34 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>395</v>
+        <v>77</v>
       </c>
       <c r="AP41" t="s" s="2">
-        <v>396</v>
+        <v>77</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>398</v>
+        <v>393</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -6932,13 +7040,13 @@
         <v>158</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>399</v>
+        <v>394</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>400</v>
+        <v>395</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>401</v>
+        <v>396</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6952,7 +7060,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>402</v>
+        <v>397</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -6988,7 +7096,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>403</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7003,10 +7111,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>404</v>
+        <v>399</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>405</v>
+        <v>400</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7015,22 +7123,22 @@
         <v>77</v>
       </c>
       <c r="AO42" t="s" s="2">
-        <v>406</v>
+        <v>77</v>
       </c>
       <c r="AP42" t="s" s="2">
-        <v>407</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>408</v>
+        <v>401</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>409</v>
+        <v>402</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7052,10 +7160,10 @@
         <v>158</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>410</v>
+        <v>403</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>411</v>
+        <v>404</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7085,10 +7193,10 @@
         <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>412</v>
+        <v>405</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>413</v>
+        <v>406</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7106,7 +7214,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>414</v>
+        <v>407</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7121,34 +7229,34 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>415</v>
+        <v>408</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>416</v>
+        <v>409</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>417</v>
+        <v>410</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>418</v>
+        <v>77</v>
       </c>
       <c r="AP43" t="s" s="2">
-        <v>419</v>
+        <v>77</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7170,10 +7278,10 @@
         <v>158</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>423</v>
+        <v>414</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7188,7 +7296,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>424</v>
+        <v>415</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7224,7 +7332,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>416</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7239,30 +7347,30 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>426</v>
+        <v>417</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>427</v>
+        <v>418</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>429</v>
+        <v>77</v>
       </c>
       <c r="AP44" t="s" s="2">
-        <v>430</v>
+        <v>77</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>431</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7288,13 +7396,13 @@
         <v>158</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>432</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>433</v>
+        <v>422</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>434</v>
+        <v>423</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7344,7 +7452,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7359,30 +7467,30 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>436</v>
+        <v>425</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>437</v>
+        <v>426</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>438</v>
+        <v>427</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>439</v>
+        <v>77</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>440</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7408,14 +7516,14 @@
         <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7428,7 +7536,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7464,7 +7572,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7479,7 +7587,7 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>330</v>
@@ -7499,12 +7607,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="C47" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="C47" t="s" s="2">
+        <v>436</v>
+      </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7516,26 +7626,28 @@
         <v>87</v>
       </c>
       <c r="H47" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>219</v>
+        <v>332</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>449</v>
+        <v>333</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>450</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>334</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>335</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>451</v>
+        <v>336</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7584,28 +7696,28 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>448</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>339</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>243</v>
+        <v>340</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>452</v>
+        <v>341</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>162</v>
+        <v>342</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7619,10 +7731,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>453</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7633,7 +7745,7 @@
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7645,20 +7757,16 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>454</v>
+        <v>158</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>455</v>
+        <v>159</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>456</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>457</v>
-      </c>
-      <c r="O48" t="s" s="2">
-        <v>458</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
       </c>
@@ -7706,25 +7814,25 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>453</v>
+        <v>161</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>459</v>
+        <v>162</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7741,21 +7849,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>460</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>460</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7767,15 +7875,17 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N49" s="2"/>
+        <v>164</v>
+      </c>
+      <c r="N49" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7812,31 +7922,31 @@
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
@@ -7859,44 +7969,46 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>461</v>
+        <v>439</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>461</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E50" s="2"/>
       <c r="F50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I50" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J50" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>134</v>
+        <v>346</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>164</v>
+        <v>347</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O50" s="2"/>
+        <v>348</v>
+      </c>
+      <c r="O50" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7908,7 +8020,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -7920,13 +8032,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7944,28 +8056,28 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH50" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>162</v>
+        <v>318</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>77</v>
+        <v>355</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7979,46 +8091,44 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>462</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>463</v>
+        <v>77</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I51" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J51" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>464</v>
+        <v>357</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>465</v>
+        <v>358</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O51" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>359</v>
+      </c>
+      <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -8030,7 +8140,7 @@
         <v>77</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -8042,13 +8152,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8066,25 +8176,25 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>466</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>138</v>
+        <v>441</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>130</v>
+        <v>318</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8093,7 +8203,7 @@
         <v>77</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>77</v>
+        <v>442</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>77</v>
@@ -8101,10 +8211,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>467</v>
+        <v>443</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>467</v>
+        <v>365</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8124,20 +8234,22 @@
         <v>77</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>179</v>
+        <v>158</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>468</v>
+        <v>366</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>469</v>
-      </c>
-      <c r="N52" s="2"/>
+        <v>367</v>
+      </c>
+      <c r="N52" t="s" s="2">
+        <v>368</v>
+      </c>
       <c r="O52" t="s" s="2">
-        <v>470</v>
+        <v>369</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8150,7 +8262,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -8162,13 +8274,13 @@
         <v>77</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>471</v>
+        <v>77</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>472</v>
+        <v>77</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>77</v>
@@ -8186,7 +8298,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>467</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8201,10 +8313,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>473</v>
+        <v>373</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8221,10 +8333,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>474</v>
+        <v>444</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>474</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8235,30 +8347,28 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>87</v>
+        <v>375</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J53" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>475</v>
+        <v>158</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>476</v>
+        <v>376</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>477</v>
+        <v>377</v>
       </c>
       <c r="N53" s="2"/>
-      <c r="O53" t="s" s="2">
-        <v>478</v>
-      </c>
+      <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
         <v>77</v>
       </c>
@@ -8270,7 +8380,7 @@
         <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>77</v>
@@ -8306,13 +8416,13 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>474</v>
+        <v>379</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH53" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI53" t="s" s="2">
         <v>77</v>
@@ -8321,64 +8431,62 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>479</v>
+        <v>380</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>480</v>
+        <v>381</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>77</v>
+        <v>382</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>481</v>
+        <v>445</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>77</v>
+        <v>446</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>482</v>
+        <v>447</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>482</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H54" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J54" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>279</v>
+        <v>158</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>483</v>
+        <v>385</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>484</v>
+        <v>386</v>
       </c>
       <c r="N54" s="2"/>
-      <c r="O54" t="s" s="2">
-        <v>485</v>
-      </c>
+      <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>77</v>
       </c>
@@ -8390,7 +8498,7 @@
         <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>77</v>
+        <v>387</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8426,13 +8534,13 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>482</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>77</v>
@@ -8441,34 +8549,34 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>486</v>
+        <v>389</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>487</v>
+        <v>390</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>77</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>77</v>
+        <v>449</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>488</v>
+        <v>450</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>488</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>77</v>
+        <v>393</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8484,18 +8592,20 @@
         <v>77</v>
       </c>
       <c r="J55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>159</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N55" s="2"/>
+        <v>395</v>
+      </c>
+      <c r="N55" t="s" s="2">
+        <v>396</v>
+      </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8508,7 +8618,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>77</v>
+        <v>397</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8544,7 +8654,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>161</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8556,13 +8666,13 @@
         <v>77</v>
       </c>
       <c r="AJ55" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>162</v>
+        <v>400</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8571,51 +8681,49 @@
         <v>77</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>77</v>
+        <v>451</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>77</v>
+        <v>452</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>489</v>
+        <v>453</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>489</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>132</v>
+        <v>402</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H56" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J56" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>134</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8640,73 +8748,73 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>77</v>
+        <v>405</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>77</v>
+        <v>406</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB56" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC56" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE56" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>167</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ56" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>77</v>
+        <v>408</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>162</v>
+        <v>409</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>77</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>77</v>
+        <v>454</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>77</v>
+        <v>455</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>490</v>
+        <v>456</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>490</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>77</v>
+        <v>412</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8716,7 +8824,7 @@
         <v>87</v>
       </c>
       <c r="H57" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I57" t="s" s="2">
         <v>77</v>
@@ -8725,13 +8833,13 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>292</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>293</v>
+        <v>414</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8746,7 +8854,7 @@
         <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>77</v>
+        <v>415</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>77</v>
@@ -8758,13 +8866,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8782,7 +8890,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>296</v>
+        <v>416</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8791,36 +8899,36 @@
         <v>87</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="AJ57" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>298</v>
+        <v>417</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>299</v>
+        <v>418</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>300</v>
+        <v>419</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>77</v>
+        <v>457</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>77</v>
+        <v>458</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>491</v>
+        <v>459</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>491</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8834,7 +8942,7 @@
         <v>87</v>
       </c>
       <c r="H58" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I58" t="s" s="2">
         <v>77</v>
@@ -8846,17 +8954,15 @@
         <v>158</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>302</v>
+        <v>421</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>303</v>
+        <v>422</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O58" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>423</v>
+      </c>
+      <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
         <v>77</v>
       </c>
@@ -8904,7 +9010,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>306</v>
+        <v>424</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8919,30 +9025,30 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>307</v>
+        <v>425</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>308</v>
+        <v>426</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>207</v>
+        <v>427</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>492</v>
+        <v>460</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>77</v>
+        <v>461</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>493</v>
+        <v>462</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>493</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8959,25 +9065,23 @@
         <v>77</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>310</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N59" t="s" s="2">
-        <v>312</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>313</v>
+        <v>431</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -8990,7 +9094,7 @@
         <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>77</v>
+        <v>432</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>77</v>
@@ -9002,13 +9106,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>314</v>
+        <v>77</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -9026,7 +9130,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>316</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9041,13 +9145,13 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>317</v>
+        <v>434</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>319</v>
+        <v>217</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -9061,12 +9165,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>494</v>
+        <v>463</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="C60" s="2"/>
+        <v>331</v>
+      </c>
+      <c r="C60" t="s" s="2">
+        <v>464</v>
+      </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
       </c>
@@ -9078,27 +9184,29 @@
         <v>87</v>
       </c>
       <c r="H60" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O60" s="2"/>
+        <v>335</v>
+      </c>
+      <c r="O60" t="s" s="2">
+        <v>336</v>
+      </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
       </c>
@@ -9146,28 +9254,28 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>77</v>
+        <v>338</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>99</v>
+        <v>339</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>162</v>
+        <v>340</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>162</v>
+        <v>341</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>77</v>
+        <v>342</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -9181,10 +9289,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>495</v>
+        <v>465</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>495</v>
+        <v>343</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9204,16 +9312,16 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>211</v>
+        <v>158</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>327</v>
+        <v>159</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>328</v>
+        <v>160</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9264,7 +9372,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>329</v>
+        <v>161</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9276,16 +9384,16 @@
         <v>77</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>330</v>
+        <v>162</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -9299,21 +9407,21 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>496</v>
+        <v>466</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>496</v>
+        <v>344</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H62" t="s" s="2">
         <v>77</v>
@@ -9325,18 +9433,18 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>332</v>
+        <v>133</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>497</v>
+        <v>134</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>498</v>
-      </c>
-      <c r="N62" s="2"/>
-      <c r="O62" t="s" s="2">
-        <v>499</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="N62" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>77</v>
       </c>
@@ -9372,37 +9480,37 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE62" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>496</v>
+        <v>167</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>500</v>
+        <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>501</v>
+        <v>162</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9419,10 +9527,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>502</v>
+        <v>467</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>502</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9433,29 +9541,31 @@
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I63" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J63" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>503</v>
+        <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>504</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>347</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>348</v>
+      </c>
       <c r="O63" t="s" s="2">
-        <v>506</v>
+        <v>349</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9468,7 +9578,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9480,13 +9590,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9504,13 +9614,13 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>502</v>
+        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
@@ -9519,26 +9629,3140 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>77</v>
+        <v>354</v>
       </c>
       <c r="AL63" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM63" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AN63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP63" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="64" hidden="true">
+      <c r="A64" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B64" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="C64" s="2"/>
+      <c r="D64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E64" s="2"/>
+      <c r="F64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K64" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L64" t="s" s="2">
+        <v>357</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>358</v>
+      </c>
+      <c r="N64" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="O64" s="2"/>
+      <c r="P64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q64" s="2"/>
+      <c r="R64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T64" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="U64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X64" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y64" t="s" s="2">
+        <v>361</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
+        <v>363</v>
+      </c>
+      <c r="AG64" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH64" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ64" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AK64" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO64" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AP64" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>366</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="N65" t="s" s="2">
+        <v>368</v>
+      </c>
+      <c r="O65" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="P65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>371</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>373</v>
+      </c>
+      <c r="AM65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP65" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>375</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>380</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM66" t="s" s="2">
+        <v>382</v>
+      </c>
+      <c r="AN66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO66" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AP66" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>383</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>384</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>385</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="AM67" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AN67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO67" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="AP67" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>395</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>396</v>
+      </c>
+      <c r="O68" s="2"/>
+      <c r="P68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>398</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>399</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>400</v>
+      </c>
+      <c r="AM68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP68" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>402</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>409</v>
+      </c>
+      <c r="AM69" t="s" s="2">
+        <v>410</v>
+      </c>
+      <c r="AN69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO69" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AP69" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>411</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>412</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>414</v>
+      </c>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AM70" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="AN70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO70" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AP70" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>421</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>422</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>425</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="AM71" t="s" s="2">
+        <v>427</v>
+      </c>
+      <c r="AN71" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO71" t="s" s="2">
+        <v>482</v>
+      </c>
+      <c r="AP71" t="s" s="2">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>483</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>428</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="N72" s="2"/>
+      <c r="O72" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="P72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>433</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM72" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP72" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="73" hidden="true">
+      <c r="A73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="B73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="C73" s="2"/>
+      <c r="D73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E73" s="2"/>
+      <c r="F73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K73" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L73" t="s" s="2">
+        <v>485</v>
+      </c>
+      <c r="M73" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="N73" s="2"/>
+      <c r="O73" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="P73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q73" s="2"/>
+      <c r="R73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF73" t="s" s="2">
+        <v>484</v>
+      </c>
+      <c r="AG73" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH73" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ73" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK73" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL73" t="s" s="2">
+        <v>488</v>
+      </c>
+      <c r="AM73" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AM63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP63" t="s" s="2">
+      <c r="AN73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP73" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="74" hidden="true">
+      <c r="A74" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="B74" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="C74" s="2"/>
+      <c r="D74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E74" s="2"/>
+      <c r="F74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K74" t="s" s="2">
+        <v>490</v>
+      </c>
+      <c r="L74" t="s" s="2">
+        <v>491</v>
+      </c>
+      <c r="M74" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>493</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q74" s="2"/>
+      <c r="R74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF74" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="AG74" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH74" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ74" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL74" t="s" s="2">
+        <v>495</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP74" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="75" hidden="true">
+      <c r="A75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="B75" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C75" s="2"/>
+      <c r="D75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E75" s="2"/>
+      <c r="F75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M75" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q75" s="2"/>
+      <c r="R75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF75" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG75" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH75" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL75" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP75" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="76" hidden="true">
+      <c r="A76" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="B76" t="s" s="2">
+        <v>497</v>
+      </c>
+      <c r="C76" s="2"/>
+      <c r="D76" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E76" s="2"/>
+      <c r="F76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K76" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L76" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M76" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N76" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O76" s="2"/>
+      <c r="P76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q76" s="2"/>
+      <c r="R76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF76" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG76" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH76" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ76" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL76" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP76" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="77" hidden="true">
+      <c r="A77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="B77" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C77" s="2"/>
+      <c r="D77" t="s" s="2">
+        <v>499</v>
+      </c>
+      <c r="E77" s="2"/>
+      <c r="F77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J77" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K77" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L77" t="s" s="2">
+        <v>500</v>
+      </c>
+      <c r="M77" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N77" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q77" s="2"/>
+      <c r="R77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF77" t="s" s="2">
+        <v>502</v>
+      </c>
+      <c r="AG77" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH77" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ77" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL77" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP77" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" hidden="true">
+      <c r="A78" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="B78" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="C78" s="2"/>
+      <c r="D78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E78" s="2"/>
+      <c r="F78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K78" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="L78" t="s" s="2">
+        <v>504</v>
+      </c>
+      <c r="M78" t="s" s="2">
+        <v>505</v>
+      </c>
+      <c r="N78" s="2"/>
+      <c r="O78" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="P78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q78" s="2"/>
+      <c r="R78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X78" t="s" s="2">
+        <v>184</v>
+      </c>
+      <c r="Y78" t="s" s="2">
+        <v>507</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>508</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF78" t="s" s="2">
+        <v>503</v>
+      </c>
+      <c r="AG78" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH78" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ78" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL78" t="s" s="2">
+        <v>509</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP78" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79" hidden="true">
+      <c r="A79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="B79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="C79" s="2"/>
+      <c r="D79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E79" s="2"/>
+      <c r="F79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K79" t="s" s="2">
+        <v>511</v>
+      </c>
+      <c r="L79" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="M79" t="s" s="2">
+        <v>513</v>
+      </c>
+      <c r="N79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>514</v>
+      </c>
+      <c r="P79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q79" s="2"/>
+      <c r="R79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF79" t="s" s="2">
+        <v>510</v>
+      </c>
+      <c r="AG79" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH79" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ79" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK79" t="s" s="2">
+        <v>515</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>516</v>
+      </c>
+      <c r="AM79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO79" t="s" s="2">
+        <v>517</v>
+      </c>
+      <c r="AP79" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="80" hidden="true">
+      <c r="A80" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="B80" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="C80" s="2"/>
+      <c r="D80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E80" s="2"/>
+      <c r="F80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K80" t="s" s="2">
+        <v>279</v>
+      </c>
+      <c r="L80" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="M80" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="N80" s="2"/>
+      <c r="O80" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="P80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q80" s="2"/>
+      <c r="R80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF80" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="AG80" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH80" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ80" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK80" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="AL80" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP80" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="81" hidden="true">
+      <c r="A81" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B81" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C81" s="2"/>
+      <c r="D81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E81" s="2"/>
+      <c r="F81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K81" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L81" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M81" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q81" s="2"/>
+      <c r="R81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF81" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="AG81" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH81" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL81" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP81" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="82" hidden="true">
+      <c r="A82" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="C82" s="2"/>
+      <c r="D82" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E82" s="2"/>
+      <c r="F82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K82" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L82" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M82" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O82" s="2"/>
+      <c r="P82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q82" s="2"/>
+      <c r="R82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB82" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AC82" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AD82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE82" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF82" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AG82" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH82" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ82" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP82" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="83" hidden="true">
+      <c r="A83" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="C83" s="2"/>
+      <c r="D83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E83" s="2"/>
+      <c r="F83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J83" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K83" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L83" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="M83" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q83" s="2"/>
+      <c r="R83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X83" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y83" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="Z83" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF83" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AG83" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH83" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI83" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AJ83" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK83" t="s" s="2">
+        <v>298</v>
+      </c>
+      <c r="AL83" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="AN83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP83" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="84" hidden="true">
+      <c r="A84" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="B84" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="C84" s="2"/>
+      <c r="D84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E84" s="2"/>
+      <c r="F84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J84" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K84" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L84" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="M84" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="O84" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="P84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q84" s="2"/>
+      <c r="R84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF84" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AG84" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH84" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ84" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK84" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AM84" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="AN84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO84" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="AP84" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" hidden="true">
+      <c r="A85" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="B85" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="C85" s="2"/>
+      <c r="D85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E85" s="2"/>
+      <c r="F85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J85" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K85" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L85" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M85" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O85" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q85" s="2"/>
+      <c r="R85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X85" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="Y85" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="Z85" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AA85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF85" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AG85" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH85" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ85" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK85" t="s" s="2">
+        <v>317</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="AM85" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="AN85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP85" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="86" hidden="true">
+      <c r="A86" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="B86" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="C86" s="2"/>
+      <c r="D86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E86" s="2"/>
+      <c r="F86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K86" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="L86" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="M86" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="O86" s="2"/>
+      <c r="P86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q86" s="2"/>
+      <c r="R86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF86" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AG86" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH86" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ86" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK86" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP86" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="87" hidden="true">
+      <c r="A87" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B87" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C87" s="2"/>
+      <c r="D87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E87" s="2"/>
+      <c r="F87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K87" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="L87" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="M87" t="s" s="2">
+        <v>328</v>
+      </c>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="2"/>
+      <c r="R87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF87" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="AG87" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH87" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ87" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK87" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="AM87" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP87" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="88" hidden="true">
+      <c r="A88" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B88" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C88" s="2"/>
+      <c r="D88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E88" s="2"/>
+      <c r="F88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K88" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="L88" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="M88" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="P88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q88" s="2"/>
+      <c r="R88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF88" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="AG88" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH88" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ88" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK88" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AM88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP88" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="89" hidden="true">
+      <c r="A89" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B89" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C89" s="2"/>
+      <c r="D89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E89" s="2"/>
+      <c r="F89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K89" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="L89" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="M89" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="N89" s="2"/>
+      <c r="O89" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="P89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q89" s="2"/>
+      <c r="R89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF89" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AG89" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH89" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ89" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AM89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP89" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP63">
+  <autoFilter ref="A1:AP89">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -9548,7 +12772,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI62">
+  <conditionalFormatting sqref="A2:AI88">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$89</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3426" uniqueCount="543">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="606">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-15T20:37:43+00:00</t>
+    <t>2023-11-29T20:32:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,221 +505,6 @@
   </si>
   <si>
     <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Organization.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>./IdentifierType</t>
-  </si>
-  <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>./Value</t>
-  </si>
-  <si>
-    <t>1252: source value from INSTITUTION - NPI (#4-41.99) case NPI slice</t>
-  </si>
-  <si>
-    <t>Dim.Institution.NPI</t>
-  </si>
-  <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
   </si>
   <si>
     <t>Organization.identifier:NPI</t>
@@ -736,6 +521,245 @@
 &lt;/valueIdentifier&gt;</t>
   </si>
   <si>
+    <t>Organization.identifier:NPI.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>./IdentifierType</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>./Value</t>
+  </si>
+  <si>
+    <t>1252: source value from INSTITUTION - NPI (#4-41.99)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.NPI</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>./IdentifierIssuingAuthority</t>
+  </si>
+  <si>
     <t>Organization.identifier:CLIA</t>
   </si>
   <si>
@@ -819,7 +843,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-23:1254: fixed value = prov {null}</t>
+inv-23:1254: fixed value = #prov {null}</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -831,7 +855,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1254: fixed value = prov</t>
+    <t>1254: fixed value = #prov</t>
   </si>
   <si>
     <t>Organization.name</t>
@@ -1071,7 +1095,7 @@
     <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:type}
+    <t xml:space="preserve">value:use}
 </t>
   </si>
   <si>
@@ -1394,10 +1418,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-24:1257: fixed value = physical {null}</t>
-  </si>
-  <si>
-    <t>1257: fixed value = physical</t>
+inv-24:1257: fixed value = #physical {null}</t>
+  </si>
+  <si>
+    <t>1257: fixed value = #physical</t>
   </si>
   <si>
     <t>Organization.address:physical.text</t>
@@ -1480,10 +1504,10 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-25:1268: fixed value = postal {null}</t>
-  </si>
-  <si>
-    <t>1268: fixed value = postal</t>
+inv-25:1268: fixed value = #postal {null}</t>
+  </si>
+  <si>
+    <t>1268: fixed value = #postal</t>
   </si>
   <si>
     <t>Organization.address:postal.text</t>
@@ -1628,7 +1652,174 @@
     <t>./name</t>
   </si>
   <si>
+    <t>Organization.contact.name.id</t>
+  </si>
+  <si>
+    <t>Organization.contact.name.extension</t>
+  </si>
+  <si>
+    <t>Organization.contact.name.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | nickname | anonymous | old | maiden</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this name.</t>
+  </si>
+  <si>
+    <t>Applications can assume that a name is current unless it explicitly says that it is temporary or old.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate name for a particular context of use to be selected from among a set of names.</t>
+  </si>
+  <si>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+  </si>
+  <si>
+    <t>HumanName.use</t>
+  </si>
+  <si>
+    <t>XPN.7, but often indicated by which field contains the name</t>
+  </si>
+  <si>
+    <t>./NamePurpose</t>
+  </si>
+  <si>
+    <t>Organization.contact.name.text</t>
+  </si>
+  <si>
+    <t>Text representation of the full name</t>
+  </si>
+  <si>
+    <t>Specifies the entire name as it should be displayed e.g. on an application UI. This may be provided instead of or as well as the specific parts.</t>
+  </si>
+  <si>
+    <t>Can provide both a text representation and parts. Applications updating a name SHALL ensure that when both text and parts are present,  no content is included in the text that isn't found in a part.</t>
+  </si>
+  <si>
+    <t>HumanName.text</t>
+  </si>
+  <si>
+    <t>implied by XPN.11</t>
+  </si>
+  <si>
     <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT – NAME (#4-4 &gt; 4.03-.01)</t>
+  </si>
+  <si>
+    <t>Organization.contact.name.family</t>
+  </si>
+  <si>
+    <t xml:space="preserve">surname
+</t>
+  </si>
+  <si>
+    <t>Family name (often called 'Surname')</t>
+  </si>
+  <si>
+    <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
+  </si>
+  <si>
+    <t>Family Name may be decomposed into specific parts using extensions (de, nl, es related cultures).</t>
+  </si>
+  <si>
+    <t>HumanName.family</t>
+  </si>
+  <si>
+    <t>XPN.1/FN.1</t>
+  </si>
+  <si>
+    <t>./part[partType = FAM]</t>
+  </si>
+  <si>
+    <t>./FamilyName</t>
+  </si>
+  <si>
+    <t>Organization.contact.name.given</t>
+  </si>
+  <si>
+    <t>first name
+middle name</t>
+  </si>
+  <si>
+    <t>Given names (not always 'first'). Includes middle names</t>
+  </si>
+  <si>
+    <t>Given name.</t>
+  </si>
+  <si>
+    <t>If only initials are recorded, they may be used in place of the full name parts. Initials may be separated into multiple given names but often aren't due to paractical limitations.  This element is not called "first name" since given names do not always come first.</t>
+  </si>
+  <si>
+    <t>HumanName.given</t>
+  </si>
+  <si>
+    <t>XPN.2 + XPN.3</t>
+  </si>
+  <si>
+    <t>./part[partType = GIV]</t>
+  </si>
+  <si>
+    <t>./GivenNames</t>
+  </si>
+  <si>
+    <t>Organization.contact.name.prefix</t>
+  </si>
+  <si>
+    <t>Parts that come before the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the start of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.prefix</t>
+  </si>
+  <si>
+    <t>XPN.5</t>
+  </si>
+  <si>
+    <t>./part[partType = PFX]</t>
+  </si>
+  <si>
+    <t>./TitleCode</t>
+  </si>
+  <si>
+    <t>Organization.contact.name.suffix</t>
+  </si>
+  <si>
+    <t>Parts that come after the name</t>
+  </si>
+  <si>
+    <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>HumanName.suffix</t>
+  </si>
+  <si>
+    <t>XPN/4</t>
+  </si>
+  <si>
+    <t>./part[partType = SFX]</t>
+  </si>
+  <si>
+    <t>Organization.contact.name.period</t>
+  </si>
+  <si>
+    <t>Time period when name was/is in use</t>
+  </si>
+  <si>
+    <t>Indicates the period of time when this name was valid for the named person.</t>
+  </si>
+  <si>
+    <t>Allows names to be placed in historical context.</t>
+  </si>
+  <si>
+    <t>HumanName.period</t>
+  </si>
+  <si>
+    <t>XPN.13 + XPN.14</t>
   </si>
   <si>
     <t>Organization.contact.telecom</t>
@@ -2021,7 +2212,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP89"/>
+  <dimension ref="A1:AP98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.625" customWidth="true" bestFit="true"/>
@@ -3400,9 +3591,11 @@
         <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3414,25 +3607,27 @@
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3441,7 +3636,7 @@
         <v>77</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>77</v>
@@ -3480,31 +3675,31 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>77</v>
@@ -3515,21 +3710,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3541,17 +3736,15 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3588,37 +3781,37 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF13" t="s" s="2">
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3638,43 +3831,41 @@
         <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3698,49 +3889,49 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3757,10 +3948,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3777,25 +3968,25 @@
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3820,13 +4011,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3844,7 +4035,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3859,10 +4050,10 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3879,10 +4070,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3896,7 +4087,7 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
@@ -3905,19 +4096,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3930,25 +4121,25 @@
         <v>77</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3984,10 +4175,10 @@
         <v>196</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -4001,10 +4192,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4018,7 +4209,7 @@
         <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
@@ -4027,18 +4218,20 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -4113,18 +4306,18 @@
         <v>77</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>77</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4147,15 +4340,17 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -4168,7 +4363,7 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>77</v>
@@ -4231,18 +4426,18 @@
         <v>77</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>77</v>
+        <v>218</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>77</v>
+        <v>219</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4265,17 +4460,15 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4324,7 +4517,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4339,13 +4532,13 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -4359,14 +4552,12 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4378,7 +4569,7 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
@@ -4387,18 +4578,18 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4407,7 +4598,7 @@
         <v>77</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>77</v>
@@ -4446,31 +4637,31 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>77</v>
@@ -4481,13 +4672,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4512,7 +4703,7 @@
         <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>147</v>
@@ -4529,7 +4720,7 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>77</v>
@@ -4603,10 +4794,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4629,25 +4820,25 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q22" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="R22" t="s" s="2">
         <v>77</v>
@@ -4692,7 +4883,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4704,22 +4895,22 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>77</v>
@@ -4727,10 +4918,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4753,19 +4944,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4790,13 +4981,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4814,7 +5005,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4826,22 +5017,22 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>77</v>
@@ -4849,10 +5040,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4875,19 +5066,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4936,7 +5127,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4951,30 +5142,30 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4997,19 +5188,19 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5058,7 +5249,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5076,7 +5267,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -5085,18 +5276,18 @@
         <v>77</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>277</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5119,19 +5310,19 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5180,7 +5371,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5189,19 +5380,19 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -5215,10 +5406,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5241,13 +5432,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5298,7 +5489,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5316,7 +5507,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5333,10 +5524,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5365,7 +5556,7 @@
         <v>134</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>136</v>
@@ -5406,10 +5597,10 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
@@ -5418,7 +5609,7 @@
         <v>151</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5436,7 +5627,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5453,10 +5644,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5482,10 +5673,10 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5512,13 +5703,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5536,7 +5727,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5545,19 +5736,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5571,10 +5762,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5597,19 +5788,19 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5658,7 +5849,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5673,13 +5864,13 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5693,10 +5884,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5722,16 +5913,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5756,13 +5947,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5780,7 +5971,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5795,13 +5986,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5815,10 +6006,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5841,16 +6032,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5900,7 +6091,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5915,10 +6106,10 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -5935,10 +6126,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5961,13 +6152,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6018,7 +6209,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6036,10 +6227,10 @@
         <v>130</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -6053,10 +6244,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6079,19 +6270,19 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6128,7 +6319,7 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -6138,7 +6329,7 @@
         <v>151</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6147,19 +6338,19 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -6173,10 +6364,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6199,13 +6390,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6256,7 +6447,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6274,7 +6465,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -6291,10 +6482,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6323,7 +6514,7 @@
         <v>134</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>136</v>
@@ -6364,10 +6555,10 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
@@ -6376,7 +6567,7 @@
         <v>151</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6394,7 +6585,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6411,10 +6602,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6440,16 +6631,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6462,7 +6653,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6474,13 +6665,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6498,7 +6689,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6513,13 +6704,13 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6533,10 +6724,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6562,13 +6753,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6582,7 +6773,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6594,13 +6785,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6618,7 +6809,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6633,10 +6824,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6653,10 +6844,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6679,19 +6870,19 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6704,7 +6895,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6740,7 +6931,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6755,10 +6946,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6775,10 +6966,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6789,7 +6980,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -6801,13 +6992,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6822,7 +7013,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -6858,7 +7049,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6873,13 +7064,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -6893,14 +7084,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -6919,13 +7110,13 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6940,7 +7131,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -6976,7 +7167,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6991,13 +7182,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -7011,14 +7202,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7037,16 +7228,16 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7060,7 +7251,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -7096,7 +7287,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7111,10 +7302,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7131,14 +7322,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7157,13 +7348,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7190,13 +7381,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7214,7 +7405,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7229,13 +7420,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -7249,14 +7440,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7275,13 +7466,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7296,7 +7487,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7332,7 +7523,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7347,13 +7538,13 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7367,10 +7558,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7393,16 +7584,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7452,7 +7643,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7467,13 +7658,13 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7487,10 +7678,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7513,17 +7704,17 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7536,7 +7727,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7572,7 +7763,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7587,13 +7778,13 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7607,13 +7798,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>443</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>436</v>
+        <v>444</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7635,19 +7826,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7696,7 +7887,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7705,19 +7896,19 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7731,10 +7922,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>445</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7757,13 +7948,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7814,7 +8005,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7832,7 +8023,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -7849,10 +8040,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>446</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7881,7 +8072,7 @@
         <v>134</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>136</v>
@@ -7922,10 +8113,10 @@
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
@@ -7934,7 +8125,7 @@
         <v>151</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7952,7 +8143,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -7969,10 +8160,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7998,16 +8189,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8020,7 +8211,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -8032,13 +8223,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -8056,7 +8247,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8071,13 +8262,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8091,10 +8282,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>440</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8120,13 +8311,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8140,7 +8331,7 @@
         <v>77</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -8152,13 +8343,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8176,7 +8367,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8188,13 +8379,13 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>441</v>
+        <v>449</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8203,7 +8394,7 @@
         <v>77</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>442</v>
+        <v>450</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>77</v>
@@ -8211,10 +8402,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>443</v>
+        <v>451</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8237,19 +8428,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8262,7 +8453,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -8298,7 +8489,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8313,10 +8504,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8333,10 +8524,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>444</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8347,7 +8538,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>88</v>
@@ -8359,13 +8550,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8380,7 +8571,7 @@
         <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>77</v>
@@ -8416,7 +8607,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8431,34 +8622,34 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>446</v>
+        <v>454</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>447</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8477,13 +8668,13 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8498,7 +8689,7 @@
         <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8534,7 +8725,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8549,34 +8740,34 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>448</v>
+        <v>456</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>449</v>
+        <v>457</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>450</v>
+        <v>458</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8595,16 +8786,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8618,7 +8809,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8654,7 +8845,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8669,10 +8860,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8681,22 +8872,22 @@
         <v>77</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>452</v>
+        <v>460</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>453</v>
+        <v>461</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8715,13 +8906,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8748,13 +8939,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8772,7 +8963,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8787,34 +8978,34 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>454</v>
+        <v>462</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>455</v>
+        <v>463</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8833,13 +9024,13 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8854,7 +9045,7 @@
         <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>77</v>
@@ -8890,7 +9081,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8905,30 +9096,30 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>457</v>
+        <v>465</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>458</v>
+        <v>466</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>459</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8951,16 +9142,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9010,7 +9201,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9025,30 +9216,30 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>460</v>
+        <v>468</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>462</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9071,17 +9262,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9094,7 +9285,7 @@
         <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>77</v>
@@ -9130,7 +9321,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9145,13 +9336,13 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -9165,13 +9356,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9193,19 +9384,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9254,7 +9445,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9263,19 +9454,19 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -9289,10 +9480,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9315,13 +9506,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9372,7 +9563,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9390,7 +9581,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9407,10 +9598,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9439,7 +9630,7 @@
         <v>134</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>136</v>
@@ -9480,10 +9671,10 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
@@ -9492,7 +9683,7 @@
         <v>151</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9510,7 +9701,7 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9527,10 +9718,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9556,16 +9747,16 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9578,7 +9769,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9590,13 +9781,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9614,7 +9805,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9629,13 +9820,13 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9649,10 +9840,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9678,13 +9869,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9698,7 +9889,7 @@
         <v>77</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9710,13 +9901,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9734,7 +9925,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9746,13 +9937,13 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9761,7 +9952,7 @@
         <v>77</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>77</v>
@@ -9769,10 +9960,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>471</v>
+        <v>479</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9795,19 +9986,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9820,7 +10011,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -9856,7 +10047,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9871,10 +10062,10 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -9891,10 +10082,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>472</v>
+        <v>480</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9905,7 +10096,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>88</v>
@@ -9917,13 +10108,13 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9938,7 +10129,7 @@
         <v>77</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>77</v>
@@ -9974,7 +10165,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9989,19 +10180,19 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>77</v>
@@ -10009,14 +10200,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>474</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10035,13 +10226,13 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10056,7 +10247,7 @@
         <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>77</v>
@@ -10092,7 +10283,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10107,19 +10298,19 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>475</v>
+        <v>483</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>77</v>
@@ -10127,14 +10318,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>476</v>
+        <v>484</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10153,16 +10344,16 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10176,7 +10367,7 @@
         <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>77</v>
@@ -10212,7 +10403,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10227,10 +10418,10 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -10247,14 +10438,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>477</v>
+        <v>485</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10273,13 +10464,13 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>404</v>
+        <v>412</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10306,13 +10497,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>405</v>
+        <v>413</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>406</v>
+        <v>414</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10330,7 +10521,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>407</v>
+        <v>415</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10345,19 +10536,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>408</v>
+        <v>416</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>409</v>
+        <v>417</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>410</v>
+        <v>418</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>478</v>
+        <v>486</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10365,14 +10556,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>479</v>
+        <v>487</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>419</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>412</v>
+        <v>420</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10391,13 +10582,13 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>421</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10412,7 +10603,7 @@
         <v>77</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>415</v>
+        <v>423</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>77</v>
@@ -10448,7 +10639,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>416</v>
+        <v>424</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10463,19 +10654,19 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>417</v>
+        <v>425</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>418</v>
+        <v>426</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>419</v>
+        <v>427</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>77</v>
@@ -10483,10 +10674,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>481</v>
+        <v>489</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>420</v>
+        <v>428</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10509,16 +10700,16 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>421</v>
+        <v>429</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>422</v>
+        <v>430</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>423</v>
+        <v>431</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10568,7 +10759,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10583,30 +10774,30 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>426</v>
+        <v>434</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>427</v>
+        <v>435</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>482</v>
+        <v>490</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>461</v>
+        <v>469</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>483</v>
+        <v>491</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>428</v>
+        <v>436</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10629,17 +10820,17 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>430</v>
+        <v>438</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10652,7 +10843,7 @@
         <v>77</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>432</v>
+        <v>440</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>77</v>
@@ -10688,7 +10879,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>433</v>
+        <v>441</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10703,13 +10894,13 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>434</v>
+        <v>442</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10723,10 +10914,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10749,17 +10940,17 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>485</v>
+        <v>493</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10808,7 +10999,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>484</v>
+        <v>492</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10823,13 +11014,13 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -10843,10 +11034,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10869,19 +11060,19 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -10930,7 +11121,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10948,7 +11139,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10965,10 +11156,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10991,13 +11182,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11048,7 +11239,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11066,7 +11257,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -11083,10 +11274,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>497</v>
+        <v>505</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11115,7 +11306,7 @@
         <v>134</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>136</v>
@@ -11168,7 +11359,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11186,7 +11377,7 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
@@ -11203,14 +11394,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>499</v>
+        <v>507</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11232,10 +11423,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>500</v>
+        <v>508</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>501</v>
+        <v>509</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>136</v>
@@ -11290,7 +11481,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>502</v>
+        <v>510</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11325,10 +11516,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11351,17 +11542,17 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>504</v>
+        <v>512</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>505</v>
+        <v>513</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>506</v>
+        <v>514</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11386,13 +11577,13 @@
         <v>77</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>507</v>
+        <v>515</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>508</v>
+        <v>516</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11410,7 +11601,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>503</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11428,7 +11619,7 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>509</v>
+        <v>517</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11445,10 +11636,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11471,17 +11662,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>511</v>
+        <v>519</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>512</v>
+        <v>520</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>513</v>
+        <v>521</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>514</v>
+        <v>522</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11530,7 +11721,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>510</v>
+        <v>518</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11545,10 +11736,10 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>515</v>
+        <v>523</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>516</v>
+        <v>524</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11557,7 +11748,7 @@
         <v>77</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>517</v>
+        <v>77</v>
       </c>
       <c r="AP79" t="s" s="2">
         <v>77</v>
@@ -11565,10 +11756,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11579,7 +11770,7 @@
         <v>78</v>
       </c>
       <c r="G80" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H80" t="s" s="2">
         <v>77</v>
@@ -11591,18 +11782,16 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>279</v>
+        <v>163</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>519</v>
+        <v>164</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>520</v>
+        <v>165</v>
       </c>
       <c r="N80" s="2"/>
-      <c r="O80" t="s" s="2">
-        <v>521</v>
-      </c>
+      <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
         <v>77</v>
       </c>
@@ -11650,25 +11839,25 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>518</v>
+        <v>166</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH80" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>522</v>
+        <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>523</v>
+        <v>167</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
@@ -11685,21 +11874,21 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11711,15 +11900,17 @@
         <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>159</v>
+        <v>134</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N81" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N81" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11756,37 +11947,37 @@
         <v>77</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>161</v>
+        <v>173</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11803,44 +11994,46 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J82" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>134</v>
+        <v>528</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>164</v>
+        <v>529</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O82" s="2"/>
+        <v>530</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>531</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -11864,52 +12057,52 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>77</v>
+        <v>532</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>77</v>
+        <v>533</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB82" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC82" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE82" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>167</v>
+        <v>534</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH82" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ82" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>77</v>
+        <v>535</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>162</v>
+        <v>326</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>77</v>
+        <v>536</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>77</v>
@@ -11923,10 +12116,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11949,16 +12142,20 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>292</v>
+        <v>538</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>539</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -11982,13 +12179,13 @@
         <v>77</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>295</v>
+        <v>77</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>77</v>
@@ -12006,7 +12203,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>296</v>
+        <v>541</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12015,25 +12212,25 @@
         <v>87</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>297</v>
+        <v>77</v>
       </c>
       <c r="AJ83" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>298</v>
+        <v>542</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>299</v>
+        <v>381</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>77</v>
+        <v>543</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>77</v>
@@ -12041,14 +12238,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>527</v>
+        <v>544</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>77</v>
+        <v>545</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12067,20 +12264,18 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>302</v>
+        <v>546</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>303</v>
+        <v>547</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O84" t="s" s="2">
-        <v>305</v>
-      </c>
+        <v>548</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>77</v>
       </c>
@@ -12128,7 +12323,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>306</v>
+        <v>549</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12143,19 +12338,19 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>307</v>
+        <v>550</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>308</v>
+        <v>551</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>207</v>
+        <v>552</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>528</v>
+        <v>77</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>77</v>
@@ -12163,46 +12358,44 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>529</v>
+        <v>553</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>77</v>
+        <v>554</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I85" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J85" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>310</v>
+        <v>555</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>311</v>
+        <v>556</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O85" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>557</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
       </c>
@@ -12226,13 +12419,13 @@
         <v>77</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>314</v>
+        <v>77</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>315</v>
+        <v>77</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>77</v>
@@ -12250,13 +12443,13 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>316</v>
+        <v>558</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>77</v>
@@ -12265,13 +12458,13 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>317</v>
+        <v>559</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>318</v>
+        <v>560</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>319</v>
+        <v>561</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>77</v>
@@ -12285,10 +12478,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>530</v>
+        <v>562</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12299,7 +12492,7 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
         <v>77</v>
@@ -12311,17 +12504,15 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>321</v>
+        <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>322</v>
+        <v>563</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>324</v>
-      </c>
+        <v>564</v>
+      </c>
+      <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -12370,13 +12561,13 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>325</v>
+        <v>565</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
         <v>77</v>
@@ -12385,13 +12576,13 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>162</v>
+        <v>566</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>162</v>
+        <v>567</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>77</v>
+        <v>568</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>77</v>
@@ -12405,10 +12596,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>531</v>
+        <v>569</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12419,7 +12610,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>77</v>
@@ -12431,13 +12622,13 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>211</v>
+        <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>327</v>
+        <v>570</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>328</v>
+        <v>571</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12488,13 +12679,13 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>329</v>
+        <v>572</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>77</v>
@@ -12503,13 +12694,13 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>130</v>
+        <v>573</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>330</v>
+        <v>574</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="AN87" t="s" s="2">
         <v>77</v>
@@ -12523,10 +12714,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>532</v>
+        <v>575</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>532</v>
+        <v>575</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12546,20 +12737,20 @@
         <v>77</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>332</v>
+        <v>222</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>533</v>
+        <v>576</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>534</v>
+        <v>577</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>535</v>
+        <v>578</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12608,7 +12799,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>532</v>
+        <v>579</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12623,13 +12814,13 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>536</v>
+        <v>580</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>537</v>
+        <v>338</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>77</v>
+        <v>228</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>77</v>
@@ -12643,10 +12834,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>538</v>
+        <v>581</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>538</v>
+        <v>581</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12669,17 +12860,17 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>539</v>
+        <v>287</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>540</v>
+        <v>582</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>541</v>
+        <v>583</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>542</v>
+        <v>584</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12728,7 +12919,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>538</v>
+        <v>581</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12743,10 +12934,10 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>77</v>
+        <v>585</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>162</v>
+        <v>586</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12758,11 +12949,1089 @@
         <v>77</v>
       </c>
       <c r="AP89" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="90" hidden="true">
+      <c r="A90" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="B90" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="C90" s="2"/>
+      <c r="D90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E90" s="2"/>
+      <c r="F90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K90" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L90" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M90" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q90" s="2"/>
+      <c r="R90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF90" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG90" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH90" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL90" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP90" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="91" hidden="true">
+      <c r="A91" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="B91" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="C91" s="2"/>
+      <c r="D91" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E91" s="2"/>
+      <c r="F91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K91" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L91" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M91" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O91" s="2"/>
+      <c r="P91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q91" s="2"/>
+      <c r="R91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB91" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC91" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AD91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE91" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF91" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG91" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH91" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ91" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL91" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP91" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="92" hidden="true">
+      <c r="A92" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B92" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C92" s="2"/>
+      <c r="D92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E92" s="2"/>
+      <c r="F92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J92" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K92" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L92" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M92" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q92" s="2"/>
+      <c r="R92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X92" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y92" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z92" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AA92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF92" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG92" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH92" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI92" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AJ92" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK92" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM92" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP92" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" hidden="true">
+      <c r="A93" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="B93" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="C93" s="2"/>
+      <c r="D93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E93" s="2"/>
+      <c r="F93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J93" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K93" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L93" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M93" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q93" s="2"/>
+      <c r="R93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF93" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG93" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH93" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ93" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK93" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM93" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO93" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="AP93" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="94" hidden="true">
+      <c r="A94" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="B94" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="C94" s="2"/>
+      <c r="D94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E94" s="2"/>
+      <c r="F94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J94" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K94" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L94" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M94" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N94" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q94" s="2"/>
+      <c r="R94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X94" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y94" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z94" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AA94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF94" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG94" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH94" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ94" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK94" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM94" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP94" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="95" hidden="true">
+      <c r="A95" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="B95" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="C95" s="2"/>
+      <c r="D95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E95" s="2"/>
+      <c r="F95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J95" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K95" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L95" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M95" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="O95" s="2"/>
+      <c r="P95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q95" s="2"/>
+      <c r="R95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF95" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG95" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH95" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ95" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK95" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP95" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="96" hidden="true">
+      <c r="A96" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="B96" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="C96" s="2"/>
+      <c r="D96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E96" s="2"/>
+      <c r="F96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J96" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K96" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L96" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M96" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q96" s="2"/>
+      <c r="R96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF96" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG96" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH96" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ96" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK96" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM96" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP96" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="97" hidden="true">
+      <c r="A97" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="B97" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="C97" s="2"/>
+      <c r="D97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E97" s="2"/>
+      <c r="F97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K97" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L97" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="M97" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="P97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q97" s="2"/>
+      <c r="R97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF97" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AG97" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH97" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ97" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK97" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AM97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP97" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="98" hidden="true">
+      <c r="A98" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="B98" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="C98" s="2"/>
+      <c r="D98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E98" s="2"/>
+      <c r="F98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K98" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="L98" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M98" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N98" s="2"/>
+      <c r="O98" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="P98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q98" s="2"/>
+      <c r="R98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF98" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AG98" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH98" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ98" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL98" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP98" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP89">
+  <autoFilter ref="A1:AP98">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -12772,7 +14041,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI88">
+  <conditionalFormatting sqref="A2:AI97">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$98</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$124</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4753" uniqueCount="633">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.5.0</t>
+    <t>0.6.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T20:32:59+00:00</t>
+    <t>2023-11-29T21:08:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1397,6 +1397,87 @@
   </si>
   <si>
     <t>XAD.12 / XAD.13 + XAD.14</t>
+  </si>
+  <si>
+    <t>Organization.address:home</t>
+  </si>
+  <si>
+    <t>Organization.address:home.id</t>
+  </si>
+  <si>
+    <t>Organization.address:home.extension</t>
+  </si>
+  <si>
+    <t>Organization.address:home.use</t>
+  </si>
+  <si>
+    <t>Organization.address:home.type</t>
+  </si>
+  <si>
+    <t>Organization.address:home.text</t>
+  </si>
+  <si>
+    <t>Organization.address:home.line</t>
+  </si>
+  <si>
+    <t>Organization.address:home.city</t>
+  </si>
+  <si>
+    <t>Organization.address:home.district</t>
+  </si>
+  <si>
+    <t>Organization.address:home.state</t>
+  </si>
+  <si>
+    <t>Organization.address:home.postalCode</t>
+  </si>
+  <si>
+    <t>Organization.address:home.country</t>
+  </si>
+  <si>
+    <t>Organization.address:home.period</t>
+  </si>
+  <si>
+    <t>Organization.address:temp</t>
+  </si>
+  <si>
+    <t>temp</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.id</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.extension</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.use</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.type</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.text</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.line</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.city</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.district</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.state</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.postalCode</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.country</t>
+  </si>
+  <si>
+    <t>Organization.address:temp.period</t>
   </si>
   <si>
     <t>Organization.address:physical</t>
@@ -2212,7 +2293,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP98"/>
+  <dimension ref="A1:AP124"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.625" customWidth="true" bestFit="true"/>
@@ -7804,7 +7885,7 @@
         <v>339</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>444</v>
+        <v>358</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7922,7 +8003,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>351</v>
@@ -8040,7 +8121,7 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>352</v>
@@ -8160,7 +8241,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>353</v>
@@ -8282,7 +8363,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>364</v>
@@ -8379,7 +8460,7 @@
         <v>77</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>449</v>
+        <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
         <v>372</v>
@@ -8394,7 +8475,7 @@
         <v>77</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>77</v>
@@ -8402,7 +8483,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>373</v>
@@ -8524,7 +8605,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>382</v>
@@ -8634,15 +8715,15 @@
         <v>77</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>453</v>
+        <v>77</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>454</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>391</v>
@@ -8752,15 +8833,15 @@
         <v>77</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>456</v>
+        <v>77</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>457</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>458</v>
+        <v>451</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>400</v>
@@ -8872,15 +8953,15 @@
         <v>77</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>459</v>
+        <v>77</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>409</v>
@@ -8990,15 +9071,15 @@
         <v>77</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>462</v>
+        <v>77</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>463</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>419</v>
@@ -9108,15 +9189,15 @@
         <v>77</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>465</v>
+        <v>77</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>466</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>467</v>
+        <v>454</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>428</v>
@@ -9228,15 +9309,15 @@
         <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>469</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>436</v>
@@ -9356,13 +9437,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>471</v>
+        <v>456</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>339</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9480,7 +9561,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>473</v>
+        <v>458</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>351</v>
@@ -9598,7 +9679,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>459</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>352</v>
@@ -9718,7 +9799,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>460</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>353</v>
@@ -9840,7 +9921,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>476</v>
+        <v>461</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>364</v>
@@ -9937,7 +10018,7 @@
         <v>77</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>477</v>
+        <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>372</v>
@@ -9952,7 +10033,7 @@
         <v>77</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>478</v>
+        <v>77</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>77</v>
@@ -9960,7 +10041,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>373</v>
@@ -10082,7 +10163,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>480</v>
+        <v>463</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>382</v>
@@ -10192,7 +10273,7 @@
         <v>77</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>77</v>
@@ -10200,7 +10281,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>482</v>
+        <v>464</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>391</v>
@@ -10310,7 +10391,7 @@
         <v>77</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>483</v>
+        <v>77</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>77</v>
@@ -10318,7 +10399,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>484</v>
+        <v>465</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>400</v>
@@ -10438,7 +10519,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>485</v>
+        <v>466</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>409</v>
@@ -10548,7 +10629,7 @@
         <v>77</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>486</v>
+        <v>77</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10556,7 +10637,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>487</v>
+        <v>467</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>419</v>
@@ -10666,7 +10747,7 @@
         <v>77</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>488</v>
+        <v>77</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>77</v>
@@ -10674,7 +10755,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>489</v>
+        <v>468</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>428</v>
@@ -10786,15 +10867,15 @@
         <v>77</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>490</v>
+        <v>77</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>469</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>436</v>
@@ -10914,12 +10995,14 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>492</v>
+        <v>470</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>492</v>
-      </c>
-      <c r="C73" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="C73" t="s" s="2">
+        <v>471</v>
+      </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10931,26 +11014,28 @@
         <v>87</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J73" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>231</v>
+        <v>340</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>493</v>
+        <v>341</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>494</v>
-      </c>
-      <c r="N73" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N73" t="s" s="2">
+        <v>343</v>
+      </c>
       <c r="O73" t="s" s="2">
-        <v>495</v>
+        <v>344</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10999,28 +11084,28 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>492</v>
+        <v>339</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>77</v>
+        <v>346</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>99</v>
+        <v>347</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>251</v>
+        <v>348</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>496</v>
+        <v>349</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>167</v>
+        <v>350</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -11034,10 +11119,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>497</v>
+        <v>472</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>497</v>
+        <v>351</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11048,7 +11133,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -11060,20 +11145,16 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>498</v>
+        <v>163</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>499</v>
+        <v>164</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>500</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>501</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>502</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -11121,25 +11202,25 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>497</v>
+        <v>166</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>503</v>
+        <v>167</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -11156,21 +11237,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>504</v>
+        <v>473</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>504</v>
+        <v>352</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -11182,15 +11263,17 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N75" s="2"/>
+        <v>170</v>
+      </c>
+      <c r="N75" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11227,31 +11310,31 @@
         <v>77</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -11274,44 +11357,46 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>505</v>
+        <v>474</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>505</v>
+        <v>353</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>134</v>
+        <v>354</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>170</v>
+        <v>355</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O76" s="2"/>
+        <v>356</v>
+      </c>
+      <c r="O76" t="s" s="2">
+        <v>357</v>
+      </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -11323,7 +11408,7 @@
         <v>77</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>77</v>
@@ -11335,13 +11420,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -11359,28 +11444,28 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>173</v>
+        <v>361</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>77</v>
+        <v>362</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>167</v>
+        <v>326</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>77</v>
@@ -11394,46 +11479,44 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>506</v>
+        <v>475</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>506</v>
+        <v>364</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>508</v>
+        <v>365</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>509</v>
+        <v>366</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O77" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>367</v>
+      </c>
+      <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -11445,7 +11528,7 @@
         <v>77</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>77</v>
@@ -11457,13 +11540,13 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -11481,25 +11564,25 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>510</v>
+        <v>371</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>138</v>
+        <v>476</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>130</v>
+        <v>326</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -11508,7 +11591,7 @@
         <v>77</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>77</v>
+        <v>477</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>77</v>
@@ -11516,10 +11599,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>511</v>
+        <v>478</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>511</v>
+        <v>373</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11539,20 +11622,22 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>512</v>
+        <v>374</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N78" s="2"/>
+        <v>375</v>
+      </c>
+      <c r="N78" t="s" s="2">
+        <v>376</v>
+      </c>
       <c r="O78" t="s" s="2">
-        <v>514</v>
+        <v>377</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11565,7 +11650,7 @@
         <v>77</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>77</v>
@@ -11577,13 +11662,13 @@
         <v>77</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>515</v>
+        <v>77</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>516</v>
+        <v>77</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11601,7 +11686,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>511</v>
+        <v>379</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11616,10 +11701,10 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>517</v>
+        <v>381</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11636,10 +11721,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>518</v>
+        <v>479</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>518</v>
+        <v>382</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11650,30 +11735,28 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>87</v>
+        <v>383</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>519</v>
+        <v>163</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>520</v>
+        <v>384</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>521</v>
+        <v>385</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" t="s" s="2">
-        <v>522</v>
-      </c>
+      <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11685,7 +11768,7 @@
         <v>77</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>77</v>
@@ -11721,13 +11804,13 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>518</v>
+        <v>387</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
@@ -11736,34 +11819,34 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>523</v>
+        <v>388</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>524</v>
+        <v>389</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>77</v>
+        <v>390</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>77</v>
+        <v>480</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>525</v>
+        <v>482</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>525</v>
+        <v>391</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11773,22 +11856,22 @@
         <v>87</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>163</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>164</v>
+        <v>393</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>165</v>
+        <v>394</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11803,7 +11886,7 @@
         <v>77</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>77</v>
+        <v>395</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>77</v>
@@ -11839,7 +11922,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>166</v>
+        <v>396</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11851,44 +11934,44 @@
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>77</v>
+        <v>397</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>167</v>
+        <v>398</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>77</v>
+        <v>399</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>77</v>
+        <v>483</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>77</v>
+        <v>484</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>526</v>
+        <v>485</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>526</v>
+        <v>400</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>132</v>
+        <v>401</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11897,19 +11980,19 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>134</v>
+        <v>402</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>170</v>
+        <v>403</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>136</v>
+        <v>404</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11923,7 +12006,7 @@
         <v>77</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>77</v>
+        <v>405</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>77</v>
@@ -11947,37 +12030,37 @@
         <v>77</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>173</v>
+        <v>406</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>77</v>
+        <v>407</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>167</v>
+        <v>408</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -11986,22 +12069,22 @@
         <v>77</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>77</v>
+        <v>486</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>77</v>
+        <v>487</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>527</v>
+        <v>488</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>527</v>
+        <v>409</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>77</v>
+        <v>410</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12011,29 +12094,25 @@
         <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I82" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>528</v>
+        <v>411</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="N82" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="O82" t="s" s="2">
-        <v>531</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -12057,13 +12136,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>532</v>
+        <v>413</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>533</v>
+        <v>414</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12081,7 +12160,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>534</v>
+        <v>415</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12096,34 +12175,34 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>535</v>
+        <v>416</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>326</v>
+        <v>417</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>536</v>
+        <v>418</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>77</v>
+        <v>489</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>77</v>
+        <v>490</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>537</v>
+        <v>491</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>537</v>
+        <v>419</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12133,7 +12212,7 @@
         <v>87</v>
       </c>
       <c r="H83" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I83" t="s" s="2">
         <v>77</v>
@@ -12145,17 +12224,13 @@
         <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>538</v>
+        <v>421</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="N83" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="O83" t="s" s="2">
-        <v>377</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -12167,7 +12242,7 @@
         <v>77</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>77</v>
@@ -12203,7 +12278,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>541</v>
+        <v>424</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12218,34 +12293,34 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>542</v>
+        <v>425</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>381</v>
+        <v>426</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>77</v>
+        <v>427</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>543</v>
+        <v>492</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>77</v>
+        <v>493</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>544</v>
+        <v>494</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>544</v>
+        <v>428</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>545</v>
+        <v>77</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12255,7 +12330,7 @@
         <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>77</v>
@@ -12267,13 +12342,13 @@
         <v>163</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>546</v>
+        <v>429</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>547</v>
+        <v>430</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>548</v>
+        <v>431</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12323,7 +12398,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>549</v>
+        <v>432</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12338,41 +12413,41 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>550</v>
+        <v>433</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>551</v>
+        <v>434</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>552</v>
+        <v>435</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>77</v>
+        <v>495</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>77</v>
+        <v>496</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>553</v>
+        <v>497</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>553</v>
+        <v>436</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>554</v>
+        <v>77</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>77</v>
@@ -12384,18 +12459,18 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>163</v>
+        <v>222</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>555</v>
+        <v>437</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="N85" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="O85" s="2"/>
+        <v>438</v>
+      </c>
+      <c r="N85" s="2"/>
+      <c r="O85" t="s" s="2">
+        <v>439</v>
+      </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
       </c>
@@ -12407,7 +12482,7 @@
         <v>77</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>77</v>
+        <v>440</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>77</v>
@@ -12443,13 +12518,13 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>558</v>
+        <v>441</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>77</v>
@@ -12458,13 +12533,13 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>559</v>
+        <v>442</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>560</v>
+        <v>338</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>561</v>
+        <v>228</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>77</v>
@@ -12478,12 +12553,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>562</v>
+        <v>498</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="C86" t="s" s="2">
+        <v>499</v>
+      </c>
       <c r="D86" t="s" s="2">
         <v>77</v>
       </c>
@@ -12492,28 +12569,32 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H86" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J86" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>163</v>
+        <v>340</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>563</v>
+        <v>341</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
+        <v>342</v>
+      </c>
+      <c r="N86" t="s" s="2">
+        <v>343</v>
+      </c>
+      <c r="O86" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
       </c>
@@ -12561,7 +12642,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>565</v>
+        <v>339</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12570,19 +12651,19 @@
         <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>77</v>
+        <v>346</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>99</v>
+        <v>347</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>566</v>
+        <v>348</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>567</v>
+        <v>349</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>568</v>
+        <v>350</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>77</v>
@@ -12596,10 +12677,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>569</v>
+        <v>500</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>569</v>
+        <v>351</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12610,7 +12691,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>77</v>
@@ -12619,16 +12700,16 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>570</v>
+        <v>164</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>571</v>
+        <v>165</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12679,25 +12760,25 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>572</v>
+        <v>166</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>573</v>
+        <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>574</v>
+        <v>167</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -12714,21 +12795,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>575</v>
+        <v>501</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>575</v>
+        <v>352</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>77</v>
@@ -12737,21 +12818,21 @@
         <v>77</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>222</v>
+        <v>133</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>576</v>
+        <v>134</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="N88" s="2"/>
-      <c r="O88" t="s" s="2">
-        <v>578</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="N88" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12787,40 +12868,40 @@
         <v>77</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>77</v>
+        <v>171</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>77</v>
+        <v>172</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>579</v>
+        <v>173</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>580</v>
+        <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>338</v>
+        <v>167</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>228</v>
+        <v>77</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>77</v>
@@ -12834,10 +12915,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>581</v>
+        <v>502</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>581</v>
+        <v>353</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12848,29 +12929,31 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>287</v>
+        <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>582</v>
+        <v>354</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N89" s="2"/>
+        <v>355</v>
+      </c>
+      <c r="N89" t="s" s="2">
+        <v>356</v>
+      </c>
       <c r="O89" t="s" s="2">
-        <v>584</v>
+        <v>357</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12883,7 +12966,7 @@
         <v>77</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>77</v>
+        <v>358</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>77</v>
@@ -12895,13 +12978,13 @@
         <v>77</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>77</v>
+        <v>359</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>77</v>
@@ -12919,13 +13002,13 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>581</v>
+        <v>361</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>77</v>
@@ -12934,13 +13017,13 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>585</v>
+        <v>362</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>586</v>
+        <v>326</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>77</v>
+        <v>363</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>77</v>
@@ -12954,10 +13037,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>587</v>
+        <v>503</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>587</v>
+        <v>364</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12977,18 +13060,20 @@
         <v>77</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>164</v>
+        <v>365</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N90" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N90" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -13001,7 +13086,7 @@
         <v>77</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>77</v>
+        <v>368</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>77</v>
@@ -13013,13 +13098,13 @@
         <v>77</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>77</v>
+        <v>369</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>77</v>
+        <v>370</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -13037,7 +13122,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>166</v>
+        <v>371</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13049,13 +13134,13 @@
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>77</v>
+        <v>504</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>77</v>
+        <v>372</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>167</v>
+        <v>326</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -13064,7 +13149,7 @@
         <v>77</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>77</v>
+        <v>505</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>77</v>
@@ -13072,21 +13157,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>588</v>
+        <v>506</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>588</v>
+        <v>373</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>77</v>
@@ -13095,21 +13180,23 @@
         <v>77</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>134</v>
+        <v>374</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>170</v>
+        <v>375</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O91" s="2"/>
+        <v>376</v>
+      </c>
+      <c r="O91" t="s" s="2">
+        <v>377</v>
+      </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
       </c>
@@ -13121,7 +13208,7 @@
         <v>77</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>77</v>
+        <v>378</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>77</v>
@@ -13145,37 +13232,37 @@
         <v>77</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>173</v>
+        <v>379</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>77</v>
+        <v>380</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>167</v>
+        <v>381</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -13192,10 +13279,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>589</v>
+        <v>507</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>589</v>
+        <v>382</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13206,10 +13293,10 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>87</v>
+        <v>383</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>77</v>
@@ -13218,13 +13305,13 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>300</v>
+        <v>384</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>301</v>
+        <v>385</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13239,7 +13326,7 @@
         <v>77</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>77</v>
@@ -13251,13 +13338,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>302</v>
+        <v>77</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>303</v>
+        <v>77</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -13275,34 +13362,34 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>304</v>
+        <v>387</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>306</v>
+        <v>388</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>307</v>
+        <v>389</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>308</v>
+        <v>390</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>77</v>
+        <v>508</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>77</v>
@@ -13310,14 +13397,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>590</v>
+        <v>509</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>590</v>
+        <v>391</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>77</v>
+        <v>392</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13327,7 +13414,7 @@
         <v>87</v>
       </c>
       <c r="H93" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I93" t="s" s="2">
         <v>77</v>
@@ -13339,17 +13426,13 @@
         <v>163</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>310</v>
+        <v>393</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N93" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O93" t="s" s="2">
-        <v>313</v>
-      </c>
+        <v>394</v>
+      </c>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
       <c r="P93" t="s" s="2">
         <v>77</v>
       </c>
@@ -13361,7 +13444,7 @@
         <v>77</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>77</v>
+        <v>395</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>77</v>
@@ -13397,7 +13480,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>314</v>
+        <v>396</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13412,19 +13495,19 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>315</v>
+        <v>397</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>316</v>
+        <v>398</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>217</v>
+        <v>399</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>591</v>
+        <v>510</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>77</v>
@@ -13432,14 +13515,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>592</v>
+        <v>511</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>592</v>
+        <v>400</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>77</v>
+        <v>401</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13452,26 +13535,24 @@
         <v>77</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>107</v>
+        <v>163</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>318</v>
+        <v>402</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>319</v>
+        <v>403</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>320</v>
-      </c>
-      <c r="O94" t="s" s="2">
-        <v>321</v>
-      </c>
+        <v>404</v>
+      </c>
+      <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
         <v>77</v>
       </c>
@@ -13483,7 +13564,7 @@
         <v>77</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>77</v>
+        <v>405</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>77</v>
@@ -13495,13 +13576,13 @@
         <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>322</v>
+        <v>77</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -13519,7 +13600,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>324</v>
+        <v>406</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13534,13 +13615,13 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>325</v>
+        <v>407</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>77</v>
@@ -13554,14 +13635,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>593</v>
+        <v>512</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>593</v>
+        <v>409</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>77</v>
+        <v>410</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13571,7 +13652,7 @@
         <v>87</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>77</v>
@@ -13580,17 +13661,15 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>329</v>
+        <v>163</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>330</v>
+        <v>411</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="N95" t="s" s="2">
-        <v>332</v>
-      </c>
+        <v>412</v>
+      </c>
+      <c r="N95" s="2"/>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -13615,13 +13694,13 @@
         <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>77</v>
+        <v>192</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>77</v>
+        <v>413</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>77</v>
+        <v>414</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -13639,7 +13718,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>333</v>
+        <v>415</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13654,19 +13733,19 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>167</v>
+        <v>416</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>167</v>
+        <v>417</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>77</v>
+        <v>418</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>77</v>
+        <v>513</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>77</v>
@@ -13674,14 +13753,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>594</v>
+        <v>514</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>594</v>
+        <v>419</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>77</v>
+        <v>420</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13691,7 +13770,7 @@
         <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>77</v>
@@ -13700,13 +13779,13 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>222</v>
+        <v>163</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>335</v>
+        <v>421</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>336</v>
+        <v>422</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13721,7 +13800,7 @@
         <v>77</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>77</v>
+        <v>423</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>77</v>
@@ -13757,7 +13836,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>337</v>
+        <v>424</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13772,19 +13851,19 @@
         <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>130</v>
+        <v>425</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>338</v>
+        <v>426</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>228</v>
+        <v>427</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>77</v>
+        <v>515</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>77</v>
@@ -13792,10 +13871,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>595</v>
+        <v>516</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>595</v>
+        <v>428</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13809,27 +13888,27 @@
         <v>87</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>340</v>
+        <v>163</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>596</v>
+        <v>429</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="N97" s="2"/>
-      <c r="O97" t="s" s="2">
-        <v>598</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="N97" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
         <v>77</v>
       </c>
@@ -13877,7 +13956,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>595</v>
+        <v>432</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13892,30 +13971,30 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>599</v>
+        <v>433</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>600</v>
+        <v>434</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>77</v>
+        <v>435</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>77</v>
+        <v>517</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>77</v>
+        <v>496</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>601</v>
+        <v>518</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>601</v>
+        <v>436</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13926,7 +14005,7 @@
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>77</v>
@@ -13935,20 +14014,20 @@
         <v>77</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>602</v>
+        <v>222</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>603</v>
+        <v>437</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>604</v>
+        <v>438</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>605</v>
+        <v>439</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13961,7 +14040,7 @@
         <v>77</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>77</v>
+        <v>440</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>77</v>
@@ -13997,13 +14076,13 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>601</v>
+        <v>441</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>77</v>
@@ -14012,26 +14091,3144 @@
         <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>77</v>
+        <v>442</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP98" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="99" hidden="true">
+      <c r="A99" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="B99" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="C99" s="2"/>
+      <c r="D99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E99" s="2"/>
+      <c r="F99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G99" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J99" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K99" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L99" t="s" s="2">
+        <v>520</v>
+      </c>
+      <c r="M99" t="s" s="2">
+        <v>521</v>
+      </c>
+      <c r="N99" s="2"/>
+      <c r="O99" t="s" s="2">
+        <v>522</v>
+      </c>
+      <c r="P99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q99" s="2"/>
+      <c r="R99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF99" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AG99" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH99" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ99" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK99" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="AL99" t="s" s="2">
+        <v>523</v>
+      </c>
+      <c r="AM99" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AM98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP98" t="s" s="2">
+      <c r="AN99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO99" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP99" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="100" hidden="true">
+      <c r="A100" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="B100" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="C100" s="2"/>
+      <c r="D100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E100" s="2"/>
+      <c r="F100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K100" t="s" s="2">
+        <v>525</v>
+      </c>
+      <c r="L100" t="s" s="2">
+        <v>526</v>
+      </c>
+      <c r="M100" t="s" s="2">
+        <v>527</v>
+      </c>
+      <c r="N100" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O100" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="P100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q100" s="2"/>
+      <c r="R100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF100" t="s" s="2">
+        <v>524</v>
+      </c>
+      <c r="AG100" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH100" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ100" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL100" t="s" s="2">
+        <v>530</v>
+      </c>
+      <c r="AM100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO100" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP100" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="101" hidden="true">
+      <c r="A101" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="B101" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="C101" s="2"/>
+      <c r="D101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E101" s="2"/>
+      <c r="F101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G101" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K101" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L101" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M101" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q101" s="2"/>
+      <c r="R101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF101" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG101" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH101" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL101" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO101" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP101" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="102" hidden="true">
+      <c r="A102" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="B102" t="s" s="2">
+        <v>532</v>
+      </c>
+      <c r="C102" s="2"/>
+      <c r="D102" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E102" s="2"/>
+      <c r="F102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K102" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L102" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M102" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N102" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O102" s="2"/>
+      <c r="P102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q102" s="2"/>
+      <c r="R102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF102" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG102" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH102" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ102" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL102" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO102" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP102" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="103" hidden="true">
+      <c r="A103" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="B103" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="C103" s="2"/>
+      <c r="D103" t="s" s="2">
+        <v>534</v>
+      </c>
+      <c r="E103" s="2"/>
+      <c r="F103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J103" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K103" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L103" t="s" s="2">
+        <v>535</v>
+      </c>
+      <c r="M103" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N103" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O103" t="s" s="2">
+        <v>142</v>
+      </c>
+      <c r="P103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q103" s="2"/>
+      <c r="R103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF103" t="s" s="2">
+        <v>537</v>
+      </c>
+      <c r="AG103" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH103" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ103" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL103" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO103" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP103" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="104" hidden="true">
+      <c r="A104" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="C104" s="2"/>
+      <c r="D104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L104" t="s" s="2">
+        <v>539</v>
+      </c>
+      <c r="M104" t="s" s="2">
+        <v>540</v>
+      </c>
+      <c r="N104" s="2"/>
+      <c r="O104" t="s" s="2">
+        <v>541</v>
+      </c>
+      <c r="P104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q104" s="2"/>
+      <c r="R104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X104" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y104" t="s" s="2">
+        <v>542</v>
+      </c>
+      <c r="Z104" t="s" s="2">
+        <v>543</v>
+      </c>
+      <c r="AA104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF104" t="s" s="2">
+        <v>538</v>
+      </c>
+      <c r="AG104" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH104" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ104" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL104" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="AM104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO104" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP104" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="105" hidden="true">
+      <c r="A105" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="B105" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="C105" s="2"/>
+      <c r="D105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E105" s="2"/>
+      <c r="F105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K105" t="s" s="2">
+        <v>546</v>
+      </c>
+      <c r="L105" t="s" s="2">
+        <v>547</v>
+      </c>
+      <c r="M105" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N105" s="2"/>
+      <c r="O105" t="s" s="2">
+        <v>549</v>
+      </c>
+      <c r="P105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q105" s="2"/>
+      <c r="R105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF105" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="AG105" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH105" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ105" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK105" t="s" s="2">
+        <v>550</v>
+      </c>
+      <c r="AL105" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="AM105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO105" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP105" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="106" hidden="true">
+      <c r="A106" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="B106" t="s" s="2">
+        <v>552</v>
+      </c>
+      <c r="C106" s="2"/>
+      <c r="D106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E106" s="2"/>
+      <c r="F106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K106" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L106" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M106" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q106" s="2"/>
+      <c r="R106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF106" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG106" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH106" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL106" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO106" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP106" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="107" hidden="true">
+      <c r="A107" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>553</v>
+      </c>
+      <c r="C107" s="2"/>
+      <c r="D107" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E107" s="2"/>
+      <c r="F107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K107" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L107" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M107" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N107" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O107" s="2"/>
+      <c r="P107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q107" s="2"/>
+      <c r="R107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB107" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC107" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AD107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE107" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF107" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG107" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH107" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ107" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL107" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO107" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP107" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="108" hidden="true">
+      <c r="A108" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="C108" s="2"/>
+      <c r="D108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E108" s="2"/>
+      <c r="F108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G108" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J108" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K108" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L108" t="s" s="2">
+        <v>555</v>
+      </c>
+      <c r="M108" t="s" s="2">
+        <v>556</v>
+      </c>
+      <c r="N108" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="O108" t="s" s="2">
+        <v>558</v>
+      </c>
+      <c r="P108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q108" s="2"/>
+      <c r="R108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X108" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y108" t="s" s="2">
+        <v>559</v>
+      </c>
+      <c r="Z108" t="s" s="2">
+        <v>560</v>
+      </c>
+      <c r="AA108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF108" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AG108" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH108" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ108" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK108" t="s" s="2">
+        <v>562</v>
+      </c>
+      <c r="AL108" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM108" t="s" s="2">
+        <v>563</v>
+      </c>
+      <c r="AN108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO108" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP108" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="109" hidden="true">
+      <c r="A109" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="C109" s="2"/>
+      <c r="D109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E109" s="2"/>
+      <c r="F109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G109" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J109" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K109" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L109" t="s" s="2">
+        <v>565</v>
+      </c>
+      <c r="M109" t="s" s="2">
+        <v>566</v>
+      </c>
+      <c r="N109" t="s" s="2">
+        <v>567</v>
+      </c>
+      <c r="O109" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="P109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q109" s="2"/>
+      <c r="R109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF109" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="AG109" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH109" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ109" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK109" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="AL109" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="AM109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN109" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO109" t="s" s="2">
+        <v>570</v>
+      </c>
+      <c r="AP109" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="110" hidden="true">
+      <c r="A110" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="B110" t="s" s="2">
+        <v>571</v>
+      </c>
+      <c r="C110" s="2"/>
+      <c r="D110" t="s" s="2">
+        <v>572</v>
+      </c>
+      <c r="E110" s="2"/>
+      <c r="F110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G110" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J110" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K110" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L110" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="M110" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="N110" t="s" s="2">
+        <v>575</v>
+      </c>
+      <c r="O110" s="2"/>
+      <c r="P110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q110" s="2"/>
+      <c r="R110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF110" t="s" s="2">
+        <v>576</v>
+      </c>
+      <c r="AG110" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH110" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ110" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK110" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="AL110" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="AM110" t="s" s="2">
+        <v>579</v>
+      </c>
+      <c r="AN110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO110" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP110" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="111" hidden="true">
+      <c r="A111" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="B111" t="s" s="2">
+        <v>580</v>
+      </c>
+      <c r="C111" s="2"/>
+      <c r="D111" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="E111" s="2"/>
+      <c r="F111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J111" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K111" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L111" t="s" s="2">
+        <v>582</v>
+      </c>
+      <c r="M111" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="N111" t="s" s="2">
+        <v>584</v>
+      </c>
+      <c r="O111" s="2"/>
+      <c r="P111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q111" s="2"/>
+      <c r="R111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF111" t="s" s="2">
+        <v>585</v>
+      </c>
+      <c r="AG111" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH111" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ111" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK111" t="s" s="2">
+        <v>586</v>
+      </c>
+      <c r="AL111" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="AM111" t="s" s="2">
+        <v>588</v>
+      </c>
+      <c r="AN111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO111" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP111" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="112" hidden="true">
+      <c r="A112" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="B112" t="s" s="2">
+        <v>589</v>
+      </c>
+      <c r="C112" s="2"/>
+      <c r="D112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E112" s="2"/>
+      <c r="F112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J112" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K112" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L112" t="s" s="2">
+        <v>590</v>
+      </c>
+      <c r="M112" t="s" s="2">
+        <v>591</v>
+      </c>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q112" s="2"/>
+      <c r="R112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF112" t="s" s="2">
+        <v>592</v>
+      </c>
+      <c r="AG112" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH112" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ112" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK112" t="s" s="2">
+        <v>593</v>
+      </c>
+      <c r="AL112" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="AM112" t="s" s="2">
+        <v>595</v>
+      </c>
+      <c r="AN112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO112" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP112" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="113" hidden="true">
+      <c r="A113" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="B113" t="s" s="2">
+        <v>596</v>
+      </c>
+      <c r="C113" s="2"/>
+      <c r="D113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E113" s="2"/>
+      <c r="F113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J113" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K113" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>597</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>598</v>
+      </c>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q113" s="2"/>
+      <c r="R113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF113" t="s" s="2">
+        <v>599</v>
+      </c>
+      <c r="AG113" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH113" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ113" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK113" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="AL113" t="s" s="2">
+        <v>601</v>
+      </c>
+      <c r="AM113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO113" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP113" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="114" hidden="true">
+      <c r="A114" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="B114" t="s" s="2">
+        <v>602</v>
+      </c>
+      <c r="C114" s="2"/>
+      <c r="D114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E114" s="2"/>
+      <c r="F114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G114" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J114" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K114" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L114" t="s" s="2">
+        <v>603</v>
+      </c>
+      <c r="M114" t="s" s="2">
+        <v>604</v>
+      </c>
+      <c r="N114" s="2"/>
+      <c r="O114" t="s" s="2">
+        <v>605</v>
+      </c>
+      <c r="P114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q114" s="2"/>
+      <c r="R114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF114" t="s" s="2">
+        <v>606</v>
+      </c>
+      <c r="AG114" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH114" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ114" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK114" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="AL114" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM114" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO114" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP114" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="115" hidden="true">
+      <c r="A115" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="B115" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="C115" s="2"/>
+      <c r="D115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E115" s="2"/>
+      <c r="F115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K115" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="L115" t="s" s="2">
+        <v>609</v>
+      </c>
+      <c r="M115" t="s" s="2">
+        <v>610</v>
+      </c>
+      <c r="N115" s="2"/>
+      <c r="O115" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="P115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q115" s="2"/>
+      <c r="R115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF115" t="s" s="2">
+        <v>608</v>
+      </c>
+      <c r="AG115" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH115" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ115" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK115" t="s" s="2">
+        <v>612</v>
+      </c>
+      <c r="AL115" t="s" s="2">
+        <v>613</v>
+      </c>
+      <c r="AM115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO115" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP115" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="116" hidden="true">
+      <c r="A116" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="B116" t="s" s="2">
+        <v>614</v>
+      </c>
+      <c r="C116" s="2"/>
+      <c r="D116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E116" s="2"/>
+      <c r="F116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K116" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L116" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M116" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q116" s="2"/>
+      <c r="R116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF116" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AG116" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH116" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL116" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO116" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP116" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="117" hidden="true">
+      <c r="A117" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>615</v>
+      </c>
+      <c r="C117" s="2"/>
+      <c r="D117" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="E117" s="2"/>
+      <c r="F117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K117" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L117" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M117" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="N117" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="O117" s="2"/>
+      <c r="P117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q117" s="2"/>
+      <c r="R117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB117" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC117" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AD117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE117" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF117" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG117" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH117" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ117" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL117" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO117" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP117" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="118" hidden="true">
+      <c r="A118" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="B118" t="s" s="2">
+        <v>616</v>
+      </c>
+      <c r="C118" s="2"/>
+      <c r="D118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E118" s="2"/>
+      <c r="F118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G118" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J118" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K118" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L118" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
+      <c r="P118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q118" s="2"/>
+      <c r="R118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF118" t="s" s="2">
+        <v>304</v>
+      </c>
+      <c r="AG118" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI118" t="s" s="2">
+        <v>305</v>
+      </c>
+      <c r="AJ118" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK118" t="s" s="2">
+        <v>306</v>
+      </c>
+      <c r="AL118" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="AM118" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="AN118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO118" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP118" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="119" hidden="true">
+      <c r="A119" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="B119" t="s" s="2">
+        <v>617</v>
+      </c>
+      <c r="C119" s="2"/>
+      <c r="D119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E119" s="2"/>
+      <c r="F119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G119" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J119" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K119" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L119" t="s" s="2">
+        <v>310</v>
+      </c>
+      <c r="M119" t="s" s="2">
+        <v>311</v>
+      </c>
+      <c r="N119" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="O119" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="P119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q119" s="2"/>
+      <c r="R119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF119" t="s" s="2">
+        <v>314</v>
+      </c>
+      <c r="AG119" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH119" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ119" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK119" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL119" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM119" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AN119" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO119" t="s" s="2">
+        <v>618</v>
+      </c>
+      <c r="AP119" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="120" hidden="true">
+      <c r="A120" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="B120" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="C120" s="2"/>
+      <c r="D120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E120" s="2"/>
+      <c r="F120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G120" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I120" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J120" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K120" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L120" t="s" s="2">
+        <v>318</v>
+      </c>
+      <c r="M120" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="N120" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="O120" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="P120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X120" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="Y120" t="s" s="2">
+        <v>322</v>
+      </c>
+      <c r="Z120" t="s" s="2">
+        <v>323</v>
+      </c>
+      <c r="AA120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF120" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AG120" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH120" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ120" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK120" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="AL120" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="AM120" t="s" s="2">
+        <v>327</v>
+      </c>
+      <c r="AN120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO120" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP120" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="121" hidden="true">
+      <c r="A121" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="B121" t="s" s="2">
+        <v>620</v>
+      </c>
+      <c r="C121" s="2"/>
+      <c r="D121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E121" s="2"/>
+      <c r="F121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J121" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K121" t="s" s="2">
+        <v>329</v>
+      </c>
+      <c r="L121" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="M121" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="N121" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="O121" s="2"/>
+      <c r="P121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q121" s="2"/>
+      <c r="R121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF121" t="s" s="2">
+        <v>333</v>
+      </c>
+      <c r="AG121" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH121" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ121" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK121" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL121" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO121" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP121" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="B122" t="s" s="2">
+        <v>621</v>
+      </c>
+      <c r="C122" s="2"/>
+      <c r="D122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E122" s="2"/>
+      <c r="F122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G122" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J122" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K122" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q122" s="2"/>
+      <c r="R122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF122" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AG122" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH122" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ122" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK122" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AL122" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM122" t="s" s="2">
+        <v>228</v>
+      </c>
+      <c r="AN122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO122" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP122" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="123" hidden="true">
+      <c r="A123" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="B123" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="C123" s="2"/>
+      <c r="D123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E123" s="2"/>
+      <c r="F123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G123" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K123" t="s" s="2">
+        <v>340</v>
+      </c>
+      <c r="L123" t="s" s="2">
+        <v>623</v>
+      </c>
+      <c r="M123" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="N123" s="2"/>
+      <c r="O123" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="P123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q123" s="2"/>
+      <c r="R123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF123" t="s" s="2">
+        <v>622</v>
+      </c>
+      <c r="AG123" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH123" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ123" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK123" t="s" s="2">
+        <v>626</v>
+      </c>
+      <c r="AL123" t="s" s="2">
+        <v>627</v>
+      </c>
+      <c r="AM123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO123" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP123" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="124" hidden="true">
+      <c r="A124" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="B124" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="C124" s="2"/>
+      <c r="D124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E124" s="2"/>
+      <c r="F124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K124" t="s" s="2">
+        <v>629</v>
+      </c>
+      <c r="L124" t="s" s="2">
+        <v>630</v>
+      </c>
+      <c r="M124" t="s" s="2">
+        <v>631</v>
+      </c>
+      <c r="N124" s="2"/>
+      <c r="O124" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="P124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q124" s="2"/>
+      <c r="R124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF124" t="s" s="2">
+        <v>628</v>
+      </c>
+      <c r="AG124" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH124" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ124" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL124" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AM124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO124" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AP124" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP98">
+  <autoFilter ref="A1:AP124">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -14041,7 +17238,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI97">
+  <conditionalFormatting sqref="A2:AI123">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-11-29T21:08:10+00:00</t>
+    <t>2023-12-12T19:04:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4753" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4753" uniqueCount="625">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.7.0</t>
+    <t>0.9.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-12T19:04:11+00:00</t>
+    <t>2023-12-21T07:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,6 +505,221 @@
   </si>
   <si>
     <t>FiveWs.identifier</t>
+  </si>
+  <si>
+    <t>Organization.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>./IdentifierType</t>
+  </si>
+  <si>
+    <t>Organization.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>./Value</t>
+  </si>
+  <si>
+    <t>1252: source value from INSTITUTION - NPI (#4-41.99) case NPI slice</t>
+  </si>
+  <si>
+    <t>Dim.Institution.NPI</t>
+  </si>
+  <si>
+    <t>Organization.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
+    <t>Organization.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>./IdentifierIssuingAuthority</t>
   </si>
   <si>
     <t>Organization.identifier:NPI</t>
@@ -521,245 +736,6 @@
 &lt;/valueIdentifier&gt;</t>
   </si>
   <si>
-    <t>Organization.identifier:NPI.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NPI.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NPI.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NPI.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NPI.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>./IdentifierType</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NPI.value</t>
-  </si>
-  <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>./Value</t>
-  </si>
-  <si>
-    <t>1252: source value from INSTITUTION - NPI (#4-41.99)</t>
-  </si>
-  <si>
-    <t>Dim.Institution.NPI</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NPI.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NPI.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
     <t>Organization.identifier:CLIA</t>
   </si>
   <si>
@@ -798,7 +774,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-22:1253: fixed value = true {null}</t>
+inv-23:1253: fixed value = true {null}</t>
   </si>
   <si>
     <t>No equivalent in HL7 v2</t>
@@ -843,7 +819,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-23:1254: fixed value = #prov {null}</t>
+inv-24:1254: fixed value = prov {null}</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -855,7 +831,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1254: fixed value = #prov</t>
+    <t>1254: fixed value = prov</t>
   </si>
   <si>
     <t>Organization.name</t>
@@ -1499,7 +1475,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-24:1257: fixed value = #physical {null}</t>
+inv-25:1257: fixed value = #physical {null}</t>
   </si>
   <si>
     <t>1257: fixed value = #physical</t>
@@ -1585,7 +1561,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-25:1268: fixed value = #postal {null}</t>
+inv-26:1268: fixed value = #postal {null}</t>
   </si>
   <si>
     <t>1268: fixed value = #postal</t>
@@ -3672,11 +3648,9 @@
         <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C12" t="s" s="2">
-        <v>158</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3688,27 +3662,25 @@
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" t="s" s="2">
-        <v>149</v>
-      </c>
+      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3717,7 +3689,7 @@
         <v>77</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>77</v>
@@ -3756,31 +3728,31 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>153</v>
+        <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>77</v>
@@ -3791,21 +3763,21 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3817,15 +3789,17 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="L13" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="M13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" s="2"/>
+      <c r="N13" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3862,37 +3836,37 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
         <v>77</v>
@@ -3912,41 +3886,43 @@
         <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>107</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>171</v>
+      </c>
+      <c r="O14" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3970,49 +3946,49 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>77</v>
+        <v>174</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>77</v>
+        <v>130</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -4029,10 +4005,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -4049,25 +4025,25 @@
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>179</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -4092,13 +4068,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -4116,7 +4092,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4131,10 +4107,10 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -4151,10 +4127,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4168,7 +4144,7 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
@@ -4177,19 +4153,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>187</v>
+        <v>101</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -4202,7 +4178,7 @@
         <v>77</v>
       </c>
       <c r="T16" t="s" s="2">
-        <v>77</v>
+        <v>194</v>
       </c>
       <c r="U16" t="s" s="2">
         <v>77</v>
@@ -4214,13 +4190,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>192</v>
+        <v>77</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>193</v>
+        <v>77</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>194</v>
+        <v>77</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -4256,10 +4232,10 @@
         <v>196</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="AN16" t="s" s="2">
         <v>77</v>
@@ -4273,10 +4249,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4290,7 +4266,7 @@
         <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
@@ -4299,20 +4275,18 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>101</v>
+        <v>158</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="O17" t="s" s="2">
         <v>202</v>
       </c>
+      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -4387,18 +4361,18 @@
         <v>77</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4421,17 +4395,15 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>163</v>
+        <v>211</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>213</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -4444,7 +4416,7 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>77</v>
@@ -4507,18 +4479,18 @@
         <v>77</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>218</v>
+        <v>77</v>
       </c>
       <c r="AP18" t="s" s="2">
-        <v>219</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4541,15 +4513,17 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>220</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="L19" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>224</v>
-      </c>
-      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4598,7 +4572,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4613,13 +4587,13 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>225</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AL19" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="AM19" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
         <v>77</v>
@@ -4633,12 +4607,14 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C20" t="s" s="2">
+        <v>228</v>
+      </c>
       <c r="D20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4650,7 +4626,7 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
@@ -4659,18 +4635,18 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>231</v>
+        <v>145</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>234</v>
-      </c>
-      <c r="O20" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N20" s="2"/>
+      <c r="O20" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4679,7 +4655,7 @@
         <v>77</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>77</v>
+        <v>230</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>77</v>
@@ -4718,31 +4694,31 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>144</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>236</v>
+        <v>153</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>237</v>
+        <v>154</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>238</v>
+        <v>155</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
       <c r="AO20" t="s" s="2">
         <v>77</v>
@@ -4753,13 +4729,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4784,7 +4760,7 @@
         <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>147</v>
@@ -4801,7 +4777,7 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>77</v>
@@ -4875,10 +4851,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4901,97 +4877,97 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
+        <v>236</v>
+      </c>
+      <c r="L22" t="s" s="2">
+        <v>237</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>239</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="P22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q22" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="R22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
+        <v>235</v>
+      </c>
+      <c r="AG22" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH22" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ22" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AK22" t="s" s="2">
+        <v>243</v>
+      </c>
+      <c r="AL22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="L22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="M22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="N22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="R22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AG22" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH22" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ22" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="AK22" t="s" s="2">
-        <v>251</v>
-      </c>
-      <c r="AL22" t="s" s="2">
-        <v>252</v>
-      </c>
-      <c r="AM22" t="s" s="2">
-        <v>253</v>
-      </c>
-      <c r="AN22" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>255</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>77</v>
@@ -4999,10 +4975,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5025,19 +5001,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>259</v>
+        <v>251</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -5062,13 +5038,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -5086,7 +5062,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5098,22 +5074,22 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>265</v>
+        <v>257</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>77</v>
@@ -5121,10 +5097,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5147,19 +5123,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5208,7 +5184,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5223,30 +5199,30 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>278</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5269,19 +5245,19 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5330,7 +5306,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5348,7 +5324,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>275</v>
+        <v>267</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -5357,18 +5333,18 @@
         <v>77</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5391,19 +5367,19 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>289</v>
+        <v>281</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5452,7 +5428,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5461,19 +5437,19 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>293</v>
+        <v>285</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -5487,10 +5463,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5513,13 +5489,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5570,7 +5546,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5588,7 +5564,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -5605,10 +5581,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5637,7 +5613,7 @@
         <v>134</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>136</v>
@@ -5678,10 +5654,10 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
@@ -5690,7 +5666,7 @@
         <v>151</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5708,7 +5684,7 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -5725,10 +5701,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5754,10 +5730,10 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5784,13 +5760,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5808,7 +5784,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5817,19 +5793,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5843,10 +5819,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5869,19 +5845,19 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5930,7 +5906,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5945,13 +5921,13 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5965,10 +5941,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5994,16 +5970,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6028,13 +6004,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -6052,7 +6028,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6067,13 +6043,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -6087,10 +6063,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6113,16 +6089,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6172,7 +6148,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6187,10 +6163,10 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
@@ -6207,10 +6183,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6233,13 +6209,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6290,7 +6266,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6308,10 +6284,10 @@
         <v>130</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AN33" t="s" s="2">
         <v>77</v>
@@ -6325,10 +6301,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6351,19 +6327,19 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6400,7 +6376,7 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>345</v>
+        <v>337</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -6410,7 +6386,7 @@
         <v>151</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6419,19 +6395,19 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -6445,10 +6421,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6471,13 +6447,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6528,7 +6504,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6546,7 +6522,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -6563,10 +6539,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6595,7 +6571,7 @@
         <v>134</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>136</v>
@@ -6636,10 +6612,10 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
@@ -6648,7 +6624,7 @@
         <v>151</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6666,7 +6642,7 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
@@ -6683,10 +6659,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6712,16 +6688,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6734,7 +6710,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6746,13 +6722,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6770,7 +6746,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6785,13 +6761,13 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6805,10 +6781,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6834,13 +6810,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6854,7 +6830,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6866,13 +6842,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6890,7 +6866,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6905,10 +6881,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6925,10 +6901,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6951,19 +6927,19 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6976,7 +6952,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -7012,7 +6988,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7027,10 +7003,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -7047,10 +7023,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7061,7 +7037,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -7073,13 +7049,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7094,7 +7070,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -7130,7 +7106,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7145,13 +7121,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -7165,14 +7141,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7191,13 +7167,13 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7212,7 +7188,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -7248,7 +7224,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7263,13 +7239,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -7283,14 +7259,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7309,16 +7285,16 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7332,7 +7308,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -7368,7 +7344,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7383,10 +7359,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7403,14 +7379,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7429,13 +7405,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7462,13 +7438,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7486,7 +7462,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7501,13 +7477,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -7521,14 +7497,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7547,13 +7523,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7568,7 +7544,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7604,7 +7580,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7619,13 +7595,13 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7639,10 +7615,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7665,16 +7641,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7724,7 +7700,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7739,13 +7715,13 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7759,10 +7735,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7785,17 +7761,17 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7808,7 +7784,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7844,7 +7820,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7859,13 +7835,13 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -7879,13 +7855,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>443</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7907,19 +7883,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7968,7 +7944,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7977,19 +7953,19 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -8003,10 +7979,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8029,13 +8005,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -8086,7 +8062,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -8104,7 +8080,7 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
@@ -8121,10 +8097,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>445</v>
+        <v>437</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8153,7 +8129,7 @@
         <v>134</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>136</v>
@@ -8194,10 +8170,10 @@
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
@@ -8206,7 +8182,7 @@
         <v>151</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8224,7 +8200,7 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
@@ -8241,10 +8217,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>446</v>
+        <v>438</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8270,16 +8246,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8292,7 +8268,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -8304,13 +8280,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -8328,7 +8304,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8343,13 +8319,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8363,10 +8339,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>447</v>
+        <v>439</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8392,13 +8368,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8412,7 +8388,7 @@
         <v>77</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -8424,13 +8400,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8448,7 +8424,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8463,10 +8439,10 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8483,10 +8459,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8509,19 +8485,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8534,7 +8510,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -8570,7 +8546,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8585,10 +8561,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8605,10 +8581,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>449</v>
+        <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8619,7 +8595,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>88</v>
@@ -8631,13 +8607,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8652,7 +8628,7 @@
         <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>77</v>
@@ -8688,7 +8664,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8703,13 +8679,13 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -8723,14 +8699,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>450</v>
+        <v>442</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8749,13 +8725,13 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8770,7 +8746,7 @@
         <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8806,7 +8782,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8821,13 +8797,13 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -8841,14 +8817,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>451</v>
+        <v>443</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8867,16 +8843,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8890,7 +8866,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8926,7 +8902,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8941,10 +8917,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8961,14 +8937,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>444</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8987,13 +8963,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -9020,13 +8996,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -9044,7 +9020,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9059,13 +9035,13 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -9079,14 +9055,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9105,13 +9081,13 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9126,7 +9102,7 @@
         <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>77</v>
@@ -9162,7 +9138,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9177,13 +9153,13 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -9197,10 +9173,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9223,16 +9199,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9282,7 +9258,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9297,13 +9273,13 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -9317,10 +9293,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>455</v>
+        <v>447</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9343,17 +9319,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9366,7 +9342,7 @@
         <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>77</v>
@@ -9402,7 +9378,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9417,13 +9393,13 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -9437,13 +9413,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>456</v>
+        <v>448</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>457</v>
+        <v>449</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9465,19 +9441,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9526,7 +9502,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9535,19 +9511,19 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -9561,10 +9537,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>458</v>
+        <v>450</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9587,13 +9563,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9644,7 +9620,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9662,7 +9638,7 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
@@ -9679,10 +9655,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>459</v>
+        <v>451</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9711,7 +9687,7 @@
         <v>134</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>136</v>
@@ -9752,10 +9728,10 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
@@ -9764,7 +9740,7 @@
         <v>151</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9782,7 +9758,7 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
@@ -9799,10 +9775,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>460</v>
+        <v>452</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9828,16 +9804,16 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9850,7 +9826,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9862,13 +9838,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9886,7 +9862,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9901,13 +9877,13 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9921,10 +9897,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>461</v>
+        <v>453</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9950,13 +9926,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9970,7 +9946,7 @@
         <v>77</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9982,13 +9958,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -10006,7 +9982,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -10021,10 +9997,10 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -10041,10 +10017,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>462</v>
+        <v>454</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10067,19 +10043,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -10092,7 +10068,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -10128,7 +10104,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10143,10 +10119,10 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -10163,10 +10139,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>463</v>
+        <v>455</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10177,7 +10153,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>88</v>
@@ -10189,13 +10165,13 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10210,7 +10186,7 @@
         <v>77</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>77</v>
@@ -10246,7 +10222,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10261,13 +10237,13 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -10281,14 +10257,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10307,13 +10283,13 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10328,7 +10304,7 @@
         <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>77</v>
@@ -10364,7 +10340,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10379,13 +10355,13 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -10399,14 +10375,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10425,16 +10401,16 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10448,7 +10424,7 @@
         <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>77</v>
@@ -10484,7 +10460,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10499,10 +10475,10 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -10519,14 +10495,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>466</v>
+        <v>458</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10545,13 +10521,13 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10578,13 +10554,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10602,7 +10578,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10617,13 +10593,13 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -10637,14 +10613,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>467</v>
+        <v>459</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10663,13 +10639,13 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10684,7 +10660,7 @@
         <v>77</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>77</v>
@@ -10720,7 +10696,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10735,13 +10711,13 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -10755,10 +10731,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>468</v>
+        <v>460</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10781,16 +10757,16 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10840,7 +10816,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10855,13 +10831,13 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -10875,10 +10851,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10901,17 +10877,17 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10924,7 +10900,7 @@
         <v>77</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>77</v>
@@ -10960,7 +10936,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10975,13 +10951,13 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -10995,13 +10971,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>471</v>
+        <v>463</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
@@ -11023,19 +10999,19 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -11084,7 +11060,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11093,19 +11069,19 @@
         <v>79</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -11119,10 +11095,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>472</v>
+        <v>464</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11145,13 +11121,13 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -11202,7 +11178,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11220,7 +11196,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -11237,10 +11213,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>473</v>
+        <v>465</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11269,7 +11245,7 @@
         <v>134</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N75" t="s" s="2">
         <v>136</v>
@@ -11310,10 +11286,10 @@
         <v>77</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>77</v>
@@ -11322,7 +11298,7 @@
         <v>151</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11340,7 +11316,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -11357,10 +11333,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>474</v>
+        <v>466</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11386,16 +11362,16 @@
         <v>107</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -11408,7 +11384,7 @@
         <v>77</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>77</v>
@@ -11420,13 +11396,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -11444,7 +11420,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11459,13 +11435,13 @@
         <v>99</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>77</v>
@@ -11479,10 +11455,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>475</v>
+        <v>467</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11508,13 +11484,13 @@
         <v>107</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -11528,7 +11504,7 @@
         <v>77</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>77</v>
@@ -11540,13 +11516,13 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -11564,7 +11540,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11576,13 +11552,13 @@
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>476</v>
+        <v>468</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -11591,7 +11567,7 @@
         <v>77</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>477</v>
+        <v>469</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>77</v>
@@ -11599,10 +11575,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>478</v>
+        <v>470</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11625,19 +11601,19 @@
         <v>88</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="O78" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11650,7 +11626,7 @@
         <v>77</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>77</v>
@@ -11686,7 +11662,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11701,10 +11677,10 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11721,10 +11697,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>479</v>
+        <v>471</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11735,7 +11711,7 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H79" t="s" s="2">
         <v>88</v>
@@ -11747,13 +11723,13 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11768,7 +11744,7 @@
         <v>77</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>77</v>
@@ -11804,7 +11780,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11819,34 +11795,34 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>480</v>
+        <v>472</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>482</v>
+        <v>474</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11865,13 +11841,13 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11886,7 +11862,7 @@
         <v>77</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>77</v>
@@ -11922,7 +11898,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11937,34 +11913,34 @@
         <v>99</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>483</v>
+        <v>475</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>485</v>
+        <v>477</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11983,16 +11959,16 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -12006,7 +11982,7 @@
         <v>77</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>77</v>
@@ -12042,7 +12018,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -12057,10 +12033,10 @@
         <v>99</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -12069,22 +12045,22 @@
         <v>77</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>486</v>
+        <v>478</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>488</v>
+        <v>480</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12103,13 +12079,13 @@
         <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -12136,13 +12112,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12160,7 +12136,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12175,34 +12151,34 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>489</v>
+        <v>481</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>491</v>
+        <v>483</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12221,13 +12197,13 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12242,7 +12218,7 @@
         <v>77</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>77</v>
@@ -12278,7 +12254,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12293,30 +12269,30 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>492</v>
+        <v>484</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>494</v>
+        <v>486</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12339,16 +12315,16 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12398,7 +12374,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12413,30 +12389,30 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>495</v>
+        <v>487</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>497</v>
+        <v>489</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12459,17 +12435,17 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>77</v>
@@ -12482,7 +12458,7 @@
         <v>77</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>77</v>
@@ -12518,7 +12494,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12533,13 +12509,13 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>77</v>
@@ -12553,13 +12529,13 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>498</v>
+        <v>490</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>499</v>
+        <v>491</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>77</v>
@@ -12581,19 +12557,19 @@
         <v>77</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>341</v>
+        <v>333</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>343</v>
+        <v>335</v>
       </c>
       <c r="O86" t="s" s="2">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>77</v>
@@ -12642,7 +12618,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>339</v>
+        <v>331</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12651,19 +12627,19 @@
         <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>349</v>
+        <v>341</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>77</v>
@@ -12677,10 +12653,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>500</v>
+        <v>492</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12703,13 +12679,13 @@
         <v>77</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12760,7 +12736,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12778,7 +12754,7 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -12795,10 +12771,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>501</v>
+        <v>493</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12827,7 +12803,7 @@
         <v>134</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N88" t="s" s="2">
         <v>136</v>
@@ -12868,10 +12844,10 @@
         <v>77</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>77</v>
@@ -12880,7 +12856,7 @@
         <v>151</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12898,7 +12874,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -12915,10 +12891,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>502</v>
+        <v>494</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>353</v>
+        <v>345</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12944,16 +12920,16 @@
         <v>107</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="O89" t="s" s="2">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12966,7 +12942,7 @@
         <v>77</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>77</v>
@@ -12978,13 +12954,13 @@
         <v>77</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>359</v>
+        <v>351</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>77</v>
@@ -13002,7 +12978,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -13017,13 +12993,13 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>77</v>
@@ -13037,10 +13013,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>503</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13066,13 +13042,13 @@
         <v>107</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -13086,7 +13062,7 @@
         <v>77</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>77</v>
@@ -13098,13 +13074,13 @@
         <v>77</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -13122,7 +13098,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13134,13 +13110,13 @@
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>504</v>
+        <v>496</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -13149,7 +13125,7 @@
         <v>77</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>505</v>
+        <v>497</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>77</v>
@@ -13157,10 +13133,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>506</v>
+        <v>498</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13183,19 +13159,19 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>77</v>
@@ -13208,7 +13184,7 @@
         <v>77</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>77</v>
@@ -13244,7 +13220,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13259,10 +13235,10 @@
         <v>99</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -13279,10 +13255,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>507</v>
+        <v>499</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13293,7 +13269,7 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="H92" t="s" s="2">
         <v>88</v>
@@ -13305,13 +13281,13 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13326,7 +13302,7 @@
         <v>77</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>77</v>
@@ -13362,7 +13338,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13377,19 +13353,19 @@
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>77</v>
@@ -13397,14 +13373,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>509</v>
+        <v>501</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13423,13 +13399,13 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -13444,7 +13420,7 @@
         <v>77</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>395</v>
+        <v>387</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>77</v>
@@ -13480,7 +13456,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13495,19 +13471,19 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>510</v>
+        <v>502</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>77</v>
@@ -13515,14 +13491,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>511</v>
+        <v>503</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13541,16 +13517,16 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13564,7 +13540,7 @@
         <v>77</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>77</v>
@@ -13600,7 +13576,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13615,10 +13591,10 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
@@ -13635,14 +13611,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>512</v>
+        <v>504</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>409</v>
+        <v>401</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13661,13 +13637,13 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>411</v>
+        <v>403</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13694,13 +13670,13 @@
         <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>413</v>
+        <v>405</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -13718,7 +13694,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>415</v>
+        <v>407</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13733,19 +13709,19 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>417</v>
+        <v>409</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>513</v>
+        <v>505</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>77</v>
@@ -13753,14 +13729,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>514</v>
+        <v>506</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>419</v>
+        <v>411</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13779,13 +13755,13 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>421</v>
+        <v>413</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13800,7 +13776,7 @@
         <v>77</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>423</v>
+        <v>415</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>77</v>
@@ -13836,7 +13812,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>424</v>
+        <v>416</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13851,19 +13827,19 @@
         <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>427</v>
+        <v>419</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>515</v>
+        <v>507</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>77</v>
@@ -13871,10 +13847,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>516</v>
+        <v>508</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>428</v>
+        <v>420</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13897,16 +13873,16 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>429</v>
+        <v>421</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>431</v>
+        <v>423</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13956,7 +13932,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>432</v>
+        <v>424</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13971,30 +13947,30 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>433</v>
+        <v>425</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>434</v>
+        <v>426</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>435</v>
+        <v>427</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>517</v>
+        <v>509</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>518</v>
+        <v>510</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>436</v>
+        <v>428</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14017,17 +13993,17 @@
         <v>88</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>437</v>
+        <v>429</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>439</v>
+        <v>431</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -14040,7 +14016,7 @@
         <v>77</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>440</v>
+        <v>432</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>77</v>
@@ -14076,7 +14052,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>441</v>
+        <v>433</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -14091,13 +14067,13 @@
         <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>442</v>
+        <v>434</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>77</v>
@@ -14111,10 +14087,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14137,17 +14113,17 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>520</v>
+        <v>512</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>521</v>
+        <v>513</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" t="s" s="2">
-        <v>522</v>
+        <v>514</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>77</v>
@@ -14196,7 +14172,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>519</v>
+        <v>511</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -14211,13 +14187,13 @@
         <v>99</v>
       </c>
       <c r="AK99" t="s" s="2">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>523</v>
+        <v>515</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>77</v>
@@ -14231,10 +14207,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14257,19 +14233,19 @@
         <v>77</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>525</v>
+        <v>517</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>526</v>
+        <v>518</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>527</v>
+        <v>519</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>528</v>
+        <v>520</v>
       </c>
       <c r="O100" t="s" s="2">
-        <v>529</v>
+        <v>521</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -14318,7 +14294,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -14336,7 +14312,7 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>530</v>
+        <v>522</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
@@ -14353,10 +14329,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>531</v>
+        <v>523</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14379,13 +14355,13 @@
         <v>77</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14436,7 +14412,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -14454,7 +14430,7 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
@@ -14471,10 +14447,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>532</v>
+        <v>524</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14503,7 +14479,7 @@
         <v>134</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N102" t="s" s="2">
         <v>136</v>
@@ -14556,7 +14532,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -14574,7 +14550,7 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
@@ -14591,14 +14567,14 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>533</v>
+        <v>525</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="E103" s="2"/>
       <c r="F103" t="s" s="2">
@@ -14620,10 +14596,10 @@
         <v>133</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="N103" t="s" s="2">
         <v>136</v>
@@ -14678,7 +14654,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>537</v>
+        <v>529</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -14713,10 +14689,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14739,17 +14715,17 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>539</v>
+        <v>531</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>540</v>
+        <v>532</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>541</v>
+        <v>533</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>77</v>
@@ -14774,13 +14750,13 @@
         <v>77</v>
       </c>
       <c r="X104" t="s" s="2">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="Y104" t="s" s="2">
-        <v>542</v>
+        <v>534</v>
       </c>
       <c r="Z104" t="s" s="2">
-        <v>543</v>
+        <v>535</v>
       </c>
       <c r="AA104" t="s" s="2">
         <v>77</v>
@@ -14798,7 +14774,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>538</v>
+        <v>530</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -14816,7 +14792,7 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -14833,10 +14809,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14859,17 +14835,17 @@
         <v>77</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>547</v>
+        <v>539</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>548</v>
+        <v>540</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" t="s" s="2">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>77</v>
@@ -14918,7 +14894,7 @@
         <v>77</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>545</v>
+        <v>537</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -14933,10 +14909,10 @@
         <v>99</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>550</v>
+        <v>542</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -14953,10 +14929,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>552</v>
+        <v>544</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14979,13 +14955,13 @@
         <v>77</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15036,7 +15012,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -15054,7 +15030,7 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
@@ -15071,10 +15047,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>553</v>
+        <v>545</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15103,7 +15079,7 @@
         <v>134</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>136</v>
@@ -15144,10 +15120,10 @@
         <v>77</v>
       </c>
       <c r="AB107" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>77</v>
@@ -15156,7 +15132,7 @@
         <v>151</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -15174,7 +15150,7 @@
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
@@ -15191,10 +15167,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15220,16 +15196,16 @@
         <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -15254,13 +15230,13 @@
         <v>77</v>
       </c>
       <c r="X108" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>559</v>
+        <v>551</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>77</v>
@@ -15278,7 +15254,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>561</v>
+        <v>553</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -15293,13 +15269,13 @@
         <v>99</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>563</v>
+        <v>555</v>
       </c>
       <c r="AN108" t="s" s="2">
         <v>77</v>
@@ -15313,10 +15289,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>564</v>
+        <v>556</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15339,19 +15315,19 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>566</v>
+        <v>558</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -15400,7 +15376,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>568</v>
+        <v>560</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -15415,10 +15391,10 @@
         <v>99</v>
       </c>
       <c r="AK109" t="s" s="2">
-        <v>569</v>
+        <v>561</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
@@ -15427,7 +15403,7 @@
         <v>77</v>
       </c>
       <c r="AO109" t="s" s="2">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="AP109" t="s" s="2">
         <v>77</v>
@@ -15435,14 +15411,14 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>571</v>
+        <v>563</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -15461,16 +15437,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>574</v>
+        <v>566</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>575</v>
+        <v>567</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -15520,7 +15496,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>576</v>
+        <v>568</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -15535,13 +15511,13 @@
         <v>99</v>
       </c>
       <c r="AK110" t="s" s="2">
-        <v>577</v>
+        <v>569</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>578</v>
+        <v>570</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>579</v>
+        <v>571</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>77</v>
@@ -15555,14 +15531,14 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>580</v>
+        <v>572</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
-        <v>581</v>
+        <v>573</v>
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
@@ -15581,16 +15557,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>582</v>
+        <v>574</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>583</v>
+        <v>575</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>584</v>
+        <v>576</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -15640,7 +15616,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>585</v>
+        <v>577</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -15655,13 +15631,13 @@
         <v>99</v>
       </c>
       <c r="AK111" t="s" s="2">
-        <v>586</v>
+        <v>578</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>587</v>
+        <v>579</v>
       </c>
       <c r="AM111" t="s" s="2">
-        <v>588</v>
+        <v>580</v>
       </c>
       <c r="AN111" t="s" s="2">
         <v>77</v>
@@ -15675,10 +15651,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15701,13 +15677,13 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>590</v>
+        <v>582</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>591</v>
+        <v>583</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -15758,7 +15734,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>592</v>
+        <v>584</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -15773,13 +15749,13 @@
         <v>99</v>
       </c>
       <c r="AK112" t="s" s="2">
-        <v>593</v>
+        <v>585</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>594</v>
+        <v>586</v>
       </c>
       <c r="AM112" t="s" s="2">
-        <v>595</v>
+        <v>587</v>
       </c>
       <c r="AN112" t="s" s="2">
         <v>77</v>
@@ -15793,10 +15769,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15819,13 +15795,13 @@
         <v>88</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>597</v>
+        <v>589</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>598</v>
+        <v>590</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -15876,7 +15852,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>599</v>
+        <v>591</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -15891,10 +15867,10 @@
         <v>99</v>
       </c>
       <c r="AK113" t="s" s="2">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -15911,10 +15887,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>602</v>
+        <v>594</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15937,17 +15913,17 @@
         <v>88</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>603</v>
+        <v>595</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>605</v>
+        <v>597</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>77</v>
@@ -15996,7 +15972,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>606</v>
+        <v>598</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -16011,13 +15987,13 @@
         <v>99</v>
       </c>
       <c r="AK114" t="s" s="2">
-        <v>607</v>
+        <v>599</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AM114" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AN114" t="s" s="2">
         <v>77</v>
@@ -16031,10 +16007,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16057,17 +16033,17 @@
         <v>77</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>77</v>
@@ -16116,7 +16092,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -16131,10 +16107,10 @@
         <v>99</v>
       </c>
       <c r="AK115" t="s" s="2">
-        <v>612</v>
+        <v>604</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>613</v>
+        <v>605</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -16151,10 +16127,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>614</v>
+        <v>606</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16177,13 +16153,13 @@
         <v>77</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -16234,7 +16210,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -16252,7 +16228,7 @@
         <v>77</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>77</v>
@@ -16269,10 +16245,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>615</v>
+        <v>607</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16301,7 +16277,7 @@
         <v>134</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>170</v>
+        <v>164</v>
       </c>
       <c r="N117" t="s" s="2">
         <v>136</v>
@@ -16342,10 +16318,10 @@
         <v>77</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>171</v>
+        <v>165</v>
       </c>
       <c r="AC117" t="s" s="2">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="AD117" t="s" s="2">
         <v>77</v>
@@ -16354,7 +16330,7 @@
         <v>151</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>78</v>
@@ -16372,7 +16348,7 @@
         <v>77</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
@@ -16389,10 +16365,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>616</v>
+        <v>608</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16418,10 +16394,10 @@
         <v>107</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -16448,13 +16424,13 @@
         <v>77</v>
       </c>
       <c r="X118" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y118" t="s" s="2">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="Z118" t="s" s="2">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="AA118" t="s" s="2">
         <v>77</v>
@@ -16472,7 +16448,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>78</v>
@@ -16481,19 +16457,19 @@
         <v>87</v>
       </c>
       <c r="AI118" t="s" s="2">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="AM118" t="s" s="2">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="AN118" t="s" s="2">
         <v>77</v>
@@ -16507,10 +16483,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>617</v>
+        <v>609</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16533,19 +16509,19 @@
         <v>88</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -16594,7 +16570,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>78</v>
@@ -16609,19 +16585,19 @@
         <v>99</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="AM119" t="s" s="2">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="AN119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO119" t="s" s="2">
-        <v>618</v>
+        <v>610</v>
       </c>
       <c r="AP119" t="s" s="2">
         <v>77</v>
@@ -16629,10 +16605,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>619</v>
+        <v>611</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16658,16 +16634,16 @@
         <v>107</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="O120" t="s" s="2">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -16692,13 +16668,13 @@
         <v>77</v>
       </c>
       <c r="X120" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="Y120" t="s" s="2">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="Z120" t="s" s="2">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="AA120" t="s" s="2">
         <v>77</v>
@@ -16716,7 +16692,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -16731,13 +16707,13 @@
         <v>99</v>
       </c>
       <c r="AK120" t="s" s="2">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="AM120" t="s" s="2">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="AN120" t="s" s="2">
         <v>77</v>
@@ -16751,10 +16727,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>620</v>
+        <v>612</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16777,16 +16753,16 @@
         <v>88</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>331</v>
+        <v>323</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16836,7 +16812,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -16851,10 +16827,10 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
@@ -16871,10 +16847,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>621</v>
+        <v>613</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16897,13 +16873,13 @@
         <v>88</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -16954,7 +16930,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -16972,10 +16948,10 @@
         <v>130</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="AM122" t="s" s="2">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="AN122" t="s" s="2">
         <v>77</v>
@@ -16989,10 +16965,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17015,17 +16991,17 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>623</v>
+        <v>615</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>624</v>
+        <v>616</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>625</v>
+        <v>617</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -17074,7 +17050,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -17089,10 +17065,10 @@
         <v>99</v>
       </c>
       <c r="AK123" t="s" s="2">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
@@ -17109,10 +17085,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17135,17 +17111,17 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>629</v>
+        <v>621</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>630</v>
+        <v>622</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>631</v>
+        <v>623</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>632</v>
+        <v>624</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -17194,7 +17170,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -17212,7 +17188,7 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA INSTITUTION (file 4) to FHIR Organization</t>
+    <t>This StructureDefinition contains the maps for VistA file INSTITUTION (#4) to us-core-organization</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$124</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AP$98</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4753" uniqueCount="625">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="594">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.13.0</t>
+    <t>0.14.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-03T19:41:50+00:00</t>
+    <t>2024-01-13T13:47:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,10 +773,6 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-23:1253: fixed value = true {null}</t>
-  </si>
-  <si>
     <t>No equivalent in HL7 v2</t>
   </si>
   <si>
@@ -816,10 +812,6 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-24:1254: fixed value = prov {null}</t>
   </si>
   <si>
     <t>No equivalent in v2</t>
@@ -1375,87 +1367,6 @@
     <t>XAD.12 / XAD.13 + XAD.14</t>
   </si>
   <si>
-    <t>Organization.address:home</t>
-  </si>
-  <si>
-    <t>Organization.address:home.id</t>
-  </si>
-  <si>
-    <t>Organization.address:home.extension</t>
-  </si>
-  <si>
-    <t>Organization.address:home.use</t>
-  </si>
-  <si>
-    <t>Organization.address:home.type</t>
-  </si>
-  <si>
-    <t>Organization.address:home.text</t>
-  </si>
-  <si>
-    <t>Organization.address:home.line</t>
-  </si>
-  <si>
-    <t>Organization.address:home.city</t>
-  </si>
-  <si>
-    <t>Organization.address:home.district</t>
-  </si>
-  <si>
-    <t>Organization.address:home.state</t>
-  </si>
-  <si>
-    <t>Organization.address:home.postalCode</t>
-  </si>
-  <si>
-    <t>Organization.address:home.country</t>
-  </si>
-  <si>
-    <t>Organization.address:home.period</t>
-  </si>
-  <si>
-    <t>Organization.address:temp</t>
-  </si>
-  <si>
-    <t>temp</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.id</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.extension</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.use</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.type</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.text</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.line</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.city</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.district</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.state</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.postalCode</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.country</t>
-  </si>
-  <si>
-    <t>Organization.address:temp.period</t>
-  </si>
-  <si>
     <t>Organization.address:physical</t>
   </si>
   <si>
@@ -1472,10 +1383,6 @@
   </si>
   <si>
     <t>Organization.address:physical.type</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-25:1257: fixed value = #physical {null}</t>
   </si>
   <si>
     <t>1257: fixed value = #physical</t>
@@ -1558,10 +1465,6 @@
   </si>
   <si>
     <t>Organization.address:postal.type</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-26:1268: fixed value = #postal {null}</t>
   </si>
   <si>
     <t>1268: fixed value = #postal</t>
@@ -2269,7 +2172,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AP124"/>
+  <dimension ref="A1:AP98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="39.625" customWidth="true" bestFit="true"/>
@@ -4952,22 +4855,22 @@
         <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK22" t="s" s="2">
         <v>242</v>
       </c>
-      <c r="AK22" t="s" s="2">
+      <c r="AL22" t="s" s="2">
         <v>243</v>
       </c>
-      <c r="AL22" t="s" s="2">
+      <c r="AM22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AO22" t="s" s="2">
-        <v>247</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>77</v>
@@ -4975,10 +4878,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4992,7 +4895,7 @@
         <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
@@ -5004,16 +4907,16 @@
         <v>179</v>
       </c>
       <c r="L23" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="M23" t="s" s="2">
         <v>249</v>
       </c>
-      <c r="M23" t="s" s="2">
+      <c r="N23" t="s" s="2">
         <v>250</v>
       </c>
-      <c r="N23" t="s" s="2">
+      <c r="O23" t="s" s="2">
         <v>251</v>
-      </c>
-      <c r="O23" t="s" s="2">
-        <v>252</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -5038,14 +4941,14 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="Y23" t="s" s="2">
         <v>253</v>
       </c>
-      <c r="Y23" t="s" s="2">
+      <c r="Z23" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="Z23" t="s" s="2">
-        <v>255</v>
-      </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
       </c>
@@ -5062,7 +4965,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5074,22 +4977,22 @@
         <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK23" t="s" s="2">
+        <v>255</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AK23" t="s" s="2">
-        <v>257</v>
-      </c>
-      <c r="AL23" t="s" s="2">
-        <v>258</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>162</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>77</v>
@@ -5097,10 +5000,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5126,16 +5029,16 @@
         <v>158</v>
       </c>
       <c r="L24" t="s" s="2">
+        <v>260</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>261</v>
+      </c>
+      <c r="N24" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="M24" t="s" s="2">
+      <c r="O24" t="s" s="2">
         <v>263</v>
-      </c>
-      <c r="N24" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="O24" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5184,7 +5087,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5199,30 +5102,30 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AL24" t="s" s="2">
+        <v>265</v>
+      </c>
+      <c r="AM24" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="AL24" t="s" s="2">
+      <c r="AN24" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AO24" t="s" s="2">
         <v>267</v>
       </c>
-      <c r="AM24" t="s" s="2">
+      <c r="AP24" t="s" s="2">
         <v>268</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO24" t="s" s="2">
-        <v>269</v>
-      </c>
-      <c r="AP24" t="s" s="2">
-        <v>270</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5236,7 +5139,7 @@
         <v>79</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>77</v>
@@ -5248,16 +5151,16 @@
         <v>158</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>271</v>
+      </c>
+      <c r="N25" t="s" s="2">
         <v>272</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5306,7 +5209,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5324,7 +5227,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -5333,18 +5236,18 @@
         <v>77</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>277</v>
+        <v>275</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5367,19 +5270,19 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L26" t="s" s="2">
+        <v>278</v>
+      </c>
+      <c r="M26" t="s" s="2">
         <v>279</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="N26" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="M26" t="s" s="2">
+      <c r="O26" t="s" s="2">
         <v>281</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>282</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5428,7 +5331,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5437,19 +5340,19 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
+        <v>282</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="AK26" t="s" s="2">
         <v>284</v>
       </c>
-      <c r="AJ26" t="s" s="2">
+      <c r="AL26" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="AK26" t="s" s="2">
+      <c r="AM26" t="s" s="2">
         <v>286</v>
-      </c>
-      <c r="AL26" t="s" s="2">
-        <v>287</v>
-      </c>
-      <c r="AM26" t="s" s="2">
-        <v>288</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -5463,10 +5366,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5581,10 +5484,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5701,10 +5604,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5730,10 +5633,10 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5763,28 +5666,28 @@
         <v>173</v>
       </c>
       <c r="Y29" t="s" s="2">
+        <v>292</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>293</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF29" t="s" s="2">
         <v>294</v>
-      </c>
-      <c r="Z29" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AA29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF29" t="s" s="2">
-        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5793,19 +5696,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>296</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>297</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>298</v>
-      </c>
-      <c r="AL29" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AM29" t="s" s="2">
-        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5819,10 +5722,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5848,16 +5751,16 @@
         <v>158</v>
       </c>
       <c r="L30" t="s" s="2">
+        <v>300</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>301</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>302</v>
       </c>
-      <c r="M30" t="s" s="2">
+      <c r="O30" t="s" s="2">
         <v>303</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O30" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5906,7 +5809,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5921,10 +5824,10 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>207</v>
@@ -5941,10 +5844,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5970,16 +5873,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>308</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>309</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>310</v>
       </c>
-      <c r="M31" t="s" s="2">
+      <c r="O31" t="s" s="2">
         <v>311</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O31" t="s" s="2">
-        <v>313</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -6007,28 +5910,28 @@
         <v>173</v>
       </c>
       <c r="Y31" t="s" s="2">
+        <v>312</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>313</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF31" t="s" s="2">
         <v>314</v>
-      </c>
-      <c r="Z31" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AA31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF31" t="s" s="2">
-        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6043,13 +5946,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>315</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>316</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>317</v>
-      </c>
-      <c r="AL31" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AM31" t="s" s="2">
-        <v>319</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -6063,10 +5966,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6089,16 +5992,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>319</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>320</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>321</v>
       </c>
-      <c r="L32" t="s" s="2">
+      <c r="N32" t="s" s="2">
         <v>322</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N32" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6148,7 +6051,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6183,10 +6086,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6212,10 +6115,10 @@
         <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6266,7 +6169,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6284,7 +6187,7 @@
         <v>130</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>217</v>
@@ -6301,10 +6204,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6327,19 +6230,19 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M34" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L34" t="s" s="2">
+      <c r="N34" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M34" t="s" s="2">
+      <c r="O34" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N34" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O34" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6376,7 +6279,7 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -6386,7 +6289,7 @@
         <v>151</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6395,19 +6298,19 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AK34" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AJ34" t="s" s="2">
+      <c r="AL34" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AK34" t="s" s="2">
+      <c r="AM34" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AL34" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM34" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -6421,10 +6324,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6539,10 +6442,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6659,10 +6562,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6688,16 +6591,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N37" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M37" t="s" s="2">
+      <c r="O37" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O37" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6710,7 +6613,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6725,28 +6628,28 @@
         <v>173</v>
       </c>
       <c r="Y37" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF37" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="Z37" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF37" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6761,13 +6664,13 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6781,10 +6684,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6810,13 +6713,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N38" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M38" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N38" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6830,7 +6733,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6845,28 +6748,28 @@
         <v>173</v>
       </c>
       <c r="Y38" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF38" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="Z38" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AA38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF38" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6881,10 +6784,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6901,10 +6804,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6930,16 +6833,16 @@
         <v>158</v>
       </c>
       <c r="L39" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N39" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M39" t="s" s="2">
+      <c r="O39" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6952,7 +6855,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6988,7 +6891,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -7003,10 +6906,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -7023,10 +6926,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7037,7 +6940,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -7052,10 +6955,10 @@
         <v>158</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7070,7 +6973,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -7106,7 +7009,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7121,13 +7024,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>380</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>382</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -7141,14 +7044,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7170,10 +7073,10 @@
         <v>158</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7188,7 +7091,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -7224,7 +7127,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7239,13 +7142,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>389</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -7259,14 +7162,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7288,13 +7191,13 @@
         <v>158</v>
       </c>
       <c r="L42" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M42" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N42" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7308,7 +7211,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -7344,7 +7247,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7359,10 +7262,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7379,14 +7282,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7408,10 +7311,10 @@
         <v>158</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7441,28 +7344,28 @@
         <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z43" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF43" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7477,13 +7380,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>408</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -7497,14 +7400,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7526,10 +7429,10 @@
         <v>158</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7544,7 +7447,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7580,7 +7483,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7595,13 +7498,13 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>417</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>419</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7615,10 +7518,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7644,13 +7547,13 @@
         <v>158</v>
       </c>
       <c r="L45" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M45" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N45" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N45" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7700,7 +7603,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7715,13 +7618,13 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>425</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>427</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7735,10 +7638,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7764,14 +7667,14 @@
         <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7784,7 +7687,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7820,7 +7723,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7835,10 +7738,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>217</v>
@@ -7855,13 +7758,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>350</v>
+        <v>434</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7883,19 +7786,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L47" t="s" s="2">
+      <c r="N47" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M47" t="s" s="2">
+      <c r="O47" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7944,7 +7847,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7953,19 +7856,19 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AJ47" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AK47" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AJ47" t="s" s="2">
+      <c r="AL47" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AK47" t="s" s="2">
+      <c r="AM47" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7979,10 +7882,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8097,10 +8000,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8217,10 +8120,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8246,16 +8149,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N50" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M50" t="s" s="2">
+      <c r="O50" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8268,7 +8171,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -8283,28 +8186,28 @@
         <v>173</v>
       </c>
       <c r="Y50" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF50" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="Z50" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF50" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8319,13 +8222,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8339,10 +8242,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8356,7 +8259,7 @@
         <v>87</v>
       </c>
       <c r="H51" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I51" t="s" s="2">
         <v>77</v>
@@ -8368,13 +8271,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M51" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N51" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M51" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8388,7 +8291,7 @@
         <v>77</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -8403,28 +8306,28 @@
         <v>173</v>
       </c>
       <c r="Y51" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z51" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF51" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="Z51" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AA51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF51" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8439,10 +8342,10 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8451,7 +8354,7 @@
         <v>77</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>77</v>
+        <v>439</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>77</v>
@@ -8462,7 +8365,7 @@
         <v>440</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8488,16 +8391,16 @@
         <v>158</v>
       </c>
       <c r="L52" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M52" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N52" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M52" t="s" s="2">
+      <c r="O52" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N52" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8510,7 +8413,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -8546,7 +8449,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8561,10 +8464,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8584,7 +8487,7 @@
         <v>441</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8595,7 +8498,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>88</v>
@@ -8610,10 +8513,10 @@
         <v>158</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8628,7 +8531,7 @@
         <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>77</v>
@@ -8664,7 +8567,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8679,34 +8582,34 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL53" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AM53" t="s" s="2">
-        <v>382</v>
-      </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>77</v>
+        <v>442</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>77</v>
+        <v>443</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8728,10 +8631,10 @@
         <v>158</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8746,7 +8649,7 @@
         <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8782,7 +8685,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8797,34 +8700,34 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL54" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM54" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>77</v>
+        <v>445</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>77</v>
+        <v>446</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8834,7 +8737,7 @@
         <v>87</v>
       </c>
       <c r="H55" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I55" t="s" s="2">
         <v>77</v>
@@ -8846,13 +8749,13 @@
         <v>158</v>
       </c>
       <c r="L55" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M55" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N55" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M55" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N55" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8866,7 +8769,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8902,7 +8805,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8917,10 +8820,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8929,22 +8832,22 @@
         <v>77</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>77</v>
+        <v>448</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>77</v>
+        <v>449</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8966,10 +8869,10 @@
         <v>158</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8999,28 +8902,28 @@
         <v>184</v>
       </c>
       <c r="Y56" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z56" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="Z56" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -9035,34 +8938,34 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL56" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM56" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>77</v>
+        <v>451</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>77</v>
+        <v>452</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9084,10 +8987,10 @@
         <v>158</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9102,7 +9005,7 @@
         <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>77</v>
@@ -9138,7 +9041,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9153,30 +9056,30 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL57" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>77</v>
+        <v>454</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>77</v>
+        <v>455</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>446</v>
+        <v>456</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9202,13 +9105,13 @@
         <v>158</v>
       </c>
       <c r="L58" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M58" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N58" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M58" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N58" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9258,7 +9161,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9273,30 +9176,30 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL58" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AM58" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>77</v>
+        <v>457</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>77</v>
+        <v>458</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9322,14 +9225,14 @@
         <v>211</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9342,7 +9245,7 @@
         <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>77</v>
@@ -9378,7 +9281,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9393,10 +9296,10 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>217</v>
@@ -9413,13 +9316,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9441,19 +9344,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="L60" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="M60" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="L60" t="s" s="2">
+      <c r="N60" t="s" s="2">
         <v>333</v>
       </c>
-      <c r="M60" t="s" s="2">
+      <c r="O60" t="s" s="2">
         <v>334</v>
-      </c>
-      <c r="N60" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O60" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9502,7 +9405,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9511,19 +9414,19 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="AJ60" t="s" s="2">
+        <v>337</v>
+      </c>
+      <c r="AK60" t="s" s="2">
         <v>338</v>
       </c>
-      <c r="AJ60" t="s" s="2">
+      <c r="AL60" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AK60" t="s" s="2">
+      <c r="AM60" t="s" s="2">
         <v>340</v>
-      </c>
-      <c r="AL60" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="AM60" t="s" s="2">
-        <v>342</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -9537,10 +9440,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9655,10 +9558,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9775,10 +9678,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9804,16 +9707,16 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
+        <v>344</v>
+      </c>
+      <c r="M63" t="s" s="2">
+        <v>345</v>
+      </c>
+      <c r="N63" t="s" s="2">
         <v>346</v>
       </c>
-      <c r="M63" t="s" s="2">
+      <c r="O63" t="s" s="2">
         <v>347</v>
-      </c>
-      <c r="N63" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O63" t="s" s="2">
-        <v>349</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9826,7 +9729,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9841,28 +9744,28 @@
         <v>173</v>
       </c>
       <c r="Y63" t="s" s="2">
+        <v>349</v>
+      </c>
+      <c r="Z63" t="s" s="2">
+        <v>350</v>
+      </c>
+      <c r="AA63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF63" t="s" s="2">
         <v>351</v>
-      </c>
-      <c r="Z63" t="s" s="2">
-        <v>352</v>
-      </c>
-      <c r="AA63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF63" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9877,13 +9780,13 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9897,10 +9800,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9914,7 +9817,7 @@
         <v>87</v>
       </c>
       <c r="H64" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I64" t="s" s="2">
         <v>77</v>
@@ -9926,13 +9829,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="M64" t="s" s="2">
+        <v>356</v>
+      </c>
+      <c r="N64" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="M64" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N64" t="s" s="2">
-        <v>359</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9946,7 +9849,7 @@
         <v>77</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9961,28 +9864,28 @@
         <v>173</v>
       </c>
       <c r="Y64" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="Z64" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="AA64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF64" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="Z64" t="s" s="2">
-        <v>362</v>
-      </c>
-      <c r="AA64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF64" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9997,10 +9900,10 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -10009,7 +9912,7 @@
         <v>77</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>77</v>
+        <v>466</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>77</v>
@@ -10017,10 +9920,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10046,16 +9949,16 @@
         <v>158</v>
       </c>
       <c r="L65" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N65" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="M65" t="s" s="2">
+      <c r="O65" t="s" s="2">
         <v>367</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>369</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -10068,7 +9971,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -10104,7 +10007,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10119,10 +10022,10 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -10139,10 +10042,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10153,7 +10056,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>88</v>
@@ -10168,10 +10071,10 @@
         <v>158</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10186,7 +10089,7 @@
         <v>77</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>77</v>
@@ -10222,7 +10125,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10237,19 +10140,19 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL66" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="AM66" t="s" s="2">
-        <v>382</v>
-      </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>77</v>
+        <v>469</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>77</v>
@@ -10257,14 +10160,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>456</v>
+        <v>470</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10286,10 +10189,10 @@
         <v>158</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10304,7 +10207,7 @@
         <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>77</v>
@@ -10340,7 +10243,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10355,19 +10258,19 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL67" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="AM67" t="s" s="2">
-        <v>391</v>
-      </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>77</v>
+        <v>471</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>77</v>
@@ -10375,14 +10278,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>457</v>
+        <v>472</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10404,13 +10307,13 @@
         <v>158</v>
       </c>
       <c r="L68" t="s" s="2">
+        <v>392</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>393</v>
+      </c>
+      <c r="N68" t="s" s="2">
         <v>394</v>
-      </c>
-      <c r="M68" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="N68" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10424,7 +10327,7 @@
         <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>77</v>
@@ -10460,7 +10363,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10475,10 +10378,10 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -10495,14 +10398,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>458</v>
+        <v>473</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10524,10 +10427,10 @@
         <v>158</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10557,28 +10460,28 @@
         <v>184</v>
       </c>
       <c r="Y69" t="s" s="2">
+        <v>403</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>405</v>
-      </c>
-      <c r="Z69" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>407</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10593,19 +10496,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>406</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>407</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL69" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="AM69" t="s" s="2">
-        <v>410</v>
-      </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>77</v>
+        <v>474</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10613,14 +10516,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10642,10 +10545,10 @@
         <v>158</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10660,7 +10563,7 @@
         <v>77</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>77</v>
@@ -10696,7 +10599,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10711,19 +10614,19 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>415</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>416</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL70" t="s" s="2">
-        <v>418</v>
-      </c>
-      <c r="AM70" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>77</v>
+        <v>476</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>77</v>
@@ -10731,10 +10634,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>460</v>
+        <v>477</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10760,13 +10663,13 @@
         <v>158</v>
       </c>
       <c r="L71" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="N71" t="s" s="2">
         <v>421</v>
-      </c>
-      <c r="M71" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N71" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10816,7 +10719,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10831,30 +10734,30 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>423</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>424</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL71" t="s" s="2">
-        <v>426</v>
-      </c>
-      <c r="AM71" t="s" s="2">
-        <v>427</v>
-      </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>77</v>
+        <v>478</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>77</v>
+        <v>458</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>461</v>
+        <v>479</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10880,14 +10783,14 @@
         <v>211</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10900,7 +10803,7 @@
         <v>77</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>77</v>
@@ -10936,7 +10839,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10951,10 +10854,10 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>217</v>
@@ -10971,14 +10874,12 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>462</v>
+        <v>480</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="C73" t="s" s="2">
-        <v>463</v>
-      </c>
+        <v>480</v>
+      </c>
+      <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>77</v>
       </c>
@@ -10990,28 +10891,26 @@
         <v>87</v>
       </c>
       <c r="H73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J73" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K73" t="s" s="2">
-        <v>332</v>
+        <v>219</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>333</v>
+        <v>481</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N73" t="s" s="2">
-        <v>335</v>
-      </c>
+        <v>482</v>
+      </c>
+      <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>336</v>
+        <v>483</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -11060,28 +10959,28 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>331</v>
+        <v>480</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH73" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="AJ73" t="s" s="2">
-        <v>339</v>
+        <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>340</v>
+        <v>242</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>341</v>
+        <v>484</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>342</v>
+        <v>162</v>
       </c>
       <c r="AN73" t="s" s="2">
         <v>77</v>
@@ -11095,10 +10994,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>464</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>343</v>
+        <v>485</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11109,7 +11008,7 @@
         <v>78</v>
       </c>
       <c r="G74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H74" t="s" s="2">
         <v>77</v>
@@ -11121,16 +11020,20 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>158</v>
+        <v>486</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>159</v>
+        <v>487</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>490</v>
+      </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
       </c>
@@ -11178,25 +11081,25 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>161</v>
+        <v>485</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH74" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ74" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK74" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>162</v>
+        <v>491</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -11213,21 +11116,21 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>465</v>
+        <v>492</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>344</v>
+        <v>492</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G75" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H75" t="s" s="2">
         <v>77</v>
@@ -11239,17 +11142,15 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>133</v>
+        <v>158</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N75" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N75" s="2"/>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
         <v>77</v>
@@ -11286,31 +11187,31 @@
         <v>77</v>
       </c>
       <c r="AB75" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH75" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ75" t="s" s="2">
-        <v>138</v>
+        <v>77</v>
       </c>
       <c r="AK75" t="s" s="2">
         <v>77</v>
@@ -11333,46 +11234,44 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>466</v>
+        <v>493</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>345</v>
+        <v>493</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I76" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J76" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>346</v>
+        <v>134</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>347</v>
+        <v>164</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="O76" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
         <v>77</v>
       </c>
@@ -11384,7 +11283,7 @@
         <v>77</v>
       </c>
       <c r="T76" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="U76" t="s" s="2">
         <v>77</v>
@@ -11396,13 +11295,13 @@
         <v>77</v>
       </c>
       <c r="X76" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y76" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="Z76" t="s" s="2">
-        <v>352</v>
+        <v>77</v>
       </c>
       <c r="AA76" t="s" s="2">
         <v>77</v>
@@ -11420,28 +11319,28 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH76" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ76" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK76" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>318</v>
+        <v>162</v>
       </c>
       <c r="AM76" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
         <v>77</v>
@@ -11455,44 +11354,46 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>467</v>
+        <v>494</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>356</v>
+        <v>494</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>77</v>
+        <v>495</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I77" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J77" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>357</v>
+        <v>496</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>358</v>
+        <v>497</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O77" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O77" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P77" t="s" s="2">
         <v>77</v>
       </c>
@@ -11504,7 +11405,7 @@
         <v>77</v>
       </c>
       <c r="T77" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="U77" t="s" s="2">
         <v>77</v>
@@ -11516,13 +11417,13 @@
         <v>77</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>77</v>
@@ -11540,25 +11441,25 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>363</v>
+        <v>498</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH77" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ77" t="s" s="2">
-        <v>468</v>
+        <v>138</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>318</v>
+        <v>130</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
@@ -11567,7 +11468,7 @@
         <v>77</v>
       </c>
       <c r="AO77" t="s" s="2">
-        <v>469</v>
+        <v>77</v>
       </c>
       <c r="AP77" t="s" s="2">
         <v>77</v>
@@ -11575,10 +11476,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>470</v>
+        <v>499</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>365</v>
+        <v>499</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11598,22 +11499,20 @@
         <v>77</v>
       </c>
       <c r="J78" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>158</v>
+        <v>179</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>366</v>
+        <v>500</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="N78" t="s" s="2">
-        <v>368</v>
-      </c>
+        <v>501</v>
+      </c>
+      <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>369</v>
+        <v>502</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11626,7 +11525,7 @@
         <v>77</v>
       </c>
       <c r="T78" t="s" s="2">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="U78" t="s" s="2">
         <v>77</v>
@@ -11638,13 +11537,13 @@
         <v>77</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>77</v>
+        <v>184</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>77</v>
+        <v>503</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>77</v>
+        <v>504</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11662,7 +11561,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>371</v>
+        <v>499</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11677,10 +11576,10 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>373</v>
+        <v>505</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11697,10 +11596,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>471</v>
+        <v>506</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>374</v>
+        <v>506</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11711,28 +11610,30 @@
         <v>78</v>
       </c>
       <c r="G79" t="s" s="2">
-        <v>375</v>
+        <v>87</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J79" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>158</v>
+        <v>507</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>376</v>
+        <v>508</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>377</v>
+        <v>509</v>
       </c>
       <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
+      <c r="O79" t="s" s="2">
+        <v>510</v>
+      </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
       </c>
@@ -11744,7 +11645,7 @@
         <v>77</v>
       </c>
       <c r="T79" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="U79" t="s" s="2">
         <v>77</v>
@@ -11780,13 +11681,13 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>379</v>
+        <v>506</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH79" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
         <v>77</v>
@@ -11795,34 +11696,34 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>380</v>
+        <v>511</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>381</v>
+        <v>512</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>382</v>
+        <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO79" t="s" s="2">
-        <v>472</v>
+        <v>77</v>
       </c>
       <c r="AP79" t="s" s="2">
-        <v>473</v>
+        <v>77</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>474</v>
+        <v>513</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>383</v>
+        <v>513</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11832,22 +11733,22 @@
         <v>87</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J80" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>385</v>
+        <v>159</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>386</v>
+        <v>160</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11862,7 +11763,7 @@
         <v>77</v>
       </c>
       <c r="T80" t="s" s="2">
-        <v>387</v>
+        <v>77</v>
       </c>
       <c r="U80" t="s" s="2">
         <v>77</v>
@@ -11898,7 +11799,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>388</v>
+        <v>161</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11910,44 +11811,44 @@
         <v>77</v>
       </c>
       <c r="AJ80" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK80" t="s" s="2">
-        <v>389</v>
+        <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>390</v>
+        <v>162</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>391</v>
+        <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO80" t="s" s="2">
-        <v>475</v>
+        <v>77</v>
       </c>
       <c r="AP80" t="s" s="2">
-        <v>476</v>
+        <v>77</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>477</v>
+        <v>514</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>392</v>
+        <v>514</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>393</v>
+        <v>132</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H81" t="s" s="2">
         <v>77</v>
@@ -11956,19 +11857,19 @@
         <v>77</v>
       </c>
       <c r="J81" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>394</v>
+        <v>134</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>395</v>
+        <v>164</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>396</v>
+        <v>136</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11982,7 +11883,7 @@
         <v>77</v>
       </c>
       <c r="T81" t="s" s="2">
-        <v>397</v>
+        <v>77</v>
       </c>
       <c r="U81" t="s" s="2">
         <v>77</v>
@@ -12006,37 +11907,37 @@
         <v>77</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE81" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>398</v>
+        <v>167</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH81" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK81" t="s" s="2">
-        <v>399</v>
+        <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>400</v>
+        <v>162</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
@@ -12045,22 +11946,22 @@
         <v>77</v>
       </c>
       <c r="AO81" t="s" s="2">
-        <v>478</v>
+        <v>77</v>
       </c>
       <c r="AP81" t="s" s="2">
-        <v>479</v>
+        <v>77</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>480</v>
+        <v>515</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>401</v>
+        <v>515</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="E82" s="2"/>
       <c r="F82" t="s" s="2">
@@ -12070,25 +11971,29 @@
         <v>87</v>
       </c>
       <c r="H82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I82" t="s" s="2">
         <v>88</v>
-      </c>
-      <c r="I82" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="J82" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>403</v>
+        <v>516</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
+        <v>517</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="O82" t="s" s="2">
+        <v>519</v>
+      </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
       </c>
@@ -12112,13 +12017,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>405</v>
+        <v>520</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>406</v>
+        <v>521</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12136,7 +12041,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>407</v>
+        <v>522</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12151,34 +12056,34 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>408</v>
+        <v>523</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>409</v>
+        <v>316</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>410</v>
+        <v>524</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="AP82" t="s" s="2">
-        <v>482</v>
+        <v>77</v>
       </c>
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>483</v>
+        <v>525</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>411</v>
+        <v>525</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
-        <v>412</v>
+        <v>77</v>
       </c>
       <c r="E83" s="2"/>
       <c r="F83" t="s" s="2">
@@ -12200,13 +12105,17 @@
         <v>158</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>413</v>
+        <v>526</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
+        <v>527</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>528</v>
+      </c>
+      <c r="O83" t="s" s="2">
+        <v>367</v>
+      </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
       </c>
@@ -12218,7 +12127,7 @@
         <v>77</v>
       </c>
       <c r="T83" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="U83" t="s" s="2">
         <v>77</v>
@@ -12254,7 +12163,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>416</v>
+        <v>529</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12269,34 +12178,34 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>417</v>
+        <v>530</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>418</v>
+        <v>371</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>419</v>
+        <v>77</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>484</v>
+        <v>531</v>
       </c>
       <c r="AP83" t="s" s="2">
-        <v>485</v>
+        <v>77</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>486</v>
+        <v>532</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>420</v>
+        <v>532</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>77</v>
+        <v>533</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12306,7 +12215,7 @@
         <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>77</v>
@@ -12318,13 +12227,13 @@
         <v>158</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>421</v>
+        <v>534</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>422</v>
+        <v>535</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>423</v>
+        <v>536</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12374,7 +12283,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>424</v>
+        <v>537</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12389,41 +12298,41 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>425</v>
+        <v>538</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>426</v>
+        <v>539</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>427</v>
+        <v>540</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>487</v>
+        <v>77</v>
       </c>
       <c r="AP84" t="s" s="2">
-        <v>488</v>
+        <v>77</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>489</v>
+        <v>541</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>428</v>
+        <v>541</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>77</v>
+        <v>542</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H85" t="s" s="2">
         <v>77</v>
@@ -12435,18 +12344,18 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>211</v>
+        <v>158</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>429</v>
+        <v>543</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="N85" s="2"/>
-      <c r="O85" t="s" s="2">
-        <v>431</v>
-      </c>
+        <v>544</v>
+      </c>
+      <c r="N85" t="s" s="2">
+        <v>545</v>
+      </c>
+      <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
         <v>77</v>
       </c>
@@ -12458,7 +12367,7 @@
         <v>77</v>
       </c>
       <c r="T85" t="s" s="2">
-        <v>432</v>
+        <v>77</v>
       </c>
       <c r="U85" t="s" s="2">
         <v>77</v>
@@ -12494,13 +12403,13 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>433</v>
+        <v>546</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH85" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI85" t="s" s="2">
         <v>77</v>
@@ -12509,13 +12418,13 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>434</v>
+        <v>547</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>330</v>
+        <v>548</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>217</v>
+        <v>549</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>77</v>
@@ -12529,14 +12438,12 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>490</v>
+        <v>550</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>331</v>
-      </c>
-      <c r="C86" t="s" s="2">
-        <v>491</v>
-      </c>
+        <v>550</v>
+      </c>
+      <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>77</v>
       </c>
@@ -12545,32 +12452,28 @@
         <v>78</v>
       </c>
       <c r="G86" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J86" t="s" s="2">
         <v>88</v>
       </c>
-      <c r="I86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="K86" t="s" s="2">
-        <v>332</v>
+        <v>158</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>333</v>
+        <v>551</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>334</v>
-      </c>
-      <c r="N86" t="s" s="2">
-        <v>335</v>
-      </c>
-      <c r="O86" t="s" s="2">
-        <v>336</v>
-      </c>
+        <v>552</v>
+      </c>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
         <v>77</v>
       </c>
@@ -12618,7 +12521,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>331</v>
+        <v>553</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12627,19 +12530,19 @@
         <v>79</v>
       </c>
       <c r="AI86" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>339</v>
+        <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>340</v>
+        <v>554</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>341</v>
+        <v>555</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>342</v>
+        <v>556</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>77</v>
@@ -12653,10 +12556,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>492</v>
+        <v>557</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>343</v>
+        <v>557</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12667,7 +12570,7 @@
         <v>78</v>
       </c>
       <c r="G87" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H87" t="s" s="2">
         <v>77</v>
@@ -12676,16 +12579,16 @@
         <v>77</v>
       </c>
       <c r="J87" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
         <v>158</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>159</v>
+        <v>558</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>160</v>
+        <v>559</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12736,25 +12639,25 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>161</v>
+        <v>560</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH87" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ87" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>77</v>
+        <v>561</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>162</v>
+        <v>562</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -12771,21 +12674,21 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>493</v>
+        <v>563</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>344</v>
+        <v>563</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E88" s="2"/>
       <c r="F88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G88" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s" s="2">
         <v>77</v>
@@ -12794,21 +12697,21 @@
         <v>77</v>
       </c>
       <c r="J88" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>133</v>
+        <v>211</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>134</v>
+        <v>564</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N88" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O88" s="2"/>
+        <v>565</v>
+      </c>
+      <c r="N88" s="2"/>
+      <c r="O88" t="s" s="2">
+        <v>566</v>
+      </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
       </c>
@@ -12844,40 +12747,40 @@
         <v>77</v>
       </c>
       <c r="AB88" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC88" t="s" s="2">
-        <v>166</v>
+        <v>77</v>
       </c>
       <c r="AD88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE88" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>167</v>
+        <v>567</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH88" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI88" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ88" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>77</v>
+        <v>568</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>162</v>
+        <v>328</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>77</v>
+        <v>217</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>77</v>
@@ -12891,10 +12794,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>494</v>
+        <v>569</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>345</v>
+        <v>569</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12905,31 +12808,29 @@
         <v>78</v>
       </c>
       <c r="G89" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I89" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J89" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>107</v>
+        <v>277</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>346</v>
+        <v>570</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>347</v>
-      </c>
-      <c r="N89" t="s" s="2">
-        <v>348</v>
-      </c>
+        <v>571</v>
+      </c>
+      <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>349</v>
+        <v>572</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12942,7 +12843,7 @@
         <v>77</v>
       </c>
       <c r="T89" t="s" s="2">
-        <v>350</v>
+        <v>77</v>
       </c>
       <c r="U89" t="s" s="2">
         <v>77</v>
@@ -12954,13 +12855,13 @@
         <v>77</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>352</v>
+        <v>77</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>77</v>
@@ -12978,13 +12879,13 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>353</v>
+        <v>569</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH89" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI89" t="s" s="2">
         <v>77</v>
@@ -12993,13 +12894,13 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>354</v>
+        <v>573</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>318</v>
+        <v>574</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>77</v>
@@ -13013,10 +12914,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>495</v>
+        <v>575</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>356</v>
+        <v>575</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13036,20 +12937,18 @@
         <v>77</v>
       </c>
       <c r="J90" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>107</v>
+        <v>158</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>357</v>
+        <v>159</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N90" t="s" s="2">
-        <v>359</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="N90" s="2"/>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -13062,7 +12961,7 @@
         <v>77</v>
       </c>
       <c r="T90" t="s" s="2">
-        <v>360</v>
+        <v>77</v>
       </c>
       <c r="U90" t="s" s="2">
         <v>77</v>
@@ -13074,13 +12973,13 @@
         <v>77</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>173</v>
+        <v>77</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>361</v>
+        <v>77</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>77</v>
@@ -13098,7 +12997,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>363</v>
+        <v>161</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13110,13 +13009,13 @@
         <v>77</v>
       </c>
       <c r="AJ90" t="s" s="2">
-        <v>496</v>
+        <v>77</v>
       </c>
       <c r="AK90" t="s" s="2">
-        <v>364</v>
+        <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>318</v>
+        <v>162</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
@@ -13125,7 +13024,7 @@
         <v>77</v>
       </c>
       <c r="AO90" t="s" s="2">
-        <v>497</v>
+        <v>77</v>
       </c>
       <c r="AP90" t="s" s="2">
         <v>77</v>
@@ -13133,21 +13032,21 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>498</v>
+        <v>576</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>365</v>
+        <v>576</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E91" s="2"/>
       <c r="F91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G91" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H91" t="s" s="2">
         <v>77</v>
@@ -13156,23 +13055,21 @@
         <v>77</v>
       </c>
       <c r="J91" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>158</v>
+        <v>133</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>366</v>
+        <v>134</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>367</v>
+        <v>164</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>368</v>
-      </c>
-      <c r="O91" t="s" s="2">
-        <v>369</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>77</v>
       </c>
@@ -13184,7 +13081,7 @@
         <v>77</v>
       </c>
       <c r="T91" t="s" s="2">
-        <v>370</v>
+        <v>77</v>
       </c>
       <c r="U91" t="s" s="2">
         <v>77</v>
@@ -13208,37 +13105,37 @@
         <v>77</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>77</v>
+        <v>165</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>77</v>
+        <v>166</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE91" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>371</v>
+        <v>167</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH91" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>373</v>
+        <v>162</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
@@ -13255,10 +13152,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>499</v>
+        <v>577</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>374</v>
+        <v>577</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13269,10 +13166,10 @@
         <v>78</v>
       </c>
       <c r="G92" t="s" s="2">
-        <v>375</v>
+        <v>87</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>77</v>
@@ -13281,13 +13178,13 @@
         <v>88</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>376</v>
+        <v>290</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>377</v>
+        <v>291</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13302,7 +13199,7 @@
         <v>77</v>
       </c>
       <c r="T92" t="s" s="2">
-        <v>378</v>
+        <v>77</v>
       </c>
       <c r="U92" t="s" s="2">
         <v>77</v>
@@ -13314,13 +13211,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>77</v>
+        <v>292</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>77</v>
+        <v>293</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -13338,34 +13235,34 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>379</v>
+        <v>294</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH92" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>77</v>
+        <v>295</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>380</v>
+        <v>296</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>381</v>
+        <v>297</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>382</v>
+        <v>298</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>500</v>
+        <v>77</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>77</v>
@@ -13373,14 +13270,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>501</v>
+        <v>578</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>383</v>
+        <v>578</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>384</v>
+        <v>77</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13402,13 +13299,17 @@
         <v>158</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>385</v>
+        <v>300</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
+        <v>301</v>
+      </c>
+      <c r="N93" t="s" s="2">
+        <v>302</v>
+      </c>
+      <c r="O93" t="s" s="2">
+        <v>303</v>
+      </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
       </c>
@@ -13420,7 +13321,7 @@
         <v>77</v>
       </c>
       <c r="T93" t="s" s="2">
-        <v>387</v>
+        <v>77</v>
       </c>
       <c r="U93" t="s" s="2">
         <v>77</v>
@@ -13456,7 +13357,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>388</v>
+        <v>304</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13471,19 +13372,19 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>389</v>
+        <v>305</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>390</v>
+        <v>306</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>391</v>
+        <v>207</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>502</v>
+        <v>579</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>77</v>
@@ -13491,14 +13392,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>503</v>
+        <v>580</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>392</v>
+        <v>580</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>393</v>
+        <v>77</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -13511,24 +13412,26 @@
         <v>77</v>
       </c>
       <c r="I94" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J94" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>394</v>
+        <v>308</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>395</v>
+        <v>309</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="O94" s="2"/>
+        <v>310</v>
+      </c>
+      <c r="O94" t="s" s="2">
+        <v>311</v>
+      </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
       </c>
@@ -13540,7 +13443,7 @@
         <v>77</v>
       </c>
       <c r="T94" t="s" s="2">
-        <v>397</v>
+        <v>77</v>
       </c>
       <c r="U94" t="s" s="2">
         <v>77</v>
@@ -13552,13 +13455,13 @@
         <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>77</v>
+        <v>173</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>77</v>
+        <v>312</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>77</v>
+        <v>313</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -13576,7 +13479,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>398</v>
+        <v>314</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13591,13 +13494,13 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>399</v>
+        <v>315</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>400</v>
+        <v>316</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>77</v>
+        <v>317</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>77</v>
@@ -13611,14 +13514,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>504</v>
+        <v>581</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>401</v>
+        <v>581</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -13628,7 +13531,7 @@
         <v>87</v>
       </c>
       <c r="H95" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I95" t="s" s="2">
         <v>77</v>
@@ -13637,15 +13540,17 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>158</v>
+        <v>319</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>403</v>
+        <v>320</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N95" s="2"/>
+        <v>321</v>
+      </c>
+      <c r="N95" t="s" s="2">
+        <v>322</v>
+      </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -13670,13 +13575,13 @@
         <v>77</v>
       </c>
       <c r="X95" t="s" s="2">
-        <v>184</v>
+        <v>77</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>405</v>
+        <v>77</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>406</v>
+        <v>77</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>77</v>
@@ -13694,7 +13599,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>407</v>
+        <v>323</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13709,19 +13614,19 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
-        <v>408</v>
+        <v>162</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>409</v>
+        <v>162</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>410</v>
+        <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO95" t="s" s="2">
-        <v>505</v>
+        <v>77</v>
       </c>
       <c r="AP95" t="s" s="2">
         <v>77</v>
@@ -13729,14 +13634,14 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>506</v>
+        <v>582</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>411</v>
+        <v>582</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
-        <v>412</v>
+        <v>77</v>
       </c>
       <c r="E96" s="2"/>
       <c r="F96" t="s" s="2">
@@ -13746,7 +13651,7 @@
         <v>87</v>
       </c>
       <c r="H96" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I96" t="s" s="2">
         <v>77</v>
@@ -13755,13 +13660,13 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>158</v>
+        <v>211</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>413</v>
+        <v>325</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>414</v>
+        <v>326</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13776,7 +13681,7 @@
         <v>77</v>
       </c>
       <c r="T96" t="s" s="2">
-        <v>415</v>
+        <v>77</v>
       </c>
       <c r="U96" t="s" s="2">
         <v>77</v>
@@ -13812,7 +13717,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>416</v>
+        <v>327</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13827,19 +13732,19 @@
         <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
-        <v>417</v>
+        <v>130</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>418</v>
+        <v>328</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>419</v>
+        <v>217</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>507</v>
+        <v>77</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>77</v>
@@ -13847,10 +13752,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>508</v>
+        <v>583</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>420</v>
+        <v>583</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13864,27 +13769,27 @@
         <v>87</v>
       </c>
       <c r="H97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J97" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>158</v>
+        <v>330</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>421</v>
+        <v>584</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>422</v>
-      </c>
-      <c r="N97" t="s" s="2">
-        <v>423</v>
-      </c>
-      <c r="O97" s="2"/>
+        <v>585</v>
+      </c>
+      <c r="N97" s="2"/>
+      <c r="O97" t="s" s="2">
+        <v>586</v>
+      </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
       </c>
@@ -13932,7 +13837,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>424</v>
+        <v>583</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13947,30 +13852,30 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>425</v>
+        <v>587</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>426</v>
+        <v>588</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>427</v>
+        <v>77</v>
       </c>
       <c r="AN97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO97" t="s" s="2">
-        <v>509</v>
+        <v>77</v>
       </c>
       <c r="AP97" t="s" s="2">
-        <v>488</v>
+        <v>77</v>
       </c>
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>510</v>
+        <v>589</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>428</v>
+        <v>589</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13981,7 +13886,7 @@
         <v>78</v>
       </c>
       <c r="G98" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H98" t="s" s="2">
         <v>77</v>
@@ -13990,20 +13895,20 @@
         <v>77</v>
       </c>
       <c r="J98" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>211</v>
+        <v>590</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>429</v>
+        <v>591</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>430</v>
+        <v>592</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>431</v>
+        <v>593</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -14016,7 +13921,7 @@
         <v>77</v>
       </c>
       <c r="T98" t="s" s="2">
-        <v>432</v>
+        <v>77</v>
       </c>
       <c r="U98" t="s" s="2">
         <v>77</v>
@@ -14052,13 +13957,13 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>433</v>
+        <v>589</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH98" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI98" t="s" s="2">
         <v>77</v>
@@ -14067,13 +13972,13 @@
         <v>99</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>434</v>
+        <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>330</v>
+        <v>162</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>217</v>
+        <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>77</v>
@@ -14082,3129 +13987,11 @@
         <v>77</v>
       </c>
       <c r="AP98" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="99" hidden="true">
-      <c r="A99" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="B99" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="C99" s="2"/>
-      <c r="D99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E99" s="2"/>
-      <c r="F99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G99" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J99" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K99" t="s" s="2">
-        <v>219</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>512</v>
-      </c>
-      <c r="M99" t="s" s="2">
-        <v>513</v>
-      </c>
-      <c r="N99" s="2"/>
-      <c r="O99" t="s" s="2">
-        <v>514</v>
-      </c>
-      <c r="P99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q99" s="2"/>
-      <c r="R99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF99" t="s" s="2">
-        <v>511</v>
-      </c>
-      <c r="AG99" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH99" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ99" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK99" t="s" s="2">
-        <v>243</v>
-      </c>
-      <c r="AL99" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AM99" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AN99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO99" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP99" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="100" hidden="true">
-      <c r="A100" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="C100" s="2"/>
-      <c r="D100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E100" s="2"/>
-      <c r="F100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K100" t="s" s="2">
-        <v>517</v>
-      </c>
-      <c r="L100" t="s" s="2">
-        <v>518</v>
-      </c>
-      <c r="M100" t="s" s="2">
-        <v>519</v>
-      </c>
-      <c r="N100" t="s" s="2">
-        <v>520</v>
-      </c>
-      <c r="O100" t="s" s="2">
-        <v>521</v>
-      </c>
-      <c r="P100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q100" s="2"/>
-      <c r="R100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF100" t="s" s="2">
-        <v>516</v>
-      </c>
-      <c r="AG100" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH100" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ100" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL100" t="s" s="2">
-        <v>522</v>
-      </c>
-      <c r="AM100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO100" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP100" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="101" hidden="true">
-      <c r="A101" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>523</v>
-      </c>
-      <c r="C101" s="2"/>
-      <c r="D101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E101" s="2"/>
-      <c r="F101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G101" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K101" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L101" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M101" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N101" s="2"/>
-      <c r="O101" s="2"/>
-      <c r="P101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q101" s="2"/>
-      <c r="R101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF101" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG101" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH101" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL101" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO101" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP101" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="102" hidden="true">
-      <c r="A102" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>524</v>
-      </c>
-      <c r="C102" s="2"/>
-      <c r="D102" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E102" s="2"/>
-      <c r="F102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K102" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L102" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M102" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N102" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O102" s="2"/>
-      <c r="P102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q102" s="2"/>
-      <c r="R102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF102" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AG102" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH102" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ102" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL102" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO102" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP102" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="103" hidden="true">
-      <c r="A103" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>525</v>
-      </c>
-      <c r="C103" s="2"/>
-      <c r="D103" t="s" s="2">
-        <v>526</v>
-      </c>
-      <c r="E103" s="2"/>
-      <c r="F103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I103" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J103" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K103" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L103" t="s" s="2">
-        <v>527</v>
-      </c>
-      <c r="M103" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N103" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O103" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q103" s="2"/>
-      <c r="R103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF103" t="s" s="2">
-        <v>529</v>
-      </c>
-      <c r="AG103" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH103" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ103" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL103" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO103" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP103" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="104" hidden="true">
-      <c r="A104" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="B104" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E104" s="2"/>
-      <c r="F104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="L104" t="s" s="2">
-        <v>531</v>
-      </c>
-      <c r="M104" t="s" s="2">
-        <v>532</v>
-      </c>
-      <c r="N104" s="2"/>
-      <c r="O104" t="s" s="2">
-        <v>533</v>
-      </c>
-      <c r="P104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q104" s="2"/>
-      <c r="R104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X104" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="Y104" t="s" s="2">
-        <v>534</v>
-      </c>
-      <c r="Z104" t="s" s="2">
-        <v>535</v>
-      </c>
-      <c r="AA104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF104" t="s" s="2">
-        <v>530</v>
-      </c>
-      <c r="AG104" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH104" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ104" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL104" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="AM104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO104" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP104" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="105" hidden="true">
-      <c r="A105" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="B105" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="C105" s="2"/>
-      <c r="D105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E105" s="2"/>
-      <c r="F105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G105" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K105" t="s" s="2">
-        <v>538</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>539</v>
-      </c>
-      <c r="M105" t="s" s="2">
-        <v>540</v>
-      </c>
-      <c r="N105" s="2"/>
-      <c r="O105" t="s" s="2">
-        <v>541</v>
-      </c>
-      <c r="P105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q105" s="2"/>
-      <c r="R105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF105" t="s" s="2">
-        <v>537</v>
-      </c>
-      <c r="AG105" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH105" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ105" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK105" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="AL105" t="s" s="2">
-        <v>543</v>
-      </c>
-      <c r="AM105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO105" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP105" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="106" hidden="true">
-      <c r="A106" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="B106" t="s" s="2">
-        <v>544</v>
-      </c>
-      <c r="C106" s="2"/>
-      <c r="D106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E106" s="2"/>
-      <c r="F106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K106" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L106" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M106" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N106" s="2"/>
-      <c r="O106" s="2"/>
-      <c r="P106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q106" s="2"/>
-      <c r="R106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF106" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG106" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH106" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL106" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO106" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP106" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="107" hidden="true">
-      <c r="A107" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="B107" t="s" s="2">
-        <v>545</v>
-      </c>
-      <c r="C107" s="2"/>
-      <c r="D107" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E107" s="2"/>
-      <c r="F107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K107" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L107" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M107" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N107" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O107" s="2"/>
-      <c r="P107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q107" s="2"/>
-      <c r="R107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB107" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AC107" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AD107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE107" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF107" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AG107" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH107" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ107" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL107" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO107" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP107" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="108" hidden="true">
-      <c r="A108" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="B108" t="s" s="2">
-        <v>546</v>
-      </c>
-      <c r="C108" s="2"/>
-      <c r="D108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E108" s="2"/>
-      <c r="F108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I108" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J108" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K108" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L108" t="s" s="2">
-        <v>547</v>
-      </c>
-      <c r="M108" t="s" s="2">
-        <v>548</v>
-      </c>
-      <c r="N108" t="s" s="2">
-        <v>549</v>
-      </c>
-      <c r="O108" t="s" s="2">
-        <v>550</v>
-      </c>
-      <c r="P108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q108" s="2"/>
-      <c r="R108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X108" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y108" t="s" s="2">
-        <v>551</v>
-      </c>
-      <c r="Z108" t="s" s="2">
-        <v>552</v>
-      </c>
-      <c r="AA108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF108" t="s" s="2">
-        <v>553</v>
-      </c>
-      <c r="AG108" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH108" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ108" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK108" t="s" s="2">
-        <v>554</v>
-      </c>
-      <c r="AL108" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AM108" t="s" s="2">
-        <v>555</v>
-      </c>
-      <c r="AN108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO108" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP108" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="109" hidden="true">
-      <c r="A109" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="B109" t="s" s="2">
-        <v>556</v>
-      </c>
-      <c r="C109" s="2"/>
-      <c r="D109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E109" s="2"/>
-      <c r="F109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G109" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J109" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K109" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L109" t="s" s="2">
-        <v>557</v>
-      </c>
-      <c r="M109" t="s" s="2">
-        <v>558</v>
-      </c>
-      <c r="N109" t="s" s="2">
-        <v>559</v>
-      </c>
-      <c r="O109" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="P109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q109" s="2"/>
-      <c r="R109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF109" t="s" s="2">
-        <v>560</v>
-      </c>
-      <c r="AG109" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH109" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ109" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK109" t="s" s="2">
-        <v>561</v>
-      </c>
-      <c r="AL109" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="AM109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN109" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO109" t="s" s="2">
-        <v>562</v>
-      </c>
-      <c r="AP109" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="110" hidden="true">
-      <c r="A110" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="B110" t="s" s="2">
-        <v>563</v>
-      </c>
-      <c r="C110" s="2"/>
-      <c r="D110" t="s" s="2">
-        <v>564</v>
-      </c>
-      <c r="E110" s="2"/>
-      <c r="F110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G110" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J110" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K110" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L110" t="s" s="2">
-        <v>565</v>
-      </c>
-      <c r="M110" t="s" s="2">
-        <v>566</v>
-      </c>
-      <c r="N110" t="s" s="2">
-        <v>567</v>
-      </c>
-      <c r="O110" s="2"/>
-      <c r="P110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q110" s="2"/>
-      <c r="R110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF110" t="s" s="2">
-        <v>568</v>
-      </c>
-      <c r="AG110" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH110" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ110" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK110" t="s" s="2">
-        <v>569</v>
-      </c>
-      <c r="AL110" t="s" s="2">
-        <v>570</v>
-      </c>
-      <c r="AM110" t="s" s="2">
-        <v>571</v>
-      </c>
-      <c r="AN110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO110" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP110" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="111" hidden="true">
-      <c r="A111" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="B111" t="s" s="2">
-        <v>572</v>
-      </c>
-      <c r="C111" s="2"/>
-      <c r="D111" t="s" s="2">
-        <v>573</v>
-      </c>
-      <c r="E111" s="2"/>
-      <c r="F111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J111" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K111" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L111" t="s" s="2">
-        <v>574</v>
-      </c>
-      <c r="M111" t="s" s="2">
-        <v>575</v>
-      </c>
-      <c r="N111" t="s" s="2">
-        <v>576</v>
-      </c>
-      <c r="O111" s="2"/>
-      <c r="P111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q111" s="2"/>
-      <c r="R111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF111" t="s" s="2">
-        <v>577</v>
-      </c>
-      <c r="AG111" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH111" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ111" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK111" t="s" s="2">
-        <v>578</v>
-      </c>
-      <c r="AL111" t="s" s="2">
-        <v>579</v>
-      </c>
-      <c r="AM111" t="s" s="2">
-        <v>580</v>
-      </c>
-      <c r="AN111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO111" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP111" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="112" hidden="true">
-      <c r="A112" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="B112" t="s" s="2">
-        <v>581</v>
-      </c>
-      <c r="C112" s="2"/>
-      <c r="D112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E112" s="2"/>
-      <c r="F112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J112" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K112" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L112" t="s" s="2">
-        <v>582</v>
-      </c>
-      <c r="M112" t="s" s="2">
-        <v>583</v>
-      </c>
-      <c r="N112" s="2"/>
-      <c r="O112" s="2"/>
-      <c r="P112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q112" s="2"/>
-      <c r="R112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF112" t="s" s="2">
-        <v>584</v>
-      </c>
-      <c r="AG112" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH112" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ112" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK112" t="s" s="2">
-        <v>585</v>
-      </c>
-      <c r="AL112" t="s" s="2">
-        <v>586</v>
-      </c>
-      <c r="AM112" t="s" s="2">
-        <v>587</v>
-      </c>
-      <c r="AN112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO112" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP112" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="113" hidden="true">
-      <c r="A113" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="B113" t="s" s="2">
-        <v>588</v>
-      </c>
-      <c r="C113" s="2"/>
-      <c r="D113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E113" s="2"/>
-      <c r="F113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J113" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K113" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L113" t="s" s="2">
-        <v>589</v>
-      </c>
-      <c r="M113" t="s" s="2">
-        <v>590</v>
-      </c>
-      <c r="N113" s="2"/>
-      <c r="O113" s="2"/>
-      <c r="P113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q113" s="2"/>
-      <c r="R113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF113" t="s" s="2">
-        <v>591</v>
-      </c>
-      <c r="AG113" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH113" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ113" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK113" t="s" s="2">
-        <v>592</v>
-      </c>
-      <c r="AL113" t="s" s="2">
-        <v>593</v>
-      </c>
-      <c r="AM113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO113" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP113" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="114" hidden="true">
-      <c r="A114" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="B114" t="s" s="2">
-        <v>594</v>
-      </c>
-      <c r="C114" s="2"/>
-      <c r="D114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E114" s="2"/>
-      <c r="F114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J114" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K114" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>595</v>
-      </c>
-      <c r="M114" t="s" s="2">
-        <v>596</v>
-      </c>
-      <c r="N114" s="2"/>
-      <c r="O114" t="s" s="2">
-        <v>597</v>
-      </c>
-      <c r="P114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q114" s="2"/>
-      <c r="R114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF114" t="s" s="2">
-        <v>598</v>
-      </c>
-      <c r="AG114" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH114" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ114" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK114" t="s" s="2">
-        <v>599</v>
-      </c>
-      <c r="AL114" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AM114" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO114" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP114" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="115" hidden="true">
-      <c r="A115" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="B115" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="C115" s="2"/>
-      <c r="D115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E115" s="2"/>
-      <c r="F115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K115" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="L115" t="s" s="2">
-        <v>601</v>
-      </c>
-      <c r="M115" t="s" s="2">
-        <v>602</v>
-      </c>
-      <c r="N115" s="2"/>
-      <c r="O115" t="s" s="2">
-        <v>603</v>
-      </c>
-      <c r="P115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q115" s="2"/>
-      <c r="R115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF115" t="s" s="2">
-        <v>600</v>
-      </c>
-      <c r="AG115" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH115" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ115" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK115" t="s" s="2">
-        <v>604</v>
-      </c>
-      <c r="AL115" t="s" s="2">
-        <v>605</v>
-      </c>
-      <c r="AM115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO115" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP115" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="116" hidden="true">
-      <c r="A116" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="B116" t="s" s="2">
-        <v>606</v>
-      </c>
-      <c r="C116" s="2"/>
-      <c r="D116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E116" s="2"/>
-      <c r="F116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G116" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K116" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L116" t="s" s="2">
-        <v>159</v>
-      </c>
-      <c r="M116" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
-      <c r="P116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q116" s="2"/>
-      <c r="R116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF116" t="s" s="2">
-        <v>161</v>
-      </c>
-      <c r="AG116" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH116" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL116" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO116" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP116" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="117" hidden="true">
-      <c r="A117" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="B117" t="s" s="2">
-        <v>607</v>
-      </c>
-      <c r="C117" s="2"/>
-      <c r="D117" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E117" s="2"/>
-      <c r="F117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K117" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L117" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M117" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N117" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O117" s="2"/>
-      <c r="P117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q117" s="2"/>
-      <c r="R117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB117" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="AC117" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AD117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE117" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF117" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AG117" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH117" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ117" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL117" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO117" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP117" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="118" hidden="true">
-      <c r="A118" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>608</v>
-      </c>
-      <c r="C118" s="2"/>
-      <c r="D118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E118" s="2"/>
-      <c r="F118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G118" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J118" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K118" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L118" t="s" s="2">
-        <v>292</v>
-      </c>
-      <c r="M118" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="N118" s="2"/>
-      <c r="O118" s="2"/>
-      <c r="P118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>294</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>295</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF118" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>297</v>
-      </c>
-      <c r="AJ118" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK118" t="s" s="2">
-        <v>298</v>
-      </c>
-      <c r="AL118" t="s" s="2">
-        <v>299</v>
-      </c>
-      <c r="AM118" t="s" s="2">
-        <v>300</v>
-      </c>
-      <c r="AN118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO118" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP118" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="119" hidden="true">
-      <c r="A119" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="B119" t="s" s="2">
-        <v>609</v>
-      </c>
-      <c r="C119" s="2"/>
-      <c r="D119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E119" s="2"/>
-      <c r="F119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J119" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K119" t="s" s="2">
-        <v>158</v>
-      </c>
-      <c r="L119" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="M119" t="s" s="2">
-        <v>303</v>
-      </c>
-      <c r="N119" t="s" s="2">
-        <v>304</v>
-      </c>
-      <c r="O119" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="P119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q119" s="2"/>
-      <c r="R119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF119" t="s" s="2">
-        <v>306</v>
-      </c>
-      <c r="AG119" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH119" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ119" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK119" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="AL119" t="s" s="2">
-        <v>308</v>
-      </c>
-      <c r="AM119" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN119" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO119" t="s" s="2">
-        <v>610</v>
-      </c>
-      <c r="AP119" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="120" hidden="true">
-      <c r="A120" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="B120" t="s" s="2">
-        <v>611</v>
-      </c>
-      <c r="C120" s="2"/>
-      <c r="D120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E120" s="2"/>
-      <c r="F120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G120" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I120" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J120" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K120" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="L120" t="s" s="2">
-        <v>310</v>
-      </c>
-      <c r="M120" t="s" s="2">
-        <v>311</v>
-      </c>
-      <c r="N120" t="s" s="2">
-        <v>312</v>
-      </c>
-      <c r="O120" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="P120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q120" s="2"/>
-      <c r="R120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X120" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="Y120" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="Z120" t="s" s="2">
-        <v>315</v>
-      </c>
-      <c r="AA120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF120" t="s" s="2">
-        <v>316</v>
-      </c>
-      <c r="AG120" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH120" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ120" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK120" t="s" s="2">
-        <v>317</v>
-      </c>
-      <c r="AL120" t="s" s="2">
-        <v>318</v>
-      </c>
-      <c r="AM120" t="s" s="2">
-        <v>319</v>
-      </c>
-      <c r="AN120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO120" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP120" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="121" hidden="true">
-      <c r="A121" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="B121" t="s" s="2">
-        <v>612</v>
-      </c>
-      <c r="C121" s="2"/>
-      <c r="D121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E121" s="2"/>
-      <c r="F121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J121" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K121" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="L121" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="M121" t="s" s="2">
-        <v>323</v>
-      </c>
-      <c r="N121" t="s" s="2">
-        <v>324</v>
-      </c>
-      <c r="O121" s="2"/>
-      <c r="P121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q121" s="2"/>
-      <c r="R121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF121" t="s" s="2">
-        <v>325</v>
-      </c>
-      <c r="AG121" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH121" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ121" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK121" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AL121" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO121" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP121" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="122" hidden="true">
-      <c r="A122" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="B122" t="s" s="2">
-        <v>613</v>
-      </c>
-      <c r="C122" s="2"/>
-      <c r="D122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E122" s="2"/>
-      <c r="F122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G122" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J122" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K122" t="s" s="2">
-        <v>211</v>
-      </c>
-      <c r="L122" t="s" s="2">
-        <v>327</v>
-      </c>
-      <c r="M122" t="s" s="2">
-        <v>328</v>
-      </c>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q122" s="2"/>
-      <c r="R122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF122" t="s" s="2">
-        <v>329</v>
-      </c>
-      <c r="AG122" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH122" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ122" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK122" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AL122" t="s" s="2">
-        <v>330</v>
-      </c>
-      <c r="AM122" t="s" s="2">
-        <v>217</v>
-      </c>
-      <c r="AN122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO122" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP122" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="123" hidden="true">
-      <c r="A123" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="B123" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="C123" s="2"/>
-      <c r="D123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E123" s="2"/>
-      <c r="F123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G123" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K123" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="L123" t="s" s="2">
-        <v>615</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>616</v>
-      </c>
-      <c r="N123" s="2"/>
-      <c r="O123" t="s" s="2">
-        <v>617</v>
-      </c>
-      <c r="P123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q123" s="2"/>
-      <c r="R123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF123" t="s" s="2">
-        <v>614</v>
-      </c>
-      <c r="AG123" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH123" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ123" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK123" t="s" s="2">
-        <v>618</v>
-      </c>
-      <c r="AL123" t="s" s="2">
-        <v>619</v>
-      </c>
-      <c r="AM123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO123" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP123" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="124" hidden="true">
-      <c r="A124" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="B124" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="C124" s="2"/>
-      <c r="D124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E124" s="2"/>
-      <c r="F124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K124" t="s" s="2">
-        <v>621</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>622</v>
-      </c>
-      <c r="M124" t="s" s="2">
-        <v>623</v>
-      </c>
-      <c r="N124" s="2"/>
-      <c r="O124" t="s" s="2">
-        <v>624</v>
-      </c>
-      <c r="P124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q124" s="2"/>
-      <c r="R124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF124" t="s" s="2">
-        <v>620</v>
-      </c>
-      <c r="AG124" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH124" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ124" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL124" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="AM124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO124" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP124" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP124">
+  <autoFilter ref="A1:AP98">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -17214,7 +14001,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI123">
+  <conditionalFormatting sqref="A2:AI97">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.14.0</t>
+    <t>0.15.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-13T13:47:03+00:00</t>
+    <t>2024-01-14T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.15.0</t>
+    <t>0.16.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-01-14T11:16:16+00:00</t>
+    <t>2024-02-08T09:36:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1666,7 +1666,7 @@
     <t>implied by XPN.11</t>
   </si>
   <si>
-    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT – NAME (#4-4 &gt; 4.03-.01)</t>
+    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT - NAME (#4-4 &gt; 4.03-.01)</t>
   </si>
   <si>
     <t>Organization.contact.name.family</t>
@@ -1812,7 +1812,7 @@
     <t>Organization.contact.telecom.value</t>
   </si>
   <si>
-    <t>1266: source value from INSTITUTION - CONTACT &gt; CONTACT – PHONE # (#4-4 &gt; 4.03-.03)</t>
+    <t>1266: source value from INSTITUTION - CONTACT &gt; CONTACT - PHONE # (#4-4 &gt; 4.03-.03)</t>
   </si>
   <si>
     <t>Organization.contact.telecom.use</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-08T09:36:20+00:00</t>
+    <t>2024-02-09T16:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-09T16:38:59+00:00</t>
+    <t>2024-02-11T14:24:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.16.0</t>
+    <t>0.17.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-11T14:24:24+00:00</t>
+    <t>2024-02-12T08:51:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.17.0</t>
+    <t>0.18.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T08:51:11+00:00</t>
+    <t>2024-02-13T17:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.18.0</t>
+    <t>0.19.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T17:27:52+00:00</t>
+    <t>2024-02-13T18:57:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T18:57:41+00:00</t>
+    <t>2024-02-13T19:55:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.19.0</t>
+    <t>0.20.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-13T19:55:01+00:00</t>
+    <t>2024-02-17T09:04:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.20.0</t>
+    <t>0.21.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:04:28+00:00</t>
+    <t>2024-02-17T09:43:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.21.0</t>
+    <t>0.22.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-17T09:43:43+00:00</t>
+    <t>2024-02-18T11:03:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="596">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.22.0</t>
+    <t>0.23.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-18T11:03:00+00:00</t>
+    <t>2024-02-23T15:31:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -773,6 +773,9 @@
     <t>This resource is generally assumed to be active if no value is provided for the active element</t>
   </si>
   <si>
+    <t>true</t>
+  </si>
+  <si>
     <t>No equivalent in HL7 v2</t>
   </si>
   <si>
@@ -805,6 +808,13 @@
     <t>Need to be able to track the kind of organization that this is - different organization types have different uses.</t>
   </si>
   <si>
+    <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
+  &lt;coding&gt;
+    &lt;code value="prov"/&gt;
+  &lt;/coding&gt;
+&lt;/valueCodeableConcept&gt;</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -823,7 +833,7 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1254: fixed value = prov</t>
+    <t>1254: fixed value = #prov</t>
   </si>
   <si>
     <t>Organization.name</t>
@@ -4804,7 +4814,7 @@
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>77</v>
+        <v>242</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>77</v>
@@ -4858,19 +4868,19 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AP22" t="s" s="2">
         <v>77</v>
@@ -4878,10 +4888,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4907,16 +4917,16 @@
         <v>179</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4926,7 +4936,7 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>77</v>
+        <v>253</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>77</v>
@@ -4941,13 +4951,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -4965,7 +4975,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4980,19 +4990,19 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>162</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AP23" t="s" s="2">
         <v>77</v>
@@ -5000,10 +5010,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5029,16 +5039,16 @@
         <v>158</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5087,7 +5097,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5102,30 +5112,30 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5151,16 +5161,16 @@
         <v>158</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5209,7 +5219,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5227,7 +5237,7 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
@@ -5236,18 +5246,18 @@
         <v>77</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5270,19 +5280,19 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5331,7 +5341,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5340,19 +5350,19 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>77</v>
@@ -5366,10 +5376,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5484,10 +5494,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5604,10 +5614,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5633,10 +5643,10 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5666,10 +5676,10 @@
         <v>173</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5687,7 +5697,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5696,19 +5706,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
@@ -5722,10 +5732,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5751,16 +5761,16 @@
         <v>158</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5809,7 +5819,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5824,10 +5834,10 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>207</v>
@@ -5844,10 +5854,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5873,16 +5883,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5910,10 +5920,10 @@
         <v>173</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5931,7 +5941,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5946,13 +5956,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5966,10 +5976,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5992,16 +6002,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6051,7 +6061,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6086,10 +6096,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6115,10 +6125,10 @@
         <v>211</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6169,7 +6179,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6187,7 +6197,7 @@
         <v>130</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>217</v>
@@ -6204,10 +6214,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6230,19 +6240,19 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6279,7 +6289,7 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -6289,7 +6299,7 @@
         <v>151</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6298,19 +6308,19 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -6324,10 +6334,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6442,10 +6452,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6562,10 +6572,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6591,16 +6601,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6613,7 +6623,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6628,10 +6638,10 @@
         <v>173</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6649,7 +6659,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6664,13 +6674,13 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -6684,10 +6694,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6713,13 +6723,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6733,7 +6743,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6748,10 +6758,10 @@
         <v>173</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6769,7 +6779,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6784,10 +6794,10 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
@@ -6804,10 +6814,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6833,16 +6843,16 @@
         <v>158</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6855,7 +6865,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6891,7 +6901,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6906,10 +6916,10 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
@@ -6926,10 +6936,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6940,7 +6950,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -6955,10 +6965,10 @@
         <v>158</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6973,7 +6983,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -7009,7 +7019,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7024,13 +7034,13 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>77</v>
@@ -7044,14 +7054,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7073,10 +7083,10 @@
         <v>158</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7091,7 +7101,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -7127,7 +7137,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7142,13 +7152,13 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>77</v>
@@ -7162,14 +7172,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7191,13 +7201,13 @@
         <v>158</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7211,7 +7221,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -7247,7 +7257,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7262,10 +7272,10 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -7282,14 +7292,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7311,10 +7321,10 @@
         <v>158</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7344,10 +7354,10 @@
         <v>184</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7365,7 +7375,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7380,13 +7390,13 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>77</v>
@@ -7400,14 +7410,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7429,10 +7439,10 @@
         <v>158</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7447,7 +7457,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7483,7 +7493,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7498,13 +7508,13 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -7518,10 +7528,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7547,13 +7557,13 @@
         <v>158</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7603,7 +7613,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7618,13 +7628,13 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>77</v>
@@ -7638,10 +7648,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7667,14 +7677,14 @@
         <v>211</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7687,7 +7697,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7723,7 +7733,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7738,10 +7748,10 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>217</v>
@@ -7758,13 +7768,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7786,19 +7796,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7847,7 +7857,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7856,19 +7866,19 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7882,10 +7892,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8000,10 +8010,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8120,10 +8130,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8149,16 +8159,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8171,7 +8181,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -8186,10 +8196,10 @@
         <v>173</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -8207,7 +8217,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8222,13 +8232,13 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -8242,10 +8252,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8271,13 +8281,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8288,10 +8298,10 @@
         <v>77</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>77</v>
+        <v>436</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -8306,10 +8316,10 @@
         <v>173</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8327,7 +8337,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8342,10 +8352,10 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -8354,7 +8364,7 @@
         <v>77</v>
       </c>
       <c r="AO51" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>77</v>
@@ -8362,10 +8372,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8391,16 +8401,16 @@
         <v>158</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8413,7 +8423,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -8449,7 +8459,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8464,10 +8474,10 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
@@ -8484,10 +8494,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8498,7 +8508,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>88</v>
@@ -8513,10 +8523,10 @@
         <v>158</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8531,7 +8541,7 @@
         <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>77</v>
@@ -8567,7 +8577,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8582,34 +8592,34 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8631,10 +8641,10 @@
         <v>158</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8649,7 +8659,7 @@
         <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8685,7 +8695,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8700,34 +8710,34 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8749,13 +8759,13 @@
         <v>158</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8769,7 +8779,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8805,7 +8815,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8820,10 +8830,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
@@ -8832,22 +8842,22 @@
         <v>77</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8869,10 +8879,10 @@
         <v>158</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8902,10 +8912,10 @@
         <v>184</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8923,7 +8933,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8938,34 +8948,34 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="AP56" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8987,10 +8997,10 @@
         <v>158</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9005,7 +9015,7 @@
         <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>77</v>
@@ -9041,7 +9051,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9056,30 +9066,30 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AP57" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9105,13 +9115,13 @@
         <v>158</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9161,7 +9171,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9176,30 +9186,30 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9225,14 +9235,14 @@
         <v>211</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9245,7 +9255,7 @@
         <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>77</v>
@@ -9281,7 +9291,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9296,10 +9306,10 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>217</v>
@@ -9316,13 +9326,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9344,19 +9354,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9405,7 +9415,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9414,19 +9424,19 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -9440,10 +9450,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9558,10 +9568,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9678,10 +9688,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9707,16 +9717,16 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9729,7 +9739,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9744,10 +9754,10 @@
         <v>173</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9765,7 +9775,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9780,13 +9790,13 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>77</v>
@@ -9800,10 +9810,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9829,13 +9839,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9846,10 +9856,10 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>77</v>
+        <v>463</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9864,10 +9874,10 @@
         <v>173</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9885,7 +9895,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9900,10 +9910,10 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
@@ -9912,7 +9922,7 @@
         <v>77</v>
       </c>
       <c r="AO64" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>77</v>
@@ -9920,10 +9930,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9949,16 +9959,16 @@
         <v>158</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9971,7 +9981,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -10007,7 +10017,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10022,10 +10032,10 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
@@ -10042,10 +10052,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10056,7 +10066,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>88</v>
@@ -10071,10 +10081,10 @@
         <v>158</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10089,7 +10099,7 @@
         <v>77</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>77</v>
@@ -10125,7 +10135,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10140,19 +10150,19 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>77</v>
@@ -10160,14 +10170,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10189,10 +10199,10 @@
         <v>158</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10207,7 +10217,7 @@
         <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>77</v>
@@ -10243,7 +10253,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10258,19 +10268,19 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>77</v>
@@ -10278,14 +10288,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10307,13 +10317,13 @@
         <v>158</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10327,7 +10337,7 @@
         <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>77</v>
@@ -10363,7 +10373,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10378,10 +10388,10 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
@@ -10398,14 +10408,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10427,10 +10437,10 @@
         <v>158</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10460,10 +10470,10 @@
         <v>184</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10481,7 +10491,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10496,19 +10506,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10516,14 +10526,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10545,10 +10555,10 @@
         <v>158</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10563,7 +10573,7 @@
         <v>77</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>77</v>
@@ -10599,7 +10609,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10614,19 +10624,19 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>77</v>
@@ -10634,10 +10644,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10663,13 +10673,13 @@
         <v>158</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10719,7 +10729,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10734,30 +10744,30 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10783,14 +10793,14 @@
         <v>211</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10803,7 +10813,7 @@
         <v>77</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>77</v>
@@ -10839,7 +10849,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10854,10 +10864,10 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>217</v>
@@ -10874,10 +10884,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10903,14 +10913,14 @@
         <v>219</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10959,7 +10969,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10974,10 +10984,10 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>162</v>
@@ -10994,10 +11004,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11020,19 +11030,19 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11081,7 +11091,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11099,7 +11109,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -11116,10 +11126,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11234,10 +11244,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11354,14 +11364,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11383,10 +11393,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>136</v>
@@ -11441,7 +11451,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11476,10 +11486,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11505,14 +11515,14 @@
         <v>179</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11540,10 +11550,10 @@
         <v>184</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11561,7 +11571,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11579,7 +11589,7 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
@@ -11596,10 +11606,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11622,17 +11632,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11681,7 +11691,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11696,10 +11706,10 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
@@ -11716,10 +11726,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11834,10 +11844,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11954,10 +11964,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11983,16 +11993,16 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12020,10 +12030,10 @@
         <v>173</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12041,7 +12051,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12056,13 +12066,13 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>77</v>
@@ -12076,10 +12086,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12105,16 +12115,16 @@
         <v>158</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12163,7 +12173,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12178,10 +12188,10 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="AM83" t="s" s="2">
         <v>77</v>
@@ -12190,7 +12200,7 @@
         <v>77</v>
       </c>
       <c r="AO83" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>77</v>
@@ -12198,14 +12208,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12227,13 +12237,13 @@
         <v>158</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12283,7 +12293,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12298,13 +12308,13 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>77</v>
@@ -12318,14 +12328,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12347,13 +12357,13 @@
         <v>158</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12403,7 +12413,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12418,13 +12428,13 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>77</v>
@@ -12438,10 +12448,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12467,10 +12477,10 @@
         <v>158</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12521,7 +12531,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12536,13 +12546,13 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>77</v>
@@ -12556,10 +12566,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12585,10 +12595,10 @@
         <v>158</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12639,7 +12649,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12654,10 +12664,10 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
@@ -12674,10 +12684,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12703,14 +12713,14 @@
         <v>211</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12759,7 +12769,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12774,10 +12784,10 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>217</v>
@@ -12794,10 +12804,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12820,17 +12830,17 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12879,7 +12889,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12894,10 +12904,10 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12914,10 +12924,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13032,10 +13042,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13152,10 +13162,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13181,10 +13191,10 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13214,10 +13224,10 @@
         <v>173</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -13235,7 +13245,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13244,19 +13254,19 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>77</v>
@@ -13270,10 +13280,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13299,16 +13309,16 @@
         <v>158</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -13357,7 +13367,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13372,10 +13382,10 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>207</v>
@@ -13384,7 +13394,7 @@
         <v>77</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>77</v>
@@ -13392,10 +13402,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13421,16 +13431,16 @@
         <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -13458,10 +13468,10 @@
         <v>173</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -13479,7 +13489,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13494,13 +13504,13 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AN94" t="s" s="2">
         <v>77</v>
@@ -13514,10 +13524,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13540,16 +13550,16 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13599,7 +13609,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13634,10 +13644,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13663,10 +13673,10 @@
         <v>211</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13717,7 +13727,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13735,7 +13745,7 @@
         <v>130</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>217</v>
@@ -13752,10 +13762,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13778,17 +13788,17 @@
         <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13837,7 +13847,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13852,10 +13862,10 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
@@ -13872,10 +13882,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13898,17 +13908,17 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13957,7 +13967,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.23.0</t>
+    <t>0.24.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-23T15:31:48+00:00</t>
+    <t>2024-02-28T12:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.24.0</t>
+    <t>0.26.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-28T12:35:36+00:00</t>
+    <t>2024-03-08T13:22:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.26.0</t>
+    <t>0.27.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T13:22:05+00:00</t>
+    <t>2024-03-08T18:48:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.27.0</t>
+    <t>0.28.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-08T18:48:53+00:00</t>
+    <t>2024-03-09T10:17:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -863,9 +863,7 @@
     <t>1251: source value from INSTITUTION - NAME (#4-.01)</t>
   </si>
   <si>
-    <t>Dim.AutoDiscontinuedRule.InstitutionName
-Dim.Institution.InstitutionName
-Dim.RequestService.IFCRoutingInstitution</t>
+    <t>Dim.AutoDiscontinuedRule.InstitutionName,Dim.Institution.InstitutionName,Dim.RequestService.IFCRoutingInstitution</t>
   </si>
   <si>
     <t>Organization.alias</t>
@@ -1434,8 +1432,7 @@
     <t>1262: source value from INSTITUTION - STATE &gt; STATE - ABBREVIATION (#4-.02 &gt; 5-1)</t>
   </si>
   <si>
-    <t>Dim.State.StateAbbrev
-Dim.State.StateAbbrev</t>
+    <t>Dim.State.StateAbbrev,Dim.State.StateAbbrev</t>
   </si>
   <si>
     <t>Organization.address:physical.postalCode</t>
@@ -2225,7 +2222,7 @@
     <col min="39" max="39" width="218.1953125" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="43.94140625" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="109.390625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.28.0</t>
+    <t>0.30.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-09T10:17:01+00:00</t>
+    <t>2024-03-21T09:40:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -231,6 +231,12 @@
     <t>Constraint(s)</t>
   </si>
   <si>
+    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
+  </si>
+  <si>
+    <t>Mapping: Clinical Data Warehouse (CDW)</t>
+  </si>
+  <si>
     <t>Mapping: HL7 v2 Mapping</t>
   </si>
   <si>
@@ -241,12 +247,6 @@
   </si>
   <si>
     <t>Mapping: FiveWs Pattern Mapping</t>
-  </si>
-  <si>
-    <t>Mapping: Veterans Health Information Systems Technology and Architecture (VistA)</t>
-  </si>
-  <si>
-    <t>Mapping: Clinical Data Warehouse (CDW)</t>
   </si>
   <si>
     <t/>
@@ -654,6 +654,12 @@
     <t>Identifier.value</t>
   </si>
   <si>
+    <t>1252: source value from INSTITUTION - NPI (#4-41.99) case NPI slice</t>
+  </si>
+  <si>
+    <t>Dim.Institution.NPI</t>
+  </si>
+  <si>
     <t>CX.1 / EI.1</t>
   </si>
   <si>
@@ -661,12 +667,6 @@
   </si>
   <si>
     <t>./Value</t>
-  </si>
-  <si>
-    <t>1252: source value from INSTITUTION - NPI (#4-41.99) case NPI slice</t>
-  </si>
-  <si>
-    <t>Dim.Institution.NPI</t>
   </si>
   <si>
     <t>Organization.identifier.period</t>
@@ -776,6 +776,9 @@
     <t>true</t>
   </si>
   <si>
+    <t>1253: fixed value = true</t>
+  </si>
+  <si>
     <t>No equivalent in HL7 v2</t>
   </si>
   <si>
@@ -786,9 +789,6 @@
   </si>
   <si>
     <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>1253: fixed value = true</t>
   </si>
   <si>
     <t>Organization.type</t>
@@ -824,6 +824,9 @@
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
+    <t>1254: fixed value = #prov</t>
+  </si>
+  <si>
     <t>No equivalent in v2</t>
   </si>
   <si>
@@ -833,9 +836,6 @@
     <t>FiveWs.class</t>
   </si>
   <si>
-    <t>1254: fixed value = #prov</t>
-  </si>
-  <si>
     <t>Organization.name</t>
   </si>
   <si>
@@ -851,6 +851,12 @@
     <t>Need to use the name as the label of the organization.</t>
   </si>
   <si>
+    <t>1251: source value from INSTITUTION - NAME (#4-.01)</t>
+  </si>
+  <si>
+    <t>Dim.AutoDiscontinuedRule.InstitutionName,Dim.Institution.InstitutionName,Dim.RequestService.IFCRoutingInstitution</t>
+  </si>
+  <si>
     <t>XON.1</t>
   </si>
   <si>
@@ -858,12 +864,6 @@
   </si>
   <si>
     <t>.PreferredName/Name</t>
-  </si>
-  <si>
-    <t>1251: source value from INSTITUTION - NAME (#4-.01)</t>
-  </si>
-  <si>
-    <t>Dim.AutoDiscontinuedRule.InstitutionName,Dim.Institution.InstitutionName,Dim.RequestService.IFCRoutingInstitution</t>
   </si>
   <si>
     <t>Organization.alias</t>
@@ -1670,10 +1670,10 @@
     <t>HumanName.text</t>
   </si>
   <si>
+    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT - NAME (#4-4 &gt; 4.03-.01)</t>
+  </si>
+  <si>
     <t>implied by XPN.11</t>
-  </si>
-  <si>
-    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT - NAME (#4-4 &gt; 4.03-.01)</t>
   </si>
   <si>
     <t>Organization.contact.name.family</t>
@@ -2217,12 +2217,12 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="107.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="102.6171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="218.1953125" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="88.6875" customWidth="true" bestFit="true"/>
-    <col min="42" max="42" width="109.390625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="109.390625" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="218.1953125" customWidth="true" bestFit="true"/>
+    <col min="42" max="42" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2455,19 +2455,19 @@
         <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL2" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM2" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="AL2" t="s" s="2">
+      <c r="AN2" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="AM2" t="s" s="2">
+      <c r="AO2" t="s" s="2">
         <v>7</v>
-      </c>
-      <c r="AN2" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO2" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP2" t="s" s="2">
         <v>77</v>
@@ -3056,13 +3056,13 @@
         <v>77</v>
       </c>
       <c r="AL7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN7" t="s" s="2">
         <v>122</v>
-      </c>
-      <c r="AM7" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN7" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO7" t="s" s="2">
         <v>77</v>
@@ -3176,13 +3176,13 @@
         <v>77</v>
       </c>
       <c r="AL8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN8" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN8" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO8" t="s" s="2">
         <v>77</v>
@@ -3296,13 +3296,13 @@
         <v>77</v>
       </c>
       <c r="AL9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN9" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN9" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO9" t="s" s="2">
         <v>77</v>
@@ -3418,13 +3418,13 @@
         <v>77</v>
       </c>
       <c r="AL10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN10" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN10" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO10" t="s" s="2">
         <v>77</v>
@@ -3535,22 +3535,22 @@
         <v>99</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL11" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM11" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL11" t="s" s="2">
+      <c r="AN11" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM11" t="s" s="2">
+      <c r="AO11" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN11" t="s" s="2">
+      <c r="AP11" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AO11" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP11" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="12" hidden="true">
@@ -3656,13 +3656,13 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM12" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN12" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN12" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>77</v>
@@ -3776,13 +3776,13 @@
         <v>77</v>
       </c>
       <c r="AL13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>77</v>
@@ -3895,16 +3895,16 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM14" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="AL14" t="s" s="2">
+      <c r="AN14" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AM14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN14" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>77</v>
@@ -4017,16 +4017,16 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL15" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM15" t="s" s="2">
         <v>188</v>
       </c>
-      <c r="AL15" t="s" s="2">
+      <c r="AN15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="AM15" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN15" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>77</v>
@@ -4139,19 +4139,19 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM16" t="s" s="2">
         <v>196</v>
       </c>
-      <c r="AL16" t="s" s="2">
+      <c r="AN16" t="s" s="2">
         <v>197</v>
       </c>
-      <c r="AM16" t="s" s="2">
+      <c r="AO16" t="s" s="2">
         <v>198</v>
-      </c>
-      <c r="AN16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>77</v>
@@ -4268,13 +4268,13 @@
         <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>77</v>
+        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
-        <v>209</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" hidden="true">
@@ -4377,19 +4377,19 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL18" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM18" t="s" s="2">
         <v>215</v>
       </c>
-      <c r="AL18" t="s" s="2">
+      <c r="AN18" t="s" s="2">
         <v>216</v>
       </c>
-      <c r="AM18" t="s" s="2">
+      <c r="AO18" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>77</v>
@@ -4497,19 +4497,19 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL19" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="AL19" t="s" s="2">
+      <c r="AN19" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="AM19" t="s" s="2">
+      <c r="AO19" t="s" s="2">
         <v>226</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO19" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>77</v>
@@ -4619,22 +4619,22 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM20" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL20" t="s" s="2">
+      <c r="AN20" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM20" t="s" s="2">
+      <c r="AO20" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN20" t="s" s="2">
+      <c r="AP20" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP20" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
@@ -4741,22 +4741,22 @@
         <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>153</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AM21" t="s" s="2">
+      <c r="AO21" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="AN21" t="s" s="2">
+      <c r="AP21" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AP21" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4868,19 +4868,19 @@
         <v>243</v>
       </c>
       <c r="AL22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM22" t="s" s="2">
         <v>244</v>
       </c>
-      <c r="AM22" t="s" s="2">
+      <c r="AN22" t="s" s="2">
         <v>245</v>
       </c>
-      <c r="AN22" t="s" s="2">
+      <c r="AO22" t="s" s="2">
         <v>246</v>
       </c>
-      <c r="AO22" t="s" s="2">
+      <c r="AP22" t="s" s="2">
         <v>247</v>
-      </c>
-      <c r="AP22" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="23" hidden="true">
@@ -4990,19 +4990,19 @@
         <v>257</v>
       </c>
       <c r="AL23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM23" t="s" s="2">
         <v>258</v>
-      </c>
-      <c r="AM23" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>259</v>
       </c>
       <c r="AO23" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="AP23" t="s" s="2">
         <v>260</v>
-      </c>
-      <c r="AP23" t="s" s="2">
-        <v>77</v>
       </c>
     </row>
     <row r="24" hidden="true">
@@ -5118,13 +5118,13 @@
         <v>268</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="AP24" t="s" s="2">
-        <v>270</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" hidden="true">
@@ -5231,22 +5231,22 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>77</v>
+        <v>269</v>
       </c>
       <c r="AO25" t="s" s="2">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="AP25" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" hidden="true">
@@ -5353,19 +5353,19 @@
         <v>285</v>
       </c>
       <c r="AK26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL26" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM26" t="s" s="2">
         <v>286</v>
       </c>
-      <c r="AL26" t="s" s="2">
+      <c r="AN26" t="s" s="2">
         <v>287</v>
       </c>
-      <c r="AM26" t="s" s="2">
+      <c r="AO26" t="s" s="2">
         <v>288</v>
-      </c>
-      <c r="AN26" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO26" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>77</v>
@@ -5474,13 +5474,13 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN27" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM27" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>77</v>
@@ -5594,13 +5594,13 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM28" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN28" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM28" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN28" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>77</v>
@@ -5709,19 +5709,19 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL29" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM29" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL29" t="s" s="2">
+      <c r="AN29" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM29" t="s" s="2">
+      <c r="AO29" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN29" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO29" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>77</v>
@@ -5831,19 +5831,19 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL30" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM30" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL30" t="s" s="2">
+      <c r="AN30" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM30" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN30" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AO30" t="s" s="2">
-        <v>77</v>
+        <v>209</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>77</v>
@@ -5953,19 +5953,19 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL31" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM31" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL31" t="s" s="2">
+      <c r="AN31" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN31" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>77</v>
@@ -6073,16 +6073,16 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL32" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM32" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AL32" t="s" s="2">
+      <c r="AN32" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM32" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN32" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>77</v>
@@ -6191,19 +6191,19 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL33" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM33" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="AL33" t="s" s="2">
+      <c r="AN33" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM33" t="s" s="2">
+      <c r="AO33" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN33" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO33" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>77</v>
@@ -6311,19 +6311,19 @@
         <v>339</v>
       </c>
       <c r="AK34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL34" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM34" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL34" t="s" s="2">
+      <c r="AN34" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM34" t="s" s="2">
+      <c r="AO34" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN34" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO34" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>77</v>
@@ -6432,13 +6432,13 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM35" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM35" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>77</v>
@@ -6552,13 +6552,13 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM36" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN36" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM36" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN36" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>77</v>
@@ -6671,19 +6671,19 @@
         <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL37" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM37" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL37" t="s" s="2">
+      <c r="AN37" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN37" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO37" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>77</v>
@@ -6791,16 +6791,16 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL38" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM38" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AN38" t="s" s="2">
         <v>318</v>
-      </c>
-      <c r="AM38" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>77</v>
@@ -6913,16 +6913,16 @@
         <v>99</v>
       </c>
       <c r="AK39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL39" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM39" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL39" t="s" s="2">
+      <c r="AN39" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>77</v>
@@ -7031,19 +7031,19 @@
         <v>99</v>
       </c>
       <c r="AK40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL40" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM40" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL40" t="s" s="2">
+      <c r="AN40" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM40" t="s" s="2">
+      <c r="AO40" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO40" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>77</v>
@@ -7149,19 +7149,19 @@
         <v>99</v>
       </c>
       <c r="AK41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL41" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM41" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL41" t="s" s="2">
+      <c r="AN41" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AM41" t="s" s="2">
+      <c r="AO41" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO41" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>77</v>
@@ -7269,16 +7269,16 @@
         <v>99</v>
       </c>
       <c r="AK42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL42" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM42" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL42" t="s" s="2">
+      <c r="AN42" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>77</v>
@@ -7387,19 +7387,19 @@
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL43" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM43" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL43" t="s" s="2">
+      <c r="AN43" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AM43" t="s" s="2">
+      <c r="AO43" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO43" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>77</v>
@@ -7505,19 +7505,19 @@
         <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL44" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL44" t="s" s="2">
+      <c r="AN44" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM44" t="s" s="2">
+      <c r="AO44" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO44" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>77</v>
@@ -7625,19 +7625,19 @@
         <v>99</v>
       </c>
       <c r="AK45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL45" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM45" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL45" t="s" s="2">
+      <c r="AN45" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM45" t="s" s="2">
+      <c r="AO45" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO45" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>77</v>
@@ -7745,19 +7745,19 @@
         <v>99</v>
       </c>
       <c r="AK46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL46" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM46" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AL46" t="s" s="2">
+      <c r="AN46" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM46" t="s" s="2">
+      <c r="AO46" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>77</v>
@@ -7869,19 +7869,19 @@
         <v>339</v>
       </c>
       <c r="AK47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL47" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM47" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL47" t="s" s="2">
+      <c r="AN47" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM47" t="s" s="2">
+      <c r="AO47" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO47" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>77</v>
@@ -7990,13 +7990,13 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM48" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN48" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM48" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN48" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>77</v>
@@ -8110,13 +8110,13 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM49" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN49" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN49" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>77</v>
@@ -8229,19 +8229,19 @@
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM50" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL50" t="s" s="2">
+      <c r="AN50" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM50" t="s" s="2">
+      <c r="AO50" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN50" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO50" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>77</v>
@@ -8349,19 +8349,19 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="AL51" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM51" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL51" t="s" s="2">
+      <c r="AN51" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM51" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN51" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AO51" t="s" s="2">
-        <v>441</v>
+        <v>77</v>
       </c>
       <c r="AP51" t="s" s="2">
         <v>77</v>
@@ -8471,16 +8471,16 @@
         <v>99</v>
       </c>
       <c r="AK52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL52" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM52" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL52" t="s" s="2">
+      <c r="AN52" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AM52" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN52" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>77</v>
@@ -8589,22 +8589,22 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AL53" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="AM53" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL53" t="s" s="2">
+      <c r="AN53" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM53" t="s" s="2">
+      <c r="AO53" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="AN53" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO53" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="AP53" t="s" s="2">
-        <v>445</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" hidden="true">
@@ -8707,22 +8707,22 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AL54" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="AM54" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL54" t="s" s="2">
+      <c r="AN54" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AM54" t="s" s="2">
+      <c r="AO54" t="s" s="2">
         <v>391</v>
       </c>
-      <c r="AN54" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO54" t="s" s="2">
-        <v>447</v>
-      </c>
       <c r="AP54" t="s" s="2">
-        <v>448</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" hidden="true">
@@ -8827,22 +8827,22 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AL55" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="AM55" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL55" t="s" s="2">
+      <c r="AN55" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AM55" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN55" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AO55" t="s" s="2">
-        <v>450</v>
+        <v>77</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>451</v>
+        <v>77</v>
       </c>
     </row>
     <row r="56" hidden="true">
@@ -8945,22 +8945,22 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AL56" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="AM56" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL56" t="s" s="2">
+      <c r="AN56" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AM56" t="s" s="2">
+      <c r="AO56" t="s" s="2">
         <v>410</v>
       </c>
-      <c r="AN56" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO56" t="s" s="2">
-        <v>453</v>
-      </c>
       <c r="AP56" t="s" s="2">
-        <v>454</v>
+        <v>77</v>
       </c>
     </row>
     <row r="57" hidden="true">
@@ -9063,22 +9063,22 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="AL57" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AM57" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AN57" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM57" t="s" s="2">
+      <c r="AO57" t="s" s="2">
         <v>419</v>
       </c>
-      <c r="AN57" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO57" t="s" s="2">
-        <v>456</v>
-      </c>
       <c r="AP57" t="s" s="2">
-        <v>457</v>
+        <v>77</v>
       </c>
     </row>
     <row r="58" hidden="true">
@@ -9183,22 +9183,22 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
+        <v>459</v>
+      </c>
+      <c r="AL58" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM58" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL58" t="s" s="2">
+      <c r="AN58" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM58" t="s" s="2">
+      <c r="AO58" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AN58" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO58" t="s" s="2">
-        <v>459</v>
-      </c>
       <c r="AP58" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
     </row>
     <row r="59" hidden="true">
@@ -9303,19 +9303,19 @@
         <v>99</v>
       </c>
       <c r="AK59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL59" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM59" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AL59" t="s" s="2">
+      <c r="AN59" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM59" t="s" s="2">
+      <c r="AO59" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN59" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO59" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>77</v>
@@ -9427,19 +9427,19 @@
         <v>339</v>
       </c>
       <c r="AK60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM60" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="AL60" t="s" s="2">
+      <c r="AN60" t="s" s="2">
         <v>341</v>
       </c>
-      <c r="AM60" t="s" s="2">
+      <c r="AO60" t="s" s="2">
         <v>342</v>
-      </c>
-      <c r="AN60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO60" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>77</v>
@@ -9548,13 +9548,13 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM61" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN61" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM61" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN61" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>77</v>
@@ -9668,13 +9668,13 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM62" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN62" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM62" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN62" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>77</v>
@@ -9787,19 +9787,19 @@
         <v>99</v>
       </c>
       <c r="AK63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL63" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM63" t="s" s="2">
         <v>354</v>
       </c>
-      <c r="AL63" t="s" s="2">
+      <c r="AN63" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM63" t="s" s="2">
+      <c r="AO63" t="s" s="2">
         <v>355</v>
-      </c>
-      <c r="AN63" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO63" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>77</v>
@@ -9907,19 +9907,19 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AL64" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM64" t="s" s="2">
         <v>364</v>
       </c>
-      <c r="AL64" t="s" s="2">
+      <c r="AN64" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM64" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN64" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AO64" t="s" s="2">
-        <v>468</v>
+        <v>77</v>
       </c>
       <c r="AP64" t="s" s="2">
         <v>77</v>
@@ -10029,16 +10029,16 @@
         <v>99</v>
       </c>
       <c r="AK65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM65" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="AL65" t="s" s="2">
+      <c r="AN65" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="AM65" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN65" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -10147,19 +10147,19 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
+        <v>471</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM66" t="s" s="2">
         <v>380</v>
       </c>
-      <c r="AL66" t="s" s="2">
+      <c r="AN66" t="s" s="2">
         <v>381</v>
       </c>
-      <c r="AM66" t="s" s="2">
+      <c r="AO66" t="s" s="2">
         <v>382</v>
-      </c>
-      <c r="AN66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO66" t="s" s="2">
-        <v>471</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>77</v>
@@ -10265,19 +10265,19 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM67" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="AL67" t="s" s="2">
+      <c r="AN67" t="s" s="2">
         <v>390</v>
       </c>
-      <c r="AM67" t="s" s="2">
+      <c r="AO67" t="s" s="2">
         <v>391</v>
-      </c>
-      <c r="AN67" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO67" t="s" s="2">
-        <v>473</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>77</v>
@@ -10385,16 +10385,16 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM68" t="s" s="2">
         <v>399</v>
       </c>
-      <c r="AL68" t="s" s="2">
+      <c r="AN68" t="s" s="2">
         <v>400</v>
-      </c>
-      <c r="AM68" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN68" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>77</v>
@@ -10503,19 +10503,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM69" t="s" s="2">
         <v>408</v>
       </c>
-      <c r="AL69" t="s" s="2">
+      <c r="AN69" t="s" s="2">
         <v>409</v>
       </c>
-      <c r="AM69" t="s" s="2">
+      <c r="AO69" t="s" s="2">
         <v>410</v>
-      </c>
-      <c r="AN69" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO69" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10621,19 +10621,19 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
+        <v>478</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM70" t="s" s="2">
         <v>417</v>
       </c>
-      <c r="AL70" t="s" s="2">
+      <c r="AN70" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AM70" t="s" s="2">
+      <c r="AO70" t="s" s="2">
         <v>419</v>
-      </c>
-      <c r="AN70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO70" t="s" s="2">
-        <v>478</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>77</v>
@@ -10741,22 +10741,22 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
+        <v>480</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="AM71" t="s" s="2">
         <v>425</v>
       </c>
-      <c r="AL71" t="s" s="2">
+      <c r="AN71" t="s" s="2">
         <v>426</v>
       </c>
-      <c r="AM71" t="s" s="2">
+      <c r="AO71" t="s" s="2">
         <v>427</v>
       </c>
-      <c r="AN71" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO71" t="s" s="2">
-        <v>480</v>
-      </c>
       <c r="AP71" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
       </c>
     </row>
     <row r="72" hidden="true">
@@ -10861,19 +10861,19 @@
         <v>99</v>
       </c>
       <c r="AK72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM72" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="AL72" t="s" s="2">
+      <c r="AN72" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM72" t="s" s="2">
+      <c r="AO72" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN72" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO72" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>77</v>
@@ -10981,19 +10981,19 @@
         <v>99</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>243</v>
+        <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM73" t="s" s="2">
+        <v>244</v>
+      </c>
+      <c r="AN73" t="s" s="2">
         <v>486</v>
       </c>
-      <c r="AM73" t="s" s="2">
+      <c r="AO73" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AN73" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO73" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>77</v>
@@ -11106,13 +11106,13 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM74" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN74" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN74" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>77</v>
@@ -11224,13 +11224,13 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM75" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN75" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM75" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN75" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>77</v>
@@ -11344,13 +11344,13 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM76" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN76" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM76" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN76" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>77</v>
@@ -11466,13 +11466,13 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM77" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN77" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AM77" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN77" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO77" t="s" s="2">
         <v>77</v>
@@ -11586,13 +11586,13 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN78" t="s" s="2">
         <v>507</v>
-      </c>
-      <c r="AM78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN78" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11703,16 +11703,16 @@
         <v>99</v>
       </c>
       <c r="AK79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL79" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM79" t="s" s="2">
         <v>513</v>
       </c>
-      <c r="AL79" t="s" s="2">
+      <c r="AN79" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="AM79" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN79" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>77</v>
@@ -11824,13 +11824,13 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM80" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN80" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM80" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN80" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>77</v>
@@ -11944,13 +11944,13 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM81" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN81" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM81" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN81" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>77</v>
@@ -12063,19 +12063,19 @@
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL82" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM82" t="s" s="2">
         <v>525</v>
       </c>
-      <c r="AL82" t="s" s="2">
+      <c r="AN82" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM82" t="s" s="2">
+      <c r="AO82" t="s" s="2">
         <v>526</v>
-      </c>
-      <c r="AN82" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO82" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>77</v>
@@ -12188,16 +12188,16 @@
         <v>532</v>
       </c>
       <c r="AL83" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM83" t="s" s="2">
+        <v>533</v>
+      </c>
+      <c r="AN83" t="s" s="2">
         <v>373</v>
       </c>
-      <c r="AM83" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN83" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AO83" t="s" s="2">
-        <v>533</v>
+        <v>77</v>
       </c>
       <c r="AP83" t="s" s="2">
         <v>77</v>
@@ -12305,19 +12305,19 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL84" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM84" t="s" s="2">
         <v>540</v>
       </c>
-      <c r="AL84" t="s" s="2">
+      <c r="AN84" t="s" s="2">
         <v>541</v>
       </c>
-      <c r="AM84" t="s" s="2">
+      <c r="AO84" t="s" s="2">
         <v>542</v>
-      </c>
-      <c r="AN84" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO84" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>77</v>
@@ -12425,19 +12425,19 @@
         <v>99</v>
       </c>
       <c r="AK85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL85" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM85" t="s" s="2">
         <v>549</v>
       </c>
-      <c r="AL85" t="s" s="2">
+      <c r="AN85" t="s" s="2">
         <v>550</v>
       </c>
-      <c r="AM85" t="s" s="2">
+      <c r="AO85" t="s" s="2">
         <v>551</v>
-      </c>
-      <c r="AN85" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO85" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>77</v>
@@ -12543,19 +12543,19 @@
         <v>99</v>
       </c>
       <c r="AK86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL86" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM86" t="s" s="2">
         <v>556</v>
       </c>
-      <c r="AL86" t="s" s="2">
+      <c r="AN86" t="s" s="2">
         <v>557</v>
       </c>
-      <c r="AM86" t="s" s="2">
+      <c r="AO86" t="s" s="2">
         <v>558</v>
-      </c>
-      <c r="AN86" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO86" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>77</v>
@@ -12661,16 +12661,16 @@
         <v>99</v>
       </c>
       <c r="AK87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL87" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM87" t="s" s="2">
         <v>563</v>
       </c>
-      <c r="AL87" t="s" s="2">
+      <c r="AN87" t="s" s="2">
         <v>564</v>
-      </c>
-      <c r="AM87" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN87" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>77</v>
@@ -12781,19 +12781,19 @@
         <v>99</v>
       </c>
       <c r="AK88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL88" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM88" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="AL88" t="s" s="2">
+      <c r="AN88" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM88" t="s" s="2">
+      <c r="AO88" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN88" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO88" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>77</v>
@@ -12901,16 +12901,16 @@
         <v>99</v>
       </c>
       <c r="AK89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL89" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM89" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AL89" t="s" s="2">
+      <c r="AN89" t="s" s="2">
         <v>576</v>
-      </c>
-      <c r="AM89" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN89" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>77</v>
@@ -13022,13 +13022,13 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM90" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN90" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM90" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN90" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>77</v>
@@ -13142,13 +13142,13 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM91" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN91" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM91" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN91" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>77</v>
@@ -13257,19 +13257,19 @@
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL92" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM92" t="s" s="2">
         <v>298</v>
       </c>
-      <c r="AL92" t="s" s="2">
+      <c r="AN92" t="s" s="2">
         <v>299</v>
       </c>
-      <c r="AM92" t="s" s="2">
+      <c r="AO92" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="AN92" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO92" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>77</v>
@@ -13379,19 +13379,19 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
+        <v>581</v>
+      </c>
+      <c r="AL93" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM93" t="s" s="2">
         <v>307</v>
       </c>
-      <c r="AL93" t="s" s="2">
+      <c r="AN93" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AM93" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="AN93" t="s" s="2">
-        <v>77</v>
-      </c>
       <c r="AO93" t="s" s="2">
-        <v>581</v>
+        <v>209</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>77</v>
@@ -13501,19 +13501,19 @@
         <v>99</v>
       </c>
       <c r="AK94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL94" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM94" t="s" s="2">
         <v>317</v>
       </c>
-      <c r="AL94" t="s" s="2">
+      <c r="AN94" t="s" s="2">
         <v>318</v>
       </c>
-      <c r="AM94" t="s" s="2">
+      <c r="AO94" t="s" s="2">
         <v>319</v>
-      </c>
-      <c r="AN94" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO94" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>77</v>
@@ -13621,16 +13621,16 @@
         <v>99</v>
       </c>
       <c r="AK95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL95" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM95" t="s" s="2">
         <v>162</v>
       </c>
-      <c r="AL95" t="s" s="2">
+      <c r="AN95" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM95" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN95" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>77</v>
@@ -13739,19 +13739,19 @@
         <v>99</v>
       </c>
       <c r="AK96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL96" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM96" t="s" s="2">
         <v>130</v>
       </c>
-      <c r="AL96" t="s" s="2">
+      <c r="AN96" t="s" s="2">
         <v>330</v>
       </c>
-      <c r="AM96" t="s" s="2">
+      <c r="AO96" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="AN96" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AO96" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>77</v>
@@ -13859,16 +13859,16 @@
         <v>99</v>
       </c>
       <c r="AK97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL97" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM97" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="AL97" t="s" s="2">
+      <c r="AN97" t="s" s="2">
         <v>590</v>
-      </c>
-      <c r="AM97" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN97" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>77</v>
@@ -13982,13 +13982,13 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM98" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN98" t="s" s="2">
         <v>162</v>
-      </c>
-      <c r="AM98" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN98" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.30.0</t>
+    <t>0.32.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-21T09:40:56+00:00</t>
+    <t>2024-03-22T16:04:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="605">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.32.0</t>
+    <t>0.34.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-22T16:04:14+00:00</t>
+    <t>2024-03-29T18:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -505,221 +505,6 @@
   </si>
   <si>
     <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>Organization.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
-</t>
-  </si>
-  <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
-</t>
-  </si>
-  <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>./IdentifierType</t>
-  </si>
-  <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>1252: source value from INSTITUTION - NPI (#4-41.99) case NPI slice</t>
-  </si>
-  <si>
-    <t>Dim.Institution.NPI</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>./Value</t>
-  </si>
-  <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
   </si>
   <si>
     <t>Organization.identifier:NPI</t>
@@ -734,6 +519,245 @@
     <t>&lt;valueIdentifier xmlns="http://hl7.org/fhir"&gt;
   &lt;system value="http://hl7.org/fhir/sid/us-npi"/&gt;
 &lt;/valueIdentifier&gt;</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.id</t>
+  </si>
+  <si>
+    <t>Organization.identifier.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.use</t>
+  </si>
+  <si>
+    <t>Organization.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.type</t>
+  </si>
+  <si>
+    <t>Organization.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>extensible</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>CX.5</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.system</t>
+  </si>
+  <si>
+    <t>Organization.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>CX.4 / EI-2-4</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>./IdentifierType</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.value</t>
+  </si>
+  <si>
+    <t>Organization.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>1252: source value from INSTITUTION - NPI (#4-41.99)</t>
+  </si>
+  <si>
+    <t>Dim.Institution.NPI</t>
+  </si>
+  <si>
+    <t>CX.1 / EI.1</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>./Value</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.period</t>
+  </si>
+  <si>
+    <t>Organization.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>CX.7 + CX.8</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>./StartDate and ./EndDate</t>
+  </si>
+  <si>
+    <t>Organization.identifier:NPI.assigner</t>
+  </si>
+  <si>
+    <t>Organization.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
+    <t>./IdentifierIssuingAuthority</t>
   </si>
   <si>
     <t>Organization.identifier:CLIA</t>
@@ -913,6 +937,9 @@
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 org-3:The telecom of an organization can never be of use 'home' {where(use = 'home').empty()}</t>
+  </si>
+  <si>
+    <t>1786: target not supported</t>
   </si>
   <si>
     <t>ORC-22?</t>
@@ -3558,9 +3585,11 @@
         <v>157</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>157</v>
-      </c>
-      <c r="C12" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C12" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="D12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3572,25 +3601,27 @@
         <v>87</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J12" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="L12" t="s" s="2">
         <v>159</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" t="s" s="2">
+        <v>149</v>
+      </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
       </c>
@@ -3599,7 +3630,7 @@
         <v>77</v>
       </c>
       <c r="S12" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="T12" t="s" s="2">
         <v>77</v>
@@ -3638,19 +3669,19 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>161</v>
+        <v>144</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
         <v>77</v>
@@ -3659,35 +3690,35 @@
         <v>77</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="AO12" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AP12" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>77</v>
@@ -3699,17 +3730,15 @@
         <v>77</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>133</v>
+        <v>163</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>134</v>
+        <v>164</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>136</v>
-      </c>
+        <v>165</v>
+      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -3746,43 +3775,43 @@
         <v>77</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="AC13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF13" t="s" s="2">
         <v>166</v>
       </c>
-      <c r="AD13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE13" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="AF13" t="s" s="2">
+      <c r="AG13" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH13" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM13" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN13" t="s" s="2">
         <v>167</v>
-      </c>
-      <c r="AG13" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH13" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ13" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AM13" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AO13" t="s" s="2">
         <v>77</v>
@@ -3796,43 +3825,41 @@
         <v>168</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>107</v>
+        <v>133</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>169</v>
+        <v>134</v>
       </c>
       <c r="M14" t="s" s="2">
         <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="O14" t="s" s="2">
-        <v>172</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3856,43 +3883,43 @@
         <v>77</v>
       </c>
       <c r="X14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB14" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="AC14" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="AD14" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE14" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AF14" t="s" s="2">
         <v>173</v>
       </c>
-      <c r="Y14" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="Z14" t="s" s="2">
-        <v>175</v>
-      </c>
-      <c r="AA14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE14" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF14" t="s" s="2">
-        <v>176</v>
-      </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>77</v>
@@ -3901,10 +3928,10 @@
         <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>77</v>
@@ -3915,10 +3942,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3935,25 +3962,25 @@
         <v>77</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M15" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="O15" t="s" s="2">
         <v>179</v>
-      </c>
-      <c r="L15" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>181</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>182</v>
-      </c>
-      <c r="O15" t="s" s="2">
-        <v>183</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
@@ -3978,13 +4005,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -4002,7 +4029,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -4023,10 +4050,10 @@
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>188</v>
+        <v>130</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>77</v>
@@ -4037,10 +4064,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -4054,7 +4081,7 @@
         <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
@@ -4063,19 +4090,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>101</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M16" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="N16" t="s" s="2">
         <v>190</v>
       </c>
-      <c r="M16" t="s" s="2">
+      <c r="O16" t="s" s="2">
         <v>191</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="O16" t="s" s="2">
-        <v>193</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -4088,25 +4115,25 @@
         <v>77</v>
       </c>
       <c r="T16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W16" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="Z16" t="s" s="2">
         <v>194</v>
-      </c>
-      <c r="U16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y16" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z16" t="s" s="2">
-        <v>77</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -4148,10 +4175,10 @@
         <v>196</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="AO16" t="s" s="2">
-        <v>198</v>
+        <v>77</v>
       </c>
       <c r="AP16" t="s" s="2">
         <v>77</v>
@@ -4159,10 +4186,10 @@
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4176,7 +4203,7 @@
         <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>77</v>
@@ -4185,18 +4212,20 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>158</v>
+        <v>101</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>199</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>200</v>
       </c>
-      <c r="M17" t="s" s="2">
+      <c r="N17" t="s" s="2">
         <v>201</v>
       </c>
-      <c r="N17" t="s" s="2">
+      <c r="O17" t="s" s="2">
         <v>202</v>
       </c>
-      <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
       </c>
@@ -4259,19 +4288,19 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL17" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AM17" t="s" s="2">
         <v>205</v>
       </c>
-      <c r="AL17" t="s" s="2">
+      <c r="AN17" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="AM17" t="s" s="2">
+      <c r="AO17" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="AN17" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="AO17" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>77</v>
@@ -4279,10 +4308,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4305,15 +4334,17 @@
         <v>88</v>
       </c>
       <c r="K18" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="M18" t="s" s="2">
         <v>211</v>
       </c>
-      <c r="L18" t="s" s="2">
+      <c r="N18" t="s" s="2">
         <v>212</v>
       </c>
-      <c r="M18" t="s" s="2">
-        <v>213</v>
-      </c>
-      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>77</v>
@@ -4326,7 +4357,7 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>77</v>
+        <v>213</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>77</v>
@@ -4377,19 +4408,19 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>77</v>
+        <v>216</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>77</v>
@@ -4397,10 +4428,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4423,17 +4454,15 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>221</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>222</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -4482,7 +4511,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4503,13 +4532,13 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>77</v>
@@ -4517,14 +4546,12 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>228</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4536,7 +4563,7 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
@@ -4545,18 +4572,18 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>145</v>
+        <v>231</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" t="s" s="2">
-        <v>149</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>234</v>
+      </c>
+      <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -4565,7 +4592,7 @@
         <v>77</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>77</v>
@@ -4604,16 +4631,16 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>144</v>
+        <v>235</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
@@ -4625,27 +4652,27 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>153</v>
+        <v>236</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>154</v>
+        <v>237</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>155</v>
+        <v>238</v>
       </c>
       <c r="AP20" t="s" s="2">
-        <v>156</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4670,7 +4697,7 @@
         <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>147</v>
@@ -4687,7 +4714,7 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>77</v>
@@ -4761,10 +4788,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4787,31 +4814,31 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q22" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="R22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="T22" t="s" s="2">
         <v>77</v>
@@ -4850,7 +4877,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4865,30 +4892,30 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>247</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4911,19 +4938,19 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4933,7 +4960,7 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>77</v>
@@ -4948,31 +4975,31 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="Z23" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="AA23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE23" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF23" t="s" s="2">
         <v>256</v>
-      </c>
-      <c r="AA23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE23" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF23" t="s" s="2">
-        <v>248</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4987,30 +5014,30 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="AO23" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>260</v>
+        <v>268</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5033,19 +5060,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5094,7 +5121,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5109,19 +5136,19 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>77</v>
@@ -5129,10 +5156,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5155,19 +5182,19 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5216,7 +5243,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5231,16 +5258,16 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="AL25" t="s" s="2">
+        <v>285</v>
+      </c>
+      <c r="AM25" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>277</v>
-      </c>
-      <c r="AM25" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>269</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>77</v>
@@ -5251,10 +5278,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5277,19 +5304,19 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5338,7 +5365,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5347,25 +5374,25 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>77</v>
+        <v>294</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>77</v>
@@ -5373,10 +5400,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5399,13 +5426,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -5456,7 +5483,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5480,7 +5507,7 @@
         <v>77</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>77</v>
@@ -5491,10 +5518,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5523,7 +5550,7 @@
         <v>134</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N28" t="s" s="2">
         <v>136</v>
@@ -5564,10 +5591,10 @@
         <v>77</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>77</v>
@@ -5576,7 +5603,7 @@
         <v>151</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5600,7 +5627,7 @@
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>77</v>
@@ -5611,10 +5638,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5640,10 +5667,10 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5670,13 +5697,13 @@
         <v>77</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5694,7 +5721,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5703,7 +5730,7 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -5715,13 +5742,13 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>77</v>
@@ -5729,10 +5756,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5755,19 +5782,19 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5816,7 +5843,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5837,13 +5864,13 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>77</v>
@@ -5851,10 +5878,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5880,16 +5907,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5914,13 +5941,13 @@
         <v>77</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5938,7 +5965,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5959,13 +5986,13 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>77</v>
@@ -5973,10 +6000,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5999,16 +6026,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6058,7 +6085,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6079,10 +6106,10 @@
         <v>77</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO32" t="s" s="2">
         <v>77</v>
@@ -6093,10 +6120,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6119,13 +6146,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6176,7 +6203,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6200,10 +6227,10 @@
         <v>130</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>77</v>
@@ -6211,10 +6238,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6237,19 +6264,19 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6286,7 +6313,7 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -6296,7 +6323,7 @@
         <v>151</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6305,10 +6332,10 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
@@ -6317,13 +6344,13 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>77</v>
@@ -6331,10 +6358,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6357,13 +6384,13 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -6414,7 +6441,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -6438,7 +6465,7 @@
         <v>77</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>77</v>
@@ -6449,10 +6476,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6481,7 +6508,7 @@
         <v>134</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N36" t="s" s="2">
         <v>136</v>
@@ -6522,10 +6549,10 @@
         <v>77</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>77</v>
@@ -6534,7 +6561,7 @@
         <v>151</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -6558,7 +6585,7 @@
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>77</v>
@@ -6569,10 +6596,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6598,16 +6625,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6620,7 +6647,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6632,13 +6659,13 @@
         <v>77</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6656,7 +6683,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6677,13 +6704,13 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>77</v>
@@ -6691,10 +6718,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6720,13 +6747,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6740,7 +6767,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6752,13 +6779,13 @@
         <v>77</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6776,7 +6803,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6797,10 +6824,10 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>77</v>
@@ -6811,10 +6838,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6837,19 +6864,19 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6862,7 +6889,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6898,7 +6925,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6919,10 +6946,10 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>77</v>
@@ -6933,10 +6960,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6947,7 +6974,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -6959,13 +6986,13 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6980,7 +7007,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -7016,7 +7043,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7037,13 +7064,13 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>77</v>
@@ -7051,14 +7078,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7077,13 +7104,13 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7098,7 +7125,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -7134,7 +7161,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7155,13 +7182,13 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>77</v>
@@ -7169,14 +7196,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7195,16 +7222,16 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7218,7 +7245,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -7254,7 +7281,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7275,10 +7302,10 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>77</v>
@@ -7289,14 +7316,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7315,13 +7342,13 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7348,13 +7375,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7372,7 +7399,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7393,13 +7420,13 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>77</v>
@@ -7407,14 +7434,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7433,13 +7460,13 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7454,7 +7481,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7490,7 +7517,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7511,13 +7538,13 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>77</v>
@@ -7525,10 +7552,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7551,16 +7578,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7610,7 +7637,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7631,13 +7658,13 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>77</v>
@@ -7645,10 +7672,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7671,17 +7698,17 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7694,7 +7721,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7730,7 +7757,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7751,13 +7778,13 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>77</v>
@@ -7765,13 +7792,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7793,19 +7820,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7854,7 +7881,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7863,10 +7890,10 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7875,13 +7902,13 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>77</v>
@@ -7889,10 +7916,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7915,13 +7942,13 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7972,7 +7999,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7996,7 +8023,7 @@
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>77</v>
@@ -8007,10 +8034,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8039,7 +8066,7 @@
         <v>134</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>136</v>
@@ -8080,10 +8107,10 @@
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
@@ -8092,7 +8119,7 @@
         <v>151</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -8116,7 +8143,7 @@
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>77</v>
@@ -8127,10 +8154,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8156,16 +8183,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8178,7 +8205,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -8190,13 +8217,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -8214,7 +8241,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8235,13 +8262,13 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>77</v>
@@ -8249,10 +8276,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8278,13 +8305,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8295,10 +8322,10 @@
         <v>77</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -8310,13 +8337,13 @@
         <v>77</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8334,7 +8361,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8349,16 +8376,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>77</v>
@@ -8369,10 +8396,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8395,19 +8422,19 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8420,7 +8447,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -8456,7 +8483,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8477,10 +8504,10 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>77</v>
@@ -8491,10 +8518,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8505,7 +8532,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>88</v>
@@ -8517,13 +8544,13 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8538,7 +8565,7 @@
         <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>77</v>
@@ -8574,7 +8601,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8589,19 +8616,19 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>77</v>
@@ -8609,14 +8636,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8635,13 +8662,13 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8656,7 +8683,7 @@
         <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8692,7 +8719,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8707,19 +8734,19 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>77</v>
@@ -8727,14 +8754,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8753,16 +8780,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8776,7 +8803,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8812,7 +8839,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8827,16 +8854,16 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>451</v>
+        <v>460</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>77</v>
@@ -8847,14 +8874,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>452</v>
+        <v>461</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8873,13 +8900,13 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8906,13 +8933,13 @@
         <v>77</v>
       </c>
       <c r="X56" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8930,7 +8957,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8945,19 +8972,19 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>453</v>
+        <v>462</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>454</v>
+        <v>463</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>77</v>
@@ -8965,14 +8992,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>455</v>
+        <v>464</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8991,13 +9018,13 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9012,7 +9039,7 @@
         <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>77</v>
@@ -9048,7 +9075,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9063,19 +9090,19 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>456</v>
+        <v>465</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>457</v>
+        <v>466</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>77</v>
@@ -9083,10 +9110,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>458</v>
+        <v>467</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9109,16 +9136,16 @@
         <v>88</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9168,7 +9195,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9183,19 +9210,19 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>459</v>
+        <v>468</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>77</v>
@@ -9203,10 +9230,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>461</v>
+        <v>470</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9229,17 +9256,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9252,7 +9279,7 @@
         <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>77</v>
@@ -9288,7 +9315,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9309,13 +9336,13 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>77</v>
@@ -9323,13 +9350,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>462</v>
+        <v>471</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9351,19 +9378,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9412,7 +9439,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9421,10 +9448,10 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -9433,13 +9460,13 @@
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>77</v>
@@ -9447,10 +9474,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>464</v>
+        <v>473</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9473,13 +9500,13 @@
         <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -9530,7 +9557,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -9554,7 +9581,7 @@
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>77</v>
@@ -9565,10 +9592,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>465</v>
+        <v>474</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9597,7 +9624,7 @@
         <v>134</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>136</v>
@@ -9638,10 +9665,10 @@
         <v>77</v>
       </c>
       <c r="AB62" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>77</v>
@@ -9650,7 +9677,7 @@
         <v>151</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -9674,7 +9701,7 @@
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>77</v>
@@ -9685,10 +9712,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>466</v>
+        <v>475</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9714,16 +9741,16 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9736,7 +9763,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9748,13 +9775,13 @@
         <v>77</v>
       </c>
       <c r="X63" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9772,7 +9799,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9793,13 +9820,13 @@
         <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>77</v>
@@ -9807,10 +9834,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>467</v>
+        <v>476</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9836,13 +9863,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9853,10 +9880,10 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>463</v>
+        <v>472</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9868,13 +9895,13 @@
         <v>77</v>
       </c>
       <c r="X64" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9892,7 +9919,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9907,16 +9934,16 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>468</v>
+        <v>477</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>77</v>
@@ -9927,10 +9954,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>469</v>
+        <v>478</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9953,19 +9980,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9978,7 +10005,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -10014,7 +10041,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10035,10 +10062,10 @@
         <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -10049,10 +10076,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>470</v>
+        <v>479</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10063,7 +10090,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>88</v>
@@ -10075,13 +10102,13 @@
         <v>88</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10096,7 +10123,7 @@
         <v>77</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>77</v>
@@ -10132,7 +10159,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10147,19 +10174,19 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>471</v>
+        <v>480</v>
       </c>
       <c r="AL66" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>77</v>
@@ -10167,14 +10194,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>472</v>
+        <v>481</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10193,13 +10220,13 @@
         <v>88</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10214,7 +10241,7 @@
         <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>77</v>
@@ -10250,7 +10277,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10265,19 +10292,19 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>473</v>
+        <v>482</v>
       </c>
       <c r="AL67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>77</v>
@@ -10285,14 +10312,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>474</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10311,16 +10338,16 @@
         <v>88</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10334,7 +10361,7 @@
         <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>77</v>
@@ -10370,7 +10397,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10391,10 +10418,10 @@
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>77</v>
@@ -10405,14 +10432,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>475</v>
+        <v>484</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10431,13 +10458,13 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10464,13 +10491,13 @@
         <v>77</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10488,7 +10515,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10503,19 +10530,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>476</v>
+        <v>485</v>
       </c>
       <c r="AL69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10523,14 +10550,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>477</v>
+        <v>486</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10549,13 +10576,13 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10570,7 +10597,7 @@
         <v>77</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>77</v>
@@ -10606,7 +10633,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10621,19 +10648,19 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>478</v>
+        <v>487</v>
       </c>
       <c r="AL70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>77</v>
@@ -10641,10 +10668,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>479</v>
+        <v>488</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10667,16 +10694,16 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10726,7 +10753,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10741,19 +10768,19 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>480</v>
+        <v>489</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>460</v>
+        <v>469</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>77</v>
@@ -10761,10 +10788,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>481</v>
+        <v>490</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10787,17 +10814,17 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10810,7 +10837,7 @@
         <v>77</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>77</v>
@@ -10846,7 +10873,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>433</v>
+        <v>442</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10867,13 +10894,13 @@
         <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>77</v>
@@ -10881,10 +10908,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10907,17 +10934,17 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>483</v>
+        <v>492</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>484</v>
+        <v>493</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>485</v>
+        <v>494</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10966,7 +10993,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>482</v>
+        <v>491</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10987,13 +11014,13 @@
         <v>77</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>486</v>
+        <v>495</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AP73" t="s" s="2">
         <v>77</v>
@@ -11001,10 +11028,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11027,19 +11054,19 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>488</v>
+        <v>497</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>489</v>
+        <v>498</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>490</v>
+        <v>499</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>491</v>
+        <v>500</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>492</v>
+        <v>501</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11088,7 +11115,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>487</v>
+        <v>496</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11112,7 +11139,7 @@
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>493</v>
+        <v>502</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>77</v>
@@ -11123,10 +11150,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>494</v>
+        <v>503</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11149,13 +11176,13 @@
         <v>77</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11206,7 +11233,7 @@
         <v>77</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -11230,7 +11257,7 @@
         <v>77</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>77</v>
@@ -11241,10 +11268,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>495</v>
+        <v>504</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11273,7 +11300,7 @@
         <v>134</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N76" t="s" s="2">
         <v>136</v>
@@ -11326,7 +11353,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11350,7 +11377,7 @@
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO76" t="s" s="2">
         <v>77</v>
@@ -11361,14 +11388,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>496</v>
+        <v>505</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>497</v>
+        <v>506</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11390,10 +11417,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>498</v>
+        <v>507</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>499</v>
+        <v>508</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>136</v>
@@ -11448,7 +11475,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>500</v>
+        <v>509</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11483,10 +11510,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11509,17 +11536,17 @@
         <v>77</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>502</v>
+        <v>511</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>503</v>
+        <v>512</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11544,13 +11571,13 @@
         <v>77</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>505</v>
+        <v>514</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>506</v>
+        <v>515</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11568,7 +11595,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>501</v>
+        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11592,7 +11619,7 @@
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>507</v>
+        <v>516</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11603,10 +11630,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11629,17 +11656,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>509</v>
+        <v>518</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>510</v>
+        <v>519</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>511</v>
+        <v>520</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>512</v>
+        <v>521</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11688,7 +11715,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>508</v>
+        <v>517</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11709,10 +11736,10 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>513</v>
+        <v>522</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>514</v>
+        <v>523</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>77</v>
@@ -11723,10 +11750,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>515</v>
+        <v>524</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11749,13 +11776,13 @@
         <v>77</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11806,7 +11833,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11830,7 +11857,7 @@
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO80" t="s" s="2">
         <v>77</v>
@@ -11841,10 +11868,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>516</v>
+        <v>525</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11873,7 +11900,7 @@
         <v>134</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N81" t="s" s="2">
         <v>136</v>
@@ -11914,10 +11941,10 @@
         <v>77</v>
       </c>
       <c r="AB81" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC81" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD81" t="s" s="2">
         <v>77</v>
@@ -11926,7 +11953,7 @@
         <v>151</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11950,7 +11977,7 @@
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO81" t="s" s="2">
         <v>77</v>
@@ -11961,10 +11988,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>517</v>
+        <v>526</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11990,16 +12017,16 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>518</v>
+        <v>527</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>519</v>
+        <v>528</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>520</v>
+        <v>529</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>521</v>
+        <v>530</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12024,13 +12051,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>522</v>
+        <v>531</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>523</v>
+        <v>532</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12048,7 +12075,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>524</v>
+        <v>533</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12069,13 +12096,13 @@
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>526</v>
+        <v>535</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>77</v>
@@ -12083,10 +12110,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12109,19 +12136,19 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>528</v>
+        <v>537</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>529</v>
+        <v>538</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>530</v>
+        <v>539</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12170,7 +12197,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>531</v>
+        <v>540</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12185,16 +12212,16 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>532</v>
+        <v>541</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>533</v>
+        <v>542</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>77</v>
@@ -12205,14 +12232,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>534</v>
+        <v>543</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>535</v>
+        <v>544</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12231,16 +12258,16 @@
         <v>88</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>537</v>
+        <v>546</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12290,7 +12317,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>539</v>
+        <v>548</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12311,13 +12338,13 @@
         <v>77</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>540</v>
+        <v>549</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>541</v>
+        <v>550</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>542</v>
+        <v>551</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>77</v>
@@ -12325,14 +12352,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>543</v>
+        <v>552</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>544</v>
+        <v>553</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12351,16 +12378,16 @@
         <v>88</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>545</v>
+        <v>554</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>546</v>
+        <v>555</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>547</v>
+        <v>556</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12410,7 +12437,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>548</v>
+        <v>557</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12431,13 +12458,13 @@
         <v>77</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>549</v>
+        <v>558</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>550</v>
+        <v>559</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>551</v>
+        <v>560</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>77</v>
@@ -12445,10 +12472,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>552</v>
+        <v>561</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12471,13 +12498,13 @@
         <v>88</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>553</v>
+        <v>562</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>554</v>
+        <v>563</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12528,7 +12555,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>555</v>
+        <v>564</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12549,13 +12576,13 @@
         <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>556</v>
+        <v>565</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>557</v>
+        <v>566</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>558</v>
+        <v>567</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>77</v>
@@ -12563,10 +12590,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>559</v>
+        <v>568</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12589,13 +12616,13 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>560</v>
+        <v>569</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>561</v>
+        <v>570</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12646,7 +12673,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>562</v>
+        <v>571</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12667,10 +12694,10 @@
         <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>563</v>
+        <v>572</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>564</v>
+        <v>573</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>77</v>
@@ -12681,10 +12708,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>565</v>
+        <v>574</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12707,17 +12734,17 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>566</v>
+        <v>575</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>567</v>
+        <v>576</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>568</v>
+        <v>577</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12766,7 +12793,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>569</v>
+        <v>578</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12787,13 +12814,13 @@
         <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>570</v>
+        <v>579</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>77</v>
@@ -12801,10 +12828,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12827,17 +12854,17 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>572</v>
+        <v>581</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>573</v>
+        <v>582</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>574</v>
+        <v>583</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12886,7 +12913,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>571</v>
+        <v>580</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12907,10 +12934,10 @@
         <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>575</v>
+        <v>584</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>576</v>
+        <v>585</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>77</v>
@@ -12921,10 +12948,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>577</v>
+        <v>586</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12947,13 +12974,13 @@
         <v>77</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -13004,7 +13031,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -13028,7 +13055,7 @@
         <v>77</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO90" t="s" s="2">
         <v>77</v>
@@ -13039,10 +13066,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>578</v>
+        <v>587</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13071,7 +13098,7 @@
         <v>134</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="N91" t="s" s="2">
         <v>136</v>
@@ -13112,10 +13139,10 @@
         <v>77</v>
       </c>
       <c r="AB91" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="AC91" t="s" s="2">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="AD91" t="s" s="2">
         <v>77</v>
@@ -13124,7 +13151,7 @@
         <v>151</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -13148,7 +13175,7 @@
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO91" t="s" s="2">
         <v>77</v>
@@ -13159,10 +13186,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>579</v>
+        <v>588</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13188,10 +13215,10 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13218,13 +13245,13 @@
         <v>77</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>294</v>
+        <v>303</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -13242,7 +13269,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13251,7 +13278,7 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
@@ -13263,13 +13290,13 @@
         <v>77</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>77</v>
@@ -13277,10 +13304,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>580</v>
+        <v>589</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13303,19 +13330,19 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -13364,7 +13391,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13379,19 +13406,19 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>581</v>
+        <v>590</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>77</v>
@@ -13399,10 +13426,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>582</v>
+        <v>591</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13428,16 +13455,16 @@
         <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -13462,13 +13489,13 @@
         <v>77</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -13486,7 +13513,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13507,13 +13534,13 @@
         <v>77</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>77</v>
@@ -13521,10 +13548,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>583</v>
+        <v>592</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13547,16 +13574,16 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13606,7 +13633,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13627,10 +13654,10 @@
         <v>77</v>
       </c>
       <c r="AM95" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO95" t="s" s="2">
         <v>77</v>
@@ -13641,10 +13668,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>584</v>
+        <v>593</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13667,13 +13694,13 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13724,7 +13751,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13748,10 +13775,10 @@
         <v>130</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>77</v>
@@ -13759,10 +13786,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13785,17 +13812,17 @@
         <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>586</v>
+        <v>595</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>587</v>
+        <v>596</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>588</v>
+        <v>597</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13844,7 +13871,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>585</v>
+        <v>594</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13865,10 +13892,10 @@
         <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>589</v>
+        <v>598</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>590</v>
+        <v>599</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>77</v>
@@ -13879,10 +13906,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13905,17 +13932,17 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>592</v>
+        <v>601</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>593</v>
+        <v>602</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>594</v>
+        <v>603</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>595</v>
+        <v>604</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13964,7 +13991,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>591</v>
+        <v>600</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13988,7 +14015,7 @@
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="AO98" t="s" s="2">
         <v>77</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T18:32:47+00:00</t>
+    <t>2024-03-30T09:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.34.0</t>
+    <t>0.36.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-30T09:34:15+00:00</t>
+    <t>2024-04-03T07:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T07:33:38+00:00</t>
+    <t>2024-04-03T08:58:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-03T08:58:56+00:00</t>
+    <t>2024-04-10T18:17:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file INSTITUTION (#4) to us-core-organization</t>
+    <t>This StructureDefinition contains the maps for VistA file INSTITUTION (4) to us-core-organization</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -686,7 +686,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1252: source value from INSTITUTION - NPI (#4-41.99)</t>
+    <t>1252: source value from INSTITUTION - NPI (4-41.99)</t>
   </si>
   <si>
     <t>Dim.Institution.NPI</t>
@@ -875,7 +875,7 @@
     <t>Need to use the name as the label of the organization.</t>
   </si>
   <si>
-    <t>1251: source value from INSTITUTION - NAME (#4-.01)</t>
+    <t>1251: source value from INSTITUTION - NAME (4-.01)</t>
   </si>
   <si>
     <t>Dim.AutoDiscontinuedRule.InstitutionName,Dim.Institution.InstitutionName,Dim.RequestService.IFCRoutingInstitution</t>
@@ -906,7 +906,7 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
-    <t>1255: source value from INSTITUTION - SHORT NAME (#4-.05)</t>
+    <t>1255: source value from INSTITUTION - SHORT NAME (4-.05)</t>
   </si>
   <si>
     <t>Dim.Institution.InstitutionShortName</t>
@@ -1429,7 +1429,7 @@
     <t>Organization.address:physical.line</t>
   </si>
   <si>
-    <t>1259: source value from INSTITUTION - STREET ADDR. 2 (#4-1.02)</t>
+    <t>1259: source value from INSTITUTION - STREET ADDR. 2 (4-1.02)</t>
   </si>
   <si>
     <t>Dim.Institution.StreetAddress2</t>
@@ -1438,7 +1438,7 @@
     <t>Organization.address:physical.city</t>
   </si>
   <si>
-    <t>1260: source value from INSTITUTION - CITY (#4-1.03)</t>
+    <t>1260: source value from INSTITUTION - CITY (4-1.03)</t>
   </si>
   <si>
     <t>Dim.Institution.City</t>
@@ -1447,7 +1447,7 @@
     <t>Organization.address:physical.district</t>
   </si>
   <si>
-    <t>1261: source value from INSTITUTION - DISTRICT (#4-.03)</t>
+    <t>1261: source value from INSTITUTION - DISTRICT (4-.03)</t>
   </si>
   <si>
     <t>Dim.Institution.MedicalDistrict</t>
@@ -1456,7 +1456,7 @@
     <t>Organization.address:physical.state</t>
   </si>
   <si>
-    <t>1262: source value from INSTITUTION - STATE &gt; STATE - ABBREVIATION (#4-.02 &gt; 5-1)</t>
+    <t>1262: source value from INSTITUTION - STATE &gt; STATE - ABBREVIATION (4-.02 &gt; 5-1)</t>
   </si>
   <si>
     <t>Dim.State.StateAbbrev,Dim.State.StateAbbrev</t>
@@ -1465,7 +1465,7 @@
     <t>Organization.address:physical.postalCode</t>
   </si>
   <si>
-    <t>1263: source value from INSTITUTION - ZIP (#4-1.04)</t>
+    <t>1263: source value from INSTITUTION - ZIP (4-1.04)</t>
   </si>
   <si>
     <t>Dim.Institution.Zip</t>
@@ -1474,7 +1474,7 @@
     <t>Organization.address:physical.country</t>
   </si>
   <si>
-    <t>1264: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (#4-801 &gt; 779.004-.01)</t>
+    <t>1264: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>Dim.Country.CountryCode</t>
@@ -1510,13 +1510,13 @@
     <t>Organization.address:postal.line</t>
   </si>
   <si>
-    <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (#4-4.02)</t>
+    <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (4-4.02)</t>
   </si>
   <si>
     <t>Organization.address:postal.city</t>
   </si>
   <si>
-    <t>1271: source value from INSTITUTION - CITY (MAILING) (#4-4.03)</t>
+    <t>1271: source value from INSTITUTION - CITY (MAILING) (4-4.03)</t>
   </si>
   <si>
     <t>Organization.address:postal.district</t>
@@ -1525,19 +1525,19 @@
     <t>Organization.address:postal.state</t>
   </si>
   <si>
-    <t>1272: source value from INSTITUTION - STATE (MAILING) (#4-4.04)</t>
+    <t>1272: source value from INSTITUTION - STATE (MAILING) (4-4.04)</t>
   </si>
   <si>
     <t>Organization.address:postal.postalCode</t>
   </si>
   <si>
-    <t>1273: source value from INSTITUTION - ZIP (MAILING) (#4-4.05)</t>
+    <t>1273: source value from INSTITUTION - ZIP (MAILING) (4-4.05)</t>
   </si>
   <si>
     <t>Organization.address:postal.country</t>
   </si>
   <si>
-    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (#4-801 &gt; 779.004-.01)</t>
+    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>Organization.address:postal.period</t>
@@ -1697,7 +1697,7 @@
     <t>HumanName.text</t>
   </si>
   <si>
-    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT - NAME (#4-4 &gt; 4.03-.01)</t>
+    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT - NAME (4-4 &gt; 4.03-.01)</t>
   </si>
   <si>
     <t>implied by XPN.11</t>
@@ -1846,7 +1846,7 @@
     <t>Organization.contact.telecom.value</t>
   </si>
   <si>
-    <t>1266: source value from INSTITUTION - CONTACT &gt; CONTACT - PHONE # (#4-4 &gt; 4.03-.03)</t>
+    <t>1266: source value from INSTITUTION - CONTACT &gt; CONTACT - PHONE # (4-4 &gt; 4.03-.03)</t>
   </si>
   <si>
     <t>Organization.contact.telecom.use</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.36.0</t>
+    <t>0.37.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:17:58+00:00</t>
+    <t>2024-04-10T21:21:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.37.0</t>
+    <t>0.38.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T21:21:54+00:00</t>
+    <t>2024-04-12T10:04:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>VA (https://www.va.gov)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.38.0</t>
+    <t>0.39.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T10:04:01+00:00</t>
+    <t>2024-04-12T16:57:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.39.0</t>
+    <t>0.40.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-12T16:57:46+00:00</t>
+    <t>2024-04-13T07:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.40.0</t>
+    <t>0.41.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-13T07:20:06+00:00</t>
+    <t>2024-04-21T15:38:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.41.0</t>
+    <t>0.42.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-21T15:38:45+00:00</t>
+    <t>2024-04-22T07:04:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.42.0</t>
+    <t>0.43.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-22T07:04:34+00:00</t>
+    <t>2024-04-24T08:47:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.43.0</t>
+    <t>0.44.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-24T08:47:54+00:00</t>
+    <t>2024-04-25T08:17:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.44.0</t>
+    <t>0.45.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-25T08:17:47+00:00</t>
+    <t>2024-05-01T09:37:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1474,7 +1474,7 @@
     <t>Organization.address:physical.country</t>
   </si>
   <si>
-    <t>1264: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (4-801 &gt; 779.004-.01)</t>
+    <t>1264: source value from INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>Dim.Country.CountryCode</t>
@@ -1537,7 +1537,7 @@
     <t>Organization.address:postal.country</t>
   </si>
   <si>
-    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY - CODE (4-801 &gt; 779.004-.01)</t>
+    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>Organization.address:postal.period</t>
@@ -1697,7 +1697,7 @@
     <t>HumanName.text</t>
   </si>
   <si>
-    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT - NAME (4-4 &gt; 4.03-.01)</t>
+    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT - CONTACT (4-4 &gt; 4.03-.01)</t>
   </si>
   <si>
     <t>implied by XPN.11</t>
@@ -2244,7 +2244,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="88.6875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="92.3984375" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="109.390625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.45.0</t>
+    <t>0.46.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T09:37:14+00:00</t>
+    <t>2024-05-01T10:34:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="605">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="609">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.46.0</t>
+    <t>0.47.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-01T10:34:27+00:00</t>
+    <t>2024-05-04T09:18:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -689,7 +689,7 @@
     <t>1252: source value from INSTITUTION - NPI (4-41.99)</t>
   </si>
   <si>
-    <t>Dim.Institution.NPI</t>
+    <t>Dim.Institution.NPI,Dim.Institution.NPI,Dim.InstitutionTimeZone.NPI,NDim.MVIInstitution.NPI</t>
   </si>
   <si>
     <t>CX.1 / EI.1</t>
@@ -878,7 +878,7 @@
     <t>1251: source value from INSTITUTION - NAME (4-.01)</t>
   </si>
   <si>
-    <t>Dim.AutoDiscontinuedRule.InstitutionName,Dim.Institution.InstitutionName,Dim.RequestService.IFCRoutingInstitution</t>
+    <t>Dim.AutoDiscontinuedRule.InstitutionName,Dim.Institution.InstitutionName,Dim.Institution.InstitutionName,Dim.InstitutionTimeZone.Institution,Dim.RequestService.IFCRoutingInstitution,NDim.MVIInstitution.InstitutionName</t>
   </si>
   <si>
     <t>XON.1</t>
@@ -909,7 +909,7 @@
     <t>1255: source value from INSTITUTION - SHORT NAME (4-.05)</t>
   </si>
   <si>
-    <t>Dim.Institution.InstitutionShortName</t>
+    <t>Dim.Institution.InstitutionShortName,Dim.Institution.InstitutionShortName,Dim.InstitutionTimeZone.InstitutionShortName,NDim.MVIInstitution.InstitutionShortName</t>
   </si>
   <si>
     <t>Organization.telecom</t>
@@ -1432,7 +1432,7 @@
     <t>1259: source value from INSTITUTION - STREET ADDR. 2 (4-1.02)</t>
   </si>
   <si>
-    <t>Dim.Institution.StreetAddress2</t>
+    <t>Dim.Institution.StreetAddress2,Dim.Institution.StreetAddress2,Dim.InstitutionTimeZone.StreetAddress2,NDim.MVIInstitution.StreetAddress2</t>
   </si>
   <si>
     <t>Organization.address:physical.city</t>
@@ -1441,7 +1441,7 @@
     <t>1260: source value from INSTITUTION - CITY (4-1.03)</t>
   </si>
   <si>
-    <t>Dim.Institution.City</t>
+    <t>Dim.Institution.City,Dim.Institution.City,Dim.InstitutionTimeZone.City,NDim.MVIInstitution.City</t>
   </si>
   <si>
     <t>Organization.address:physical.district</t>
@@ -1450,7 +1450,7 @@
     <t>1261: source value from INSTITUTION - DISTRICT (4-.03)</t>
   </si>
   <si>
-    <t>Dim.Institution.MedicalDistrict</t>
+    <t>Dim.Institution.MedicalDistrict,Dim.Institution.MedicalDistrict,NDim.MVIInstitution.MedicalDistrict</t>
   </si>
   <si>
     <t>Organization.address:physical.state</t>
@@ -1459,7 +1459,8 @@
     <t>1262: source value from INSTITUTION - STATE &gt; STATE - ABBREVIATION (4-.02 &gt; 5-1)</t>
   </si>
   <si>
-    <t>Dim.State.StateAbbrev,Dim.State.StateAbbrev</t>
+    <t>Dim.Institution.StateIEN,Dim.InstitutionTimeZone.StateIEN,Dim.InstitutionTimeZone.StateSID,NDim.MVIInstitution.MVIStateIEN
+Dim.State.StateAbbrev,Dim.State.StateAbbrev,NDim.MVIState.StateAbbrev</t>
   </si>
   <si>
     <t>Organization.address:physical.postalCode</t>
@@ -1468,7 +1469,7 @@
     <t>1263: source value from INSTITUTION - ZIP (4-1.04)</t>
   </si>
   <si>
-    <t>Dim.Institution.Zip</t>
+    <t>Dim.Institution.Zip,Dim.Institution.Zip,Dim.InstitutionTimeZone.Zip,NDim.MVIInstitution.Zip</t>
   </si>
   <si>
     <t>Organization.address:physical.country</t>
@@ -1477,7 +1478,7 @@
     <t>1264: source value from INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
-    <t>Dim.Country.CountryCode</t>
+    <t>Dim.Country.CountryCode,NDim.MVICountryCode.CountryCode</t>
   </si>
   <si>
     <t>Organization.address:physical.period</t>
@@ -1513,12 +1514,18 @@
     <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (4-4.02)</t>
   </si>
   <si>
+    <t>Dim.InstitutionTimeZone.MailingStreetAddress2</t>
+  </si>
+  <si>
     <t>Organization.address:postal.city</t>
   </si>
   <si>
     <t>1271: source value from INSTITUTION - CITY (MAILING) (4-4.03)</t>
   </si>
   <si>
+    <t>Dim.InstitutionTimeZone.MailingCity</t>
+  </si>
+  <si>
     <t>Organization.address:postal.district</t>
   </si>
   <si>
@@ -1528,10 +1535,16 @@
     <t>1272: source value from INSTITUTION - STATE (MAILING) (4-4.04)</t>
   </si>
   <si>
+    <t>Dim.InstitutionTimeZone.MailingStateIEN,Dim.InstitutionTimeZone.MailingStateSID</t>
+  </si>
+  <si>
     <t>Organization.address:postal.postalCode</t>
   </si>
   <si>
     <t>1273: source value from INSTITUTION - ZIP (MAILING) (4-4.05)</t>
+  </si>
+  <si>
+    <t>Dim.InstitutionTimeZone.MailingZip</t>
   </si>
   <si>
     <t>Organization.address:postal.country</t>
@@ -2245,7 +2258,7 @@
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="92.3984375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="109.390625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="206.203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="218.1953125" customWidth="true" bestFit="true"/>
@@ -10177,7 +10190,7 @@
         <v>480</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>77</v>
+        <v>481</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>389</v>
@@ -10194,7 +10207,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>392</v>
@@ -10292,10 +10305,10 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>77</v>
+        <v>484</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>398</v>
@@ -10312,7 +10325,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>401</v>
@@ -10432,7 +10445,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>410</v>
@@ -10530,10 +10543,10 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>77</v>
+        <v>488</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>417</v>
@@ -10550,7 +10563,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>420</v>
@@ -10648,10 +10661,10 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>77</v>
+        <v>491</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>426</v>
@@ -10668,7 +10681,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>429</v>
@@ -10768,7 +10781,7 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="AL71" t="s" s="2">
         <v>469</v>
@@ -10788,7 +10801,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>437</v>
@@ -10908,10 +10921,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10937,14 +10950,14 @@
         <v>231</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10993,7 +11006,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11017,7 +11030,7 @@
         <v>252</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>167</v>
@@ -11028,10 +11041,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11054,19 +11067,19 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11115,7 +11128,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11139,7 +11152,7 @@
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>77</v>
@@ -11150,10 +11163,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11268,10 +11281,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11388,14 +11401,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11417,10 +11430,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>136</v>
@@ -11475,7 +11488,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11510,10 +11523,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11539,14 +11552,14 @@
         <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11574,28 +11587,28 @@
         <v>192</v>
       </c>
       <c r="Y78" t="s" s="2">
+        <v>518</v>
+      </c>
+      <c r="Z78" t="s" s="2">
+        <v>519</v>
+      </c>
+      <c r="AA78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE78" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF78" t="s" s="2">
         <v>514</v>
-      </c>
-      <c r="Z78" t="s" s="2">
-        <v>515</v>
-      </c>
-      <c r="AA78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE78" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF78" t="s" s="2">
-        <v>510</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11619,7 +11632,7 @@
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11630,10 +11643,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11656,17 +11669,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11715,7 +11728,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11736,10 +11749,10 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>77</v>
@@ -11750,10 +11763,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11868,10 +11881,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11988,10 +12001,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12017,16 +12030,16 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12054,10 +12067,10 @@
         <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12075,7 +12088,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12096,13 +12109,13 @@
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>327</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>77</v>
@@ -12110,10 +12123,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12139,13 +12152,13 @@
         <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>378</v>
@@ -12197,7 +12210,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12212,13 +12225,13 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>382</v>
@@ -12232,14 +12245,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12261,13 +12274,13 @@
         <v>163</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12317,7 +12330,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12338,13 +12351,13 @@
         <v>77</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>77</v>
@@ -12352,14 +12365,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12381,13 +12394,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12437,7 +12450,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12458,13 +12471,13 @@
         <v>77</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>77</v>
@@ -12472,10 +12485,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12501,10 +12514,10 @@
         <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12555,7 +12568,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12576,13 +12589,13 @@
         <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>77</v>
@@ -12590,10 +12603,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12619,10 +12632,10 @@
         <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12673,7 +12686,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12694,10 +12707,10 @@
         <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>77</v>
@@ -12708,10 +12721,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12737,14 +12750,14 @@
         <v>222</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12793,7 +12806,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12814,7 +12827,7 @@
         <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>339</v>
@@ -12828,10 +12841,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12857,14 +12870,14 @@
         <v>287</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12913,7 +12926,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12934,10 +12947,10 @@
         <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>584</v>
+        <v>588</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>77</v>
@@ -12948,10 +12961,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13066,10 +13079,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13186,10 +13199,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13304,10 +13317,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>589</v>
+        <v>593</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13406,7 +13419,7 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>77</v>
@@ -13426,10 +13439,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13548,10 +13561,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13668,10 +13681,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13786,10 +13799,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13815,14 +13828,14 @@
         <v>341</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13871,7 +13884,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13892,10 +13905,10 @@
         <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>77</v>
@@ -13906,10 +13919,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13932,17 +13945,17 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -13991,7 +14004,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.47.0</t>
+    <t>0.48.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-04T09:18:00+00:00</t>
+    <t>2024-05-06T08:00:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.48.0</t>
+    <t>0.49.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T08:00:03+00:00</t>
+    <t>2024-05-06T11:38:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.49.0</t>
+    <t>0.50.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-06T11:38:53+00:00</t>
+    <t>2024-05-08T06:31:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="611">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.50.0</t>
+    <t>0.51.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-08T06:31:45+00:00</t>
+    <t>2024-05-11T08:27:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1402,31 +1402,34 @@
     <t>XAD.12 / XAD.13 + XAD.14</t>
   </si>
   <si>
-    <t>Organization.address:physical</t>
+    <t>Organization.address:va-physical</t>
+  </si>
+  <si>
+    <t>va-physical</t>
+  </si>
+  <si>
+    <t>Organization.address:va-physical.id</t>
+  </si>
+  <si>
+    <t>Organization.address:va-physical.extension</t>
+  </si>
+  <si>
+    <t>Organization.address:va-physical.use</t>
+  </si>
+  <si>
+    <t>Organization.address:va-physical.type</t>
   </si>
   <si>
     <t>physical</t>
   </si>
   <si>
-    <t>Organization.address:physical.id</t>
-  </si>
-  <si>
-    <t>Organization.address:physical.extension</t>
-  </si>
-  <si>
-    <t>Organization.address:physical.use</t>
-  </si>
-  <si>
-    <t>Organization.address:physical.type</t>
-  </si>
-  <si>
     <t>1257: fixed value = #physical</t>
   </si>
   <si>
-    <t>Organization.address:physical.text</t>
-  </si>
-  <si>
-    <t>Organization.address:physical.line</t>
+    <t>Organization.address:va-physical.text</t>
+  </si>
+  <si>
+    <t>Organization.address:va-physical.line</t>
   </si>
   <si>
     <t>1259: source value from INSTITUTION - STREET ADDR. 2 (4-1.02)</t>
@@ -1435,7 +1438,7 @@
     <t>Dim.Institution.StreetAddress2,Dim.Institution.StreetAddress2,Dim.InstitutionTimeZone.StreetAddress2,NDim.MVIInstitution.StreetAddress2</t>
   </si>
   <si>
-    <t>Organization.address:physical.city</t>
+    <t>Organization.address:va-physical.city</t>
   </si>
   <si>
     <t>1260: source value from INSTITUTION - CITY (4-1.03)</t>
@@ -1444,7 +1447,7 @@
     <t>Dim.Institution.City,Dim.Institution.City,Dim.InstitutionTimeZone.City,NDim.MVIInstitution.City</t>
   </si>
   <si>
-    <t>Organization.address:physical.district</t>
+    <t>Organization.address:va-physical.district</t>
   </si>
   <si>
     <t>1261: source value from INSTITUTION - DISTRICT (4-.03)</t>
@@ -1453,7 +1456,7 @@
     <t>Dim.Institution.MedicalDistrict,Dim.Institution.MedicalDistrict,NDim.MVIInstitution.MedicalDistrict</t>
   </si>
   <si>
-    <t>Organization.address:physical.state</t>
+    <t>Organization.address:va-physical.state</t>
   </si>
   <si>
     <t>1262: source value from INSTITUTION - STATE &gt; STATE - ABBREVIATION (4-.02 &gt; 5-1)</t>
@@ -1463,7 +1466,7 @@
 Dim.State.StateAbbrev,Dim.State.StateAbbrev,NDim.MVIState.StateAbbrev</t>
   </si>
   <si>
-    <t>Organization.address:physical.postalCode</t>
+    <t>Organization.address:va-physical.postalCode</t>
   </si>
   <si>
     <t>1263: source value from INSTITUTION - ZIP (4-1.04)</t>
@@ -1472,7 +1475,7 @@
     <t>Dim.Institution.Zip,Dim.Institution.Zip,Dim.InstitutionTimeZone.Zip,NDim.MVIInstitution.Zip</t>
   </si>
   <si>
-    <t>Organization.address:physical.country</t>
+    <t>Organization.address:va-physical.country</t>
   </si>
   <si>
     <t>1264: source value from INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
@@ -1481,34 +1484,37 @@
     <t>Dim.Country.CountryCode,NDim.MVICountryCode.CountryCode</t>
   </si>
   <si>
-    <t>Organization.address:physical.period</t>
-  </si>
-  <si>
-    <t>Organization.address:postal</t>
+    <t>Organization.address:va-physical.period</t>
+  </si>
+  <si>
+    <t>Organization.address:va-postal</t>
+  </si>
+  <si>
+    <t>va-postal</t>
+  </si>
+  <si>
+    <t>Organization.address:va-postal.id</t>
+  </si>
+  <si>
+    <t>Organization.address:va-postal.extension</t>
+  </si>
+  <si>
+    <t>Organization.address:va-postal.use</t>
+  </si>
+  <si>
+    <t>Organization.address:va-postal.type</t>
   </si>
   <si>
     <t>postal</t>
   </si>
   <si>
-    <t>Organization.address:postal.id</t>
-  </si>
-  <si>
-    <t>Organization.address:postal.extension</t>
-  </si>
-  <si>
-    <t>Organization.address:postal.use</t>
-  </si>
-  <si>
-    <t>Organization.address:postal.type</t>
-  </si>
-  <si>
     <t>1268: fixed value = #postal</t>
   </si>
   <si>
-    <t>Organization.address:postal.text</t>
-  </si>
-  <si>
-    <t>Organization.address:postal.line</t>
+    <t>Organization.address:va-postal.text</t>
+  </si>
+  <si>
+    <t>Organization.address:va-postal.line</t>
   </si>
   <si>
     <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (4-4.02)</t>
@@ -1517,7 +1523,7 @@
     <t>Dim.InstitutionTimeZone.MailingStreetAddress2</t>
   </si>
   <si>
-    <t>Organization.address:postal.city</t>
+    <t>Organization.address:va-postal.city</t>
   </si>
   <si>
     <t>1271: source value from INSTITUTION - CITY (MAILING) (4-4.03)</t>
@@ -1526,10 +1532,10 @@
     <t>Dim.InstitutionTimeZone.MailingCity</t>
   </si>
   <si>
-    <t>Organization.address:postal.district</t>
-  </si>
-  <si>
-    <t>Organization.address:postal.state</t>
+    <t>Organization.address:va-postal.district</t>
+  </si>
+  <si>
+    <t>Organization.address:va-postal.state</t>
   </si>
   <si>
     <t>1272: source value from INSTITUTION - STATE (MAILING) (4-4.04)</t>
@@ -1538,7 +1544,7 @@
     <t>Dim.InstitutionTimeZone.MailingStateIEN,Dim.InstitutionTimeZone.MailingStateSID</t>
   </si>
   <si>
-    <t>Organization.address:postal.postalCode</t>
+    <t>Organization.address:va-postal.postalCode</t>
   </si>
   <si>
     <t>1273: source value from INSTITUTION - ZIP (MAILING) (4-4.05)</t>
@@ -1547,13 +1553,13 @@
     <t>Dim.InstitutionTimeZone.MailingZip</t>
   </si>
   <si>
-    <t>Organization.address:postal.country</t>
+    <t>Organization.address:va-postal.country</t>
   </si>
   <si>
     <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
-    <t>Organization.address:postal.period</t>
+    <t>Organization.address:va-postal.period</t>
   </si>
   <si>
     <t>Organization.partOf</t>
@@ -2222,7 +2228,7 @@
   <dimension ref="A1:AP98"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="39.625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="42.49609375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.77734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -8335,7 +8341,7 @@
         <v>77</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="T51" t="s" s="2">
         <v>369</v>
@@ -8389,7 +8395,7 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
@@ -8409,7 +8415,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>374</v>
@@ -8531,7 +8537,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>383</v>
@@ -8629,10 +8635,10 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>389</v>
@@ -8649,7 +8655,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>392</v>
@@ -8747,10 +8753,10 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>398</v>
@@ -8767,7 +8773,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>401</v>
@@ -8867,10 +8873,10 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>408</v>
@@ -8887,7 +8893,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>410</v>
@@ -8985,10 +8991,10 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>417</v>
@@ -9005,7 +9011,7 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>420</v>
@@ -9103,10 +9109,10 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>426</v>
@@ -9123,7 +9129,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>429</v>
@@ -9223,10 +9229,10 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>434</v>
@@ -9243,7 +9249,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>437</v>
@@ -9363,13 +9369,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>340</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9487,7 +9493,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>352</v>
@@ -9605,7 +9611,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>353</v>
@@ -9725,7 +9731,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>354</v>
@@ -9847,7 +9853,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>365</v>
@@ -9893,7 +9899,7 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
       <c r="T64" t="s" s="2">
         <v>369</v>
@@ -9947,7 +9953,7 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
@@ -9967,7 +9973,7 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>374</v>
@@ -10089,7 +10095,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>383</v>
@@ -10187,10 +10193,10 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>389</v>
@@ -10207,7 +10213,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>392</v>
@@ -10305,10 +10311,10 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>398</v>
@@ -10325,7 +10331,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>401</v>
@@ -10445,7 +10451,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>410</v>
@@ -10543,10 +10549,10 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>417</v>
@@ -10563,7 +10569,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>420</v>
@@ -10661,10 +10667,10 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>426</v>
@@ -10681,7 +10687,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>429</v>
@@ -10781,10 +10787,10 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>434</v>
@@ -10801,7 +10807,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>437</v>
@@ -10921,10 +10927,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10950,14 +10956,14 @@
         <v>231</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -11006,7 +11012,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11030,7 +11036,7 @@
         <v>252</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>167</v>
@@ -11041,10 +11047,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11067,19 +11073,19 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11128,7 +11134,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11152,7 +11158,7 @@
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>77</v>
@@ -11163,10 +11169,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11281,10 +11287,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11401,14 +11407,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11430,10 +11436,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>136</v>
@@ -11488,7 +11494,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11523,10 +11529,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11552,14 +11558,14 @@
         <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11587,10 +11593,10 @@
         <v>192</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11608,7 +11614,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11632,7 +11638,7 @@
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11643,10 +11649,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11669,17 +11675,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11728,7 +11734,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11749,10 +11755,10 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>77</v>
@@ -11763,10 +11769,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11881,10 +11887,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12001,10 +12007,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12030,16 +12036,16 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12067,10 +12073,10 @@
         <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12088,7 +12094,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12109,13 +12115,13 @@
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>327</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>77</v>
@@ -12123,10 +12129,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12152,13 +12158,13 @@
         <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="O83" t="s" s="2">
         <v>378</v>
@@ -12210,7 +12216,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12225,13 +12231,13 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>382</v>
@@ -12245,14 +12251,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12274,13 +12280,13 @@
         <v>163</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12330,7 +12336,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12351,13 +12357,13 @@
         <v>77</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>77</v>
@@ -12365,14 +12371,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12394,13 +12400,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12450,7 +12456,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12471,13 +12477,13 @@
         <v>77</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>77</v>
@@ -12485,10 +12491,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12514,10 +12520,10 @@
         <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12568,7 +12574,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12589,13 +12595,13 @@
         <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>77</v>
@@ -12603,10 +12609,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12632,10 +12638,10 @@
         <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12686,7 +12692,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12707,10 +12713,10 @@
         <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>77</v>
@@ -12721,10 +12727,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12750,14 +12756,14 @@
         <v>222</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12806,7 +12812,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12827,7 +12833,7 @@
         <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>339</v>
@@ -12841,10 +12847,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12870,14 +12876,14 @@
         <v>287</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12926,7 +12932,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12947,10 +12953,10 @@
         <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>77</v>
@@ -12961,10 +12967,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13079,10 +13085,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13199,10 +13205,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13317,10 +13323,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13419,7 +13425,7 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>77</v>
@@ -13439,10 +13445,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13561,10 +13567,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13681,10 +13687,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13799,10 +13805,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13828,14 +13834,14 @@
         <v>341</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13884,7 +13890,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13905,10 +13911,10 @@
         <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>77</v>
@@ -13919,10 +13925,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13945,17 +13951,17 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -14004,7 +14010,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="614">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.51.0</t>
+    <t>0.52.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-11T08:27:40+00:00</t>
+    <t>2024-05-19T08:28:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,10 +650,16 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
+    <t>http://hl7.org/fhir/sid/us-npi</t>
+  </si>
+  <si>
     <t>http://www.acme.com/identifiers/patient</t>
   </si>
   <si>
     <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>1252-1: fixed value = http://hl7.org/fhir/sid/us-npi</t>
   </si>
   <si>
     <t>CX.4 / EI-2-4</t>
@@ -1098,10 +1104,6 @@
     <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
   </si>
   <si>
-    <t xml:space="preserve">value:use}
-</t>
-  </si>
-  <si>
     <t xml:space="preserve">org-2
 </t>
   </si>
@@ -1860,6 +1862,12 @@
   </si>
   <si>
     <t>Organization.contact.telecom.system</t>
+  </si>
+  <si>
+    <t>phone</t>
+  </si>
+  <si>
+    <t>1266-1: fixed value = #phone</t>
   </si>
   <si>
     <t>Organization.contact.telecom.value</t>
@@ -4253,10 +4261,10 @@
         <v>77</v>
       </c>
       <c r="S17" t="s" s="2">
-        <v>77</v>
+        <v>203</v>
       </c>
       <c r="T17" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="U17" t="s" s="2">
         <v>77</v>
@@ -4292,7 +4300,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -4307,19 +4315,19 @@
         <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>77</v>
+        <v>206</v>
       </c>
       <c r="AL17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="AO17" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AP17" t="s" s="2">
         <v>77</v>
@@ -4327,10 +4335,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4356,13 +4364,13 @@
         <v>163</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -4376,7 +4384,7 @@
         <v>77</v>
       </c>
       <c r="T18" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="U18" t="s" s="2">
         <v>77</v>
@@ -4412,7 +4420,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -4427,19 +4435,19 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AM18" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AN18" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="AO18" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AP18" t="s" s="2">
         <v>77</v>
@@ -4447,10 +4455,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4473,13 +4481,13 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -4530,7 +4538,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -4551,13 +4559,13 @@
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP19" t="s" s="2">
         <v>77</v>
@@ -4565,10 +4573,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4591,16 +4599,16 @@
         <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -4650,7 +4658,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4671,13 +4679,13 @@
         <v>77</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="AO20" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AP20" t="s" s="2">
         <v>77</v>
@@ -4685,13 +4693,13 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B21" t="s" s="2">
         <v>144</v>
       </c>
       <c r="C21" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="D21" t="s" s="2">
         <v>77</v>
@@ -4716,7 +4724,7 @@
         <v>145</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M21" t="s" s="2">
         <v>147</v>
@@ -4733,7 +4741,7 @@
         <v>77</v>
       </c>
       <c r="S21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T21" t="s" s="2">
         <v>77</v>
@@ -4807,10 +4815,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4833,70 +4841,70 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="L22" t="s" s="2">
+        <v>247</v>
+      </c>
+      <c r="M22" t="s" s="2">
+        <v>248</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="O22" t="s" s="2">
+        <v>250</v>
+      </c>
+      <c r="P22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q22" t="s" s="2">
+        <v>251</v>
+      </c>
+      <c r="R22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S22" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="T22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE22" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF22" t="s" s="2">
         <v>245</v>
-      </c>
-      <c r="M22" t="s" s="2">
-        <v>246</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>247</v>
-      </c>
-      <c r="O22" t="s" s="2">
-        <v>248</v>
-      </c>
-      <c r="P22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q22" t="s" s="2">
-        <v>249</v>
-      </c>
-      <c r="R22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S22" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="T22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE22" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF22" t="s" s="2">
-        <v>243</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4911,30 +4919,30 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="AL22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AO22" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AP22" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4960,16 +4968,16 @@
         <v>187</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4979,7 +4987,7 @@
         <v>77</v>
       </c>
       <c r="S23" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="T23" t="s" s="2">
         <v>77</v>
@@ -4994,13 +5002,13 @@
         <v>77</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>77</v>
@@ -5018,7 +5026,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -5033,30 +5041,30 @@
         <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AL23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="AO23" t="s" s="2">
         <v>167</v>
       </c>
       <c r="AP23" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5082,16 +5090,16 @@
         <v>163</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -5140,7 +5148,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -5155,19 +5163,19 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO24" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AP24" t="s" s="2">
         <v>77</v>
@@ -5175,10 +5183,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5204,16 +5212,16 @@
         <v>163</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -5262,7 +5270,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -5277,16 +5285,16 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>77</v>
@@ -5297,10 +5305,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5323,19 +5331,19 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -5384,7 +5392,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -5393,25 +5401,25 @@
         <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>77</v>
@@ -5419,10 +5427,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5537,10 +5545,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5657,10 +5665,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5686,10 +5694,10 @@
         <v>107</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -5719,10 +5727,10 @@
         <v>180</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>77</v>
@@ -5740,7 +5748,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5749,7 +5757,7 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AJ29" t="s" s="2">
         <v>99</v>
@@ -5761,13 +5769,13 @@
         <v>77</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>77</v>
@@ -5775,10 +5783,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5804,16 +5812,16 @@
         <v>163</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5862,7 +5870,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5883,13 +5891,13 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>77</v>
@@ -5897,10 +5905,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5926,16 +5934,16 @@
         <v>107</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5963,10 +5971,10 @@
         <v>180</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>77</v>
@@ -5984,7 +5992,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -6005,13 +6013,13 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>77</v>
@@ -6019,10 +6027,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6045,16 +6053,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -6104,7 +6112,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -6139,10 +6147,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6165,13 +6173,13 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6222,7 +6230,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -6246,10 +6254,10 @@
         <v>130</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP33" t="s" s="2">
         <v>77</v>
@@ -6257,10 +6265,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -6283,19 +6291,19 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -6332,7 +6340,7 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>346</v>
+        <v>150</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -6342,7 +6350,7 @@
         <v>151</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -6351,10 +6359,10 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
@@ -6363,13 +6371,13 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>77</v>
@@ -6377,10 +6385,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6495,10 +6503,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6615,10 +6623,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6644,16 +6652,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6666,7 +6674,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6681,10 +6689,10 @@
         <v>180</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6702,7 +6710,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6723,13 +6731,13 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>77</v>
@@ -6737,10 +6745,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6766,13 +6774,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6786,7 +6794,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6801,10 +6809,10 @@
         <v>180</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6822,7 +6830,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6843,10 +6851,10 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>77</v>
@@ -6857,10 +6865,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6886,16 +6894,16 @@
         <v>163</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6908,7 +6916,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6944,7 +6952,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6965,10 +6973,10 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>77</v>
@@ -6979,10 +6987,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6993,7 +7001,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -7008,10 +7016,10 @@
         <v>163</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7026,7 +7034,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -7062,7 +7070,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7083,13 +7091,13 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>77</v>
@@ -7097,14 +7105,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7126,10 +7134,10 @@
         <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7144,7 +7152,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -7180,7 +7188,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7201,13 +7209,13 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>77</v>
@@ -7215,14 +7223,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7244,13 +7252,13 @@
         <v>163</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7264,7 +7272,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -7300,7 +7308,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7321,10 +7329,10 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>77</v>
@@ -7335,14 +7343,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7364,10 +7372,10 @@
         <v>163</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7397,10 +7405,10 @@
         <v>192</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7418,7 +7426,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7439,13 +7447,13 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>77</v>
@@ -7453,14 +7461,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7482,10 +7490,10 @@
         <v>163</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7500,7 +7508,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7536,7 +7544,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7557,13 +7565,13 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>77</v>
@@ -7571,10 +7579,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7600,13 +7608,13 @@
         <v>163</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7656,7 +7664,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7677,13 +7685,13 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>77</v>
@@ -7691,10 +7699,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7717,17 +7725,17 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7740,7 +7748,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7776,7 +7784,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7797,13 +7805,13 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>77</v>
@@ -7811,13 +7819,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7839,19 +7847,19 @@
         <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7900,7 +7908,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7909,10 +7917,10 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7921,13 +7929,13 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>77</v>
@@ -7935,10 +7943,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8053,10 +8061,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8173,10 +8181,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8202,16 +8210,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8224,7 +8232,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -8239,10 +8247,10 @@
         <v>180</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -8260,7 +8268,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8281,13 +8289,13 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>77</v>
@@ -8295,10 +8303,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8324,13 +8332,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8341,10 +8349,10 @@
         <v>77</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -8359,10 +8367,10 @@
         <v>180</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8380,7 +8388,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8395,16 +8403,16 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>77</v>
@@ -8415,10 +8423,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8444,16 +8452,16 @@
         <v>163</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8466,7 +8474,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -8502,7 +8510,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8523,10 +8531,10 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>77</v>
@@ -8537,10 +8545,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8551,7 +8559,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>88</v>
@@ -8566,10 +8574,10 @@
         <v>163</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8584,7 +8592,7 @@
         <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>77</v>
@@ -8620,7 +8628,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8635,19 +8643,19 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>77</v>
@@ -8655,14 +8663,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8684,10 +8692,10 @@
         <v>163</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8702,7 +8710,7 @@
         <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8738,7 +8746,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8753,19 +8761,19 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>77</v>
@@ -8773,14 +8781,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8802,13 +8810,13 @@
         <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8822,7 +8830,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8858,7 +8866,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8873,16 +8881,16 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>77</v>
@@ -8893,14 +8901,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8922,10 +8930,10 @@
         <v>163</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8955,10 +8963,10 @@
         <v>192</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8976,7 +8984,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8991,19 +8999,19 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>77</v>
@@ -9011,14 +9019,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9040,10 +9048,10 @@
         <v>163</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9058,7 +9066,7 @@
         <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>77</v>
@@ -9094,7 +9102,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9109,19 +9117,19 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>77</v>
@@ -9129,10 +9137,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9158,13 +9166,13 @@
         <v>163</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9214,7 +9222,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9229,19 +9237,19 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>77</v>
@@ -9249,10 +9257,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9275,17 +9283,17 @@
         <v>88</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9298,7 +9306,7 @@
         <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>77</v>
@@ -9334,7 +9342,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9355,13 +9363,13 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP59" t="s" s="2">
         <v>77</v>
@@ -9369,13 +9377,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9397,19 +9405,19 @@
         <v>77</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -9458,7 +9466,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -9467,10 +9475,10 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -9479,13 +9487,13 @@
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>77</v>
@@ -9493,10 +9501,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9611,10 +9619,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9731,10 +9739,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9760,16 +9768,16 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9782,7 +9790,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9797,10 +9805,10 @@
         <v>180</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9818,7 +9826,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9839,13 +9847,13 @@
         <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>77</v>
@@ -9853,10 +9861,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9882,13 +9890,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9899,10 +9907,10 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9917,10 +9925,10 @@
         <v>180</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9938,7 +9946,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9953,16 +9961,16 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO64" t="s" s="2">
         <v>77</v>
@@ -9973,10 +9981,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10002,16 +10010,16 @@
         <v>163</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -10024,7 +10032,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -10060,7 +10068,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10081,10 +10089,10 @@
         <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -10095,10 +10103,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10109,7 +10117,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>88</v>
@@ -10124,10 +10132,10 @@
         <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10142,7 +10150,7 @@
         <v>77</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>77</v>
@@ -10178,7 +10186,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10193,19 +10201,19 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>77</v>
@@ -10213,14 +10221,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10242,10 +10250,10 @@
         <v>163</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10260,7 +10268,7 @@
         <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>77</v>
@@ -10296,7 +10304,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10311,19 +10319,19 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>77</v>
@@ -10331,14 +10339,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10360,13 +10368,13 @@
         <v>163</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10380,7 +10388,7 @@
         <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>77</v>
@@ -10416,7 +10424,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10437,10 +10445,10 @@
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>77</v>
@@ -10451,14 +10459,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10480,10 +10488,10 @@
         <v>163</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10513,10 +10521,10 @@
         <v>192</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10534,7 +10542,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10549,19 +10557,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10569,14 +10577,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10598,10 +10606,10 @@
         <v>163</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10616,7 +10624,7 @@
         <v>77</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>77</v>
@@ -10652,7 +10660,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10667,19 +10675,19 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>77</v>
@@ -10687,10 +10695,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10716,13 +10724,13 @@
         <v>163</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10772,7 +10780,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10787,19 +10795,19 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>77</v>
@@ -10807,10 +10815,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10833,17 +10841,17 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10856,7 +10864,7 @@
         <v>77</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>77</v>
@@ -10892,7 +10900,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10913,13 +10921,13 @@
         <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP72" t="s" s="2">
         <v>77</v>
@@ -10927,10 +10935,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10953,17 +10961,17 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -11012,7 +11020,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11033,10 +11041,10 @@
         <v>77</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>167</v>
@@ -11047,10 +11055,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11073,19 +11081,19 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11134,7 +11142,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11158,7 +11166,7 @@
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>77</v>
@@ -11169,10 +11177,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11287,10 +11295,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11407,14 +11415,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11436,10 +11444,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>136</v>
@@ -11494,7 +11502,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11529,10 +11537,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11558,14 +11566,14 @@
         <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11593,10 +11601,10 @@
         <v>192</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11614,7 +11622,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11638,7 +11646,7 @@
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11649,10 +11657,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11675,17 +11683,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11734,7 +11742,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11755,10 +11763,10 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>77</v>
@@ -11769,10 +11777,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11887,10 +11895,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12007,10 +12015,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12036,16 +12044,16 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12073,10 +12081,10 @@
         <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12094,7 +12102,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12115,13 +12123,13 @@
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AN82" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>77</v>
@@ -12129,10 +12137,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12158,16 +12166,16 @@
         <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12216,7 +12224,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12231,16 +12239,16 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>77</v>
@@ -12251,14 +12259,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12280,13 +12288,13 @@
         <v>163</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12336,7 +12344,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12357,13 +12365,13 @@
         <v>77</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>77</v>
@@ -12371,14 +12379,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12400,13 +12408,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12456,7 +12464,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12477,13 +12485,13 @@
         <v>77</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>77</v>
@@ -12491,10 +12499,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12520,10 +12528,10 @@
         <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12574,7 +12582,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12595,13 +12603,13 @@
         <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>77</v>
@@ -12609,10 +12617,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12638,10 +12646,10 @@
         <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12692,7 +12700,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12713,10 +12721,10 @@
         <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>77</v>
@@ -12727,10 +12735,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12753,17 +12761,17 @@
         <v>88</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12812,7 +12820,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12833,13 +12841,13 @@
         <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AN88" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO88" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP88" t="s" s="2">
         <v>77</v>
@@ -12847,10 +12855,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12873,17 +12881,17 @@
         <v>77</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12932,7 +12940,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12953,10 +12961,10 @@
         <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>77</v>
@@ -12967,10 +12975,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13085,10 +13093,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13205,10 +13213,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13222,7 +13230,7 @@
         <v>87</v>
       </c>
       <c r="H92" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I92" t="s" s="2">
         <v>77</v>
@@ -13234,10 +13242,10 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -13249,7 +13257,7 @@
         <v>77</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>77</v>
+        <v>596</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>77</v>
@@ -13267,10 +13275,10 @@
         <v>180</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>77</v>
@@ -13288,7 +13296,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -13297,25 +13305,25 @@
         <v>87</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>77</v>
+        <v>597</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AO92" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AP92" t="s" s="2">
         <v>77</v>
@@ -13323,10 +13331,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13352,16 +13360,16 @@
         <v>163</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -13410,7 +13418,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13425,19 +13433,19 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AO93" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AP93" t="s" s="2">
         <v>77</v>
@@ -13445,10 +13453,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13474,16 +13482,16 @@
         <v>107</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -13511,10 +13519,10 @@
         <v>180</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>77</v>
@@ -13532,7 +13540,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -13553,13 +13561,13 @@
         <v>77</v>
       </c>
       <c r="AM94" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="AO94" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="AP94" t="s" s="2">
         <v>77</v>
@@ -13567,10 +13575,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13593,16 +13601,16 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -13652,7 +13660,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -13687,10 +13695,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13713,13 +13721,13 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13770,7 +13778,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -13794,10 +13802,10 @@
         <v>130</v>
       </c>
       <c r="AN96" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AO96" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="AP96" t="s" s="2">
         <v>77</v>
@@ -13805,10 +13813,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13831,17 +13839,17 @@
         <v>77</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13890,7 +13898,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13911,10 +13919,10 @@
         <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>77</v>
@@ -13925,10 +13933,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13951,17 +13959,17 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -14010,7 +14018,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.52.0</t>
+    <t>0.53.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-19T08:28:17+00:00</t>
+    <t>2024-05-22T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.53.0</t>
+    <t>0.54.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-22T14:44:53+00:00</t>
+    <t>2024-05-25T10:26:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.54.0</t>
+    <t>0.57.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-25T10:26:15+00:00</t>
+    <t>2024-06-04T15:52:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-04T15:52:07+00:00</t>
+    <t>2024-06-11T05:38:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T05:38:55+00:00</t>
+    <t>2024-06-12T18:51:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.57.0</t>
+    <t>0.58.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-12T18:51:20+00:00</t>
+    <t>2024-06-14T11:56:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.58.0</t>
+    <t>0.59.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-14T11:56:40+00:00</t>
+    <t>2024-06-21T15:05:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-21T15:05:18+00:00</t>
+    <t>2024-07-09T16:26:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.59.0</t>
+    <t>0.61.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T16:26:13+00:00</t>
+    <t>2024-07-24T18:59:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.61.0</t>
+    <t>0.62.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-24T18:59:55+00:00</t>
+    <t>2024-07-28T09:11:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.62.0</t>
+    <t>0.63.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-28T09:11:13+00:00</t>
+    <t>2024-07-31T09:58:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.63.0</t>
+    <t>0.64.311</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T09:58:27+00:00</t>
+    <t>2024-07-31T19:09:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.311</t>
+    <t>0.64.312</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-31T19:09:08+00:00</t>
+    <t>2024-08-02T13:01:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.312</t>
+    <t>0.64.316</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-02T13:01:18+00:00</t>
+    <t>2024-08-04T09:05:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.316</t>
+    <t>0.64.318</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-04T09:05:29+00:00</t>
+    <t>2024-08-05T15:01:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.64.318</t>
+    <t>0.65.329</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-05T15:01:43+00:00</t>
+    <t>2024-08-13T08:01:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.329</t>
+    <t>0.65.332</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T08:01:15+00:00</t>
+    <t>2024-08-13T15:06:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.332</t>
+    <t>0.65.334</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-13T15:06:38+00:00</t>
+    <t>2024-08-14T15:16:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-14T15:16:17+00:00</t>
+    <t>2024-08-17T06:29:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.334</t>
+    <t>0.65.339</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-17T06:29:49+00:00</t>
+    <t>2024-08-18T10:15:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.339</t>
+    <t>0.65.341</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-18T10:15:47+00:00</t>
+    <t>2024-08-20T15:42:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.341</t>
+    <t>0.65.343</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-20T15:42:57+00:00</t>
+    <t>2024-08-24T10:06:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.343</t>
+    <t>0.65.345</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-24T10:06:05+00:00</t>
+    <t>2024-08-26T15:27:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.345</t>
+    <t>0.65.348</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-08-26T15:27:18+00:00</t>
+    <t>2024-09-15T08:33:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.65.348</t>
+    <t>0.66.354</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-15T08:33:43+00:00</t>
+    <t>2024-09-19T08:45:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.366</t>
+    <t>0.66.367</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-11T07:57:28+00:00</t>
+    <t>2024-10-13T09:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.367</t>
+    <t>0.67.369</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-13T09:59:39+00:00</t>
+    <t>2024-10-18T16:05:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.369</t>
+    <t>0.67.370</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-18T16:05:33+00:00</t>
+    <t>2024-10-20T09:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.370</t>
+    <t>0.67.378</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-20T09:02:32+00:00</t>
+    <t>2024-10-30T12:26:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.378</t>
+    <t>0.67.381</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-30T12:26:51+00:00</t>
+    <t>2024-11-03T11:50:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.67.381</t>
+    <t>0.68.397</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-03T11:50:46+00:00</t>
+    <t>2024-11-10T10:13:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.397</t>
+    <t>0.68.401</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-10T10:13:24+00:00</t>
+    <t>2024-11-13T21:40:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.401</t>
+    <t>0.68.419</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-13T21:40:45+00:00</t>
+    <t>2024-11-25T07:50:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.419</t>
+    <t>0.68.424</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-25T07:50:24+00:00</t>
+    <t>2024-11-30T14:03:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.424</t>
+    <t>0.68.425</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T14:03:16+00:00</t>
+    <t>2024-11-30T15:07:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.68.425</t>
+    <t>0.69.436</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-30T15:07:22+00:00</t>
+    <t>2024-12-04T11:34:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.436</t>
+    <t>0.69.437</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T11:34:53+00:00</t>
+    <t>2024-12-04T16:25:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.437</t>
+    <t>0.69.438</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-04T16:25:11+00:00</t>
+    <t>2024-12-06T17:18:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.438</t>
+    <t>0.69.439</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-06T17:18:58+00:00</t>
+    <t>2024-12-07T11:18:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.439</t>
+    <t>0.69.440</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-07T11:18:15+00:00</t>
+    <t>2024-12-08T09:28:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.440</t>
+    <t>0.69.442</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-08T09:28:43+00:00</t>
+    <t>2024-12-11T20:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.442</t>
+    <t>0.69.448</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-11T20:06:32+00:00</t>
+    <t>2024-12-21T10:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA file INSTITUTION (4) to us-core-organization</t>
+    <t>This StructureDefinition contains the maps for VistA file INSTITUTION (4) to us-core-organization.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="614">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3767" uniqueCount="615">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.69.448</t>
+    <t>1.1.467</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-21T10:24:25+00:00</t>
+    <t>2025-01-04T09:38:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1102,6 +1102,10 @@
   </si>
   <si>
     <t>May need to keep track of the organization's addresses for contacting, billing or reporting requirements.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:$this}
+</t>
   </si>
   <si>
     <t xml:space="preserve">org-2
@@ -6340,7 +6344,7 @@
         <v>77</v>
       </c>
       <c r="AB34" t="s" s="2">
-        <v>150</v>
+        <v>348</v>
       </c>
       <c r="AC34" s="2"/>
       <c r="AD34" t="s" s="2">
@@ -6359,10 +6363,10 @@
         <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AK34" t="s" s="2">
         <v>77</v>
@@ -6371,13 +6375,13 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP34" t="s" s="2">
         <v>77</v>
@@ -6385,10 +6389,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6503,10 +6507,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6623,10 +6627,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6652,16 +6656,16 @@
         <v>107</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -6674,7 +6678,7 @@
         <v>77</v>
       </c>
       <c r="T37" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U37" t="s" s="2">
         <v>77</v>
@@ -6689,10 +6693,10 @@
         <v>180</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>77</v>
@@ -6710,7 +6714,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6731,13 +6735,13 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>329</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP37" t="s" s="2">
         <v>77</v>
@@ -6745,10 +6749,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6774,13 +6778,13 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -6794,7 +6798,7 @@
         <v>77</v>
       </c>
       <c r="T38" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="U38" t="s" s="2">
         <v>77</v>
@@ -6809,10 +6813,10 @@
         <v>180</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>77</v>
@@ -6830,7 +6834,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6851,7 +6855,7 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>329</v>
@@ -6865,10 +6869,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6894,16 +6898,16 @@
         <v>163</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O39" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6916,7 +6920,7 @@
         <v>77</v>
       </c>
       <c r="T39" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="U39" t="s" s="2">
         <v>77</v>
@@ -6952,7 +6956,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6973,10 +6977,10 @@
         <v>77</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>77</v>
@@ -6987,10 +6991,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7001,7 +7005,7 @@
         <v>78</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>88</v>
@@ -7016,10 +7020,10 @@
         <v>163</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -7034,7 +7038,7 @@
         <v>77</v>
       </c>
       <c r="T40" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="U40" t="s" s="2">
         <v>77</v>
@@ -7070,7 +7074,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -7091,13 +7095,13 @@
         <v>77</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO40" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP40" t="s" s="2">
         <v>77</v>
@@ -7105,14 +7109,14 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
@@ -7134,10 +7138,10 @@
         <v>163</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -7152,7 +7156,7 @@
         <v>77</v>
       </c>
       <c r="T41" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U41" t="s" s="2">
         <v>77</v>
@@ -7188,7 +7192,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -7209,13 +7213,13 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO41" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP41" t="s" s="2">
         <v>77</v>
@@ -7223,14 +7227,14 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
@@ -7252,13 +7256,13 @@
         <v>163</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -7272,7 +7276,7 @@
         <v>77</v>
       </c>
       <c r="T42" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U42" t="s" s="2">
         <v>77</v>
@@ -7308,7 +7312,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -7329,10 +7333,10 @@
         <v>77</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN42" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO42" t="s" s="2">
         <v>77</v>
@@ -7343,14 +7347,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7372,10 +7376,10 @@
         <v>163</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7405,10 +7409,10 @@
         <v>192</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -7426,7 +7430,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -7447,13 +7451,13 @@
         <v>77</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN43" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO43" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP43" t="s" s="2">
         <v>77</v>
@@ -7461,14 +7465,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7490,10 +7494,10 @@
         <v>163</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -7508,7 +7512,7 @@
         <v>77</v>
       </c>
       <c r="T44" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="U44" t="s" s="2">
         <v>77</v>
@@ -7544,7 +7548,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -7565,13 +7569,13 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>77</v>
@@ -7579,10 +7583,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7608,13 +7612,13 @@
         <v>163</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -7664,7 +7668,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7685,13 +7689,13 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>77</v>
@@ -7699,10 +7703,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7728,14 +7732,14 @@
         <v>224</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7748,7 +7752,7 @@
         <v>77</v>
       </c>
       <c r="T46" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U46" t="s" s="2">
         <v>77</v>
@@ -7784,7 +7788,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7805,7 +7809,7 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>341</v>
@@ -7819,13 +7823,13 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>342</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>77</v>
@@ -7917,10 +7921,10 @@
         <v>79</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
@@ -7929,13 +7933,13 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO47" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP47" t="s" s="2">
         <v>77</v>
@@ -7943,10 +7947,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8061,10 +8065,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -8181,10 +8185,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -8210,16 +8214,16 @@
         <v>107</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -8232,7 +8236,7 @@
         <v>77</v>
       </c>
       <c r="T50" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U50" t="s" s="2">
         <v>77</v>
@@ -8247,10 +8251,10 @@
         <v>180</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -8268,7 +8272,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -8289,13 +8293,13 @@
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>329</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>77</v>
@@ -8303,10 +8307,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8332,13 +8336,13 @@
         <v>107</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8349,10 +8353,10 @@
         <v>77</v>
       </c>
       <c r="S51" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="T51" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="U51" t="s" s="2">
         <v>77</v>
@@ -8367,10 +8371,10 @@
         <v>180</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>77</v>
@@ -8388,7 +8392,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8403,13 +8407,13 @@
         <v>99</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>329</v>
@@ -8423,10 +8427,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8452,16 +8456,16 @@
         <v>163</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -8474,7 +8478,7 @@
         <v>77</v>
       </c>
       <c r="T52" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="U52" t="s" s="2">
         <v>77</v>
@@ -8510,7 +8514,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8531,10 +8535,10 @@
         <v>77</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>77</v>
@@ -8545,10 +8549,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8559,7 +8563,7 @@
         <v>78</v>
       </c>
       <c r="G53" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H53" t="s" s="2">
         <v>88</v>
@@ -8574,10 +8578,10 @@
         <v>163</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8592,7 +8596,7 @@
         <v>77</v>
       </c>
       <c r="T53" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="U53" t="s" s="2">
         <v>77</v>
@@ -8628,7 +8632,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8643,19 +8647,19 @@
         <v>99</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>77</v>
@@ -8663,14 +8667,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8692,10 +8696,10 @@
         <v>163</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8710,7 +8714,7 @@
         <v>77</v>
       </c>
       <c r="T54" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U54" t="s" s="2">
         <v>77</v>
@@ -8746,7 +8750,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -8761,19 +8765,19 @@
         <v>99</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP54" t="s" s="2">
         <v>77</v>
@@ -8781,14 +8785,14 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8810,13 +8814,13 @@
         <v>163</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8830,7 +8834,7 @@
         <v>77</v>
       </c>
       <c r="T55" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U55" t="s" s="2">
         <v>77</v>
@@ -8866,7 +8870,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8881,16 +8885,16 @@
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO55" t="s" s="2">
         <v>77</v>
@@ -8901,14 +8905,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8930,10 +8934,10 @@
         <v>163</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8963,10 +8967,10 @@
         <v>192</v>
       </c>
       <c r="Y56" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>77</v>
@@ -8984,7 +8988,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8999,19 +9003,19 @@
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO56" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP56" t="s" s="2">
         <v>77</v>
@@ -9019,14 +9023,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -9048,10 +9052,10 @@
         <v>163</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9066,7 +9070,7 @@
         <v>77</v>
       </c>
       <c r="T57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="U57" t="s" s="2">
         <v>77</v>
@@ -9102,7 +9106,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -9117,19 +9121,19 @@
         <v>99</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>77</v>
@@ -9137,10 +9141,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9166,13 +9170,13 @@
         <v>163</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9222,7 +9226,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -9237,19 +9241,19 @@
         <v>99</v>
       </c>
       <c r="AK58" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP58" t="s" s="2">
         <v>77</v>
@@ -9257,10 +9261,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9286,14 +9290,14 @@
         <v>224</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>77</v>
@@ -9306,7 +9310,7 @@
         <v>77</v>
       </c>
       <c r="T59" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U59" t="s" s="2">
         <v>77</v>
@@ -9342,7 +9346,7 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -9363,7 +9367,7 @@
         <v>77</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>341</v>
@@ -9377,13 +9381,13 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>342</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="D60" t="s" s="2">
         <v>77</v>
@@ -9475,10 +9479,10 @@
         <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AJ60" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AK60" t="s" s="2">
         <v>77</v>
@@ -9487,13 +9491,13 @@
         <v>77</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AP60" t="s" s="2">
         <v>77</v>
@@ -9501,10 +9505,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9619,10 +9623,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9739,10 +9743,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9768,16 +9772,16 @@
         <v>107</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -9790,7 +9794,7 @@
         <v>77</v>
       </c>
       <c r="T63" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="U63" t="s" s="2">
         <v>77</v>
@@ -9805,10 +9809,10 @@
         <v>180</v>
       </c>
       <c r="Y63" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z63" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA63" t="s" s="2">
         <v>77</v>
@@ -9826,7 +9830,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9847,13 +9851,13 @@
         <v>77</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>329</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AP63" t="s" s="2">
         <v>77</v>
@@ -9861,10 +9865,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9890,13 +9894,13 @@
         <v>107</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9907,10 +9911,10 @@
         <v>77</v>
       </c>
       <c r="S64" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="T64" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="U64" t="s" s="2">
         <v>77</v>
@@ -9925,10 +9929,10 @@
         <v>180</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>77</v>
@@ -9946,7 +9950,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9961,13 +9965,13 @@
         <v>99</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>329</v>
@@ -9981,10 +9985,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10010,16 +10014,16 @@
         <v>163</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -10032,7 +10036,7 @@
         <v>77</v>
       </c>
       <c r="T65" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="U65" t="s" s="2">
         <v>77</v>
@@ -10068,7 +10072,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -10089,10 +10093,10 @@
         <v>77</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>77</v>
@@ -10103,10 +10107,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10117,7 +10121,7 @@
         <v>78</v>
       </c>
       <c r="G66" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H66" t="s" s="2">
         <v>88</v>
@@ -10132,10 +10136,10 @@
         <v>163</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -10150,7 +10154,7 @@
         <v>77</v>
       </c>
       <c r="T66" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="U66" t="s" s="2">
         <v>77</v>
@@ -10186,7 +10190,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -10201,19 +10205,19 @@
         <v>99</v>
       </c>
       <c r="AK66" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AN66" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AO66" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AP66" t="s" s="2">
         <v>77</v>
@@ -10221,14 +10225,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -10250,10 +10254,10 @@
         <v>163</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -10268,7 +10272,7 @@
         <v>77</v>
       </c>
       <c r="T67" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="U67" t="s" s="2">
         <v>77</v>
@@ -10304,7 +10308,7 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -10319,19 +10323,19 @@
         <v>99</v>
       </c>
       <c r="AK67" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AN67" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AO67" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AP67" t="s" s="2">
         <v>77</v>
@@ -10339,14 +10343,14 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10368,13 +10372,13 @@
         <v>163</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -10388,7 +10392,7 @@
         <v>77</v>
       </c>
       <c r="T68" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="U68" t="s" s="2">
         <v>77</v>
@@ -10424,7 +10428,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10445,10 +10449,10 @@
         <v>77</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AO68" t="s" s="2">
         <v>77</v>
@@ -10459,14 +10463,14 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="E69" s="2"/>
       <c r="F69" t="s" s="2">
@@ -10488,10 +10492,10 @@
         <v>163</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10521,10 +10525,10 @@
         <v>192</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>77</v>
@@ -10542,7 +10546,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10557,19 +10561,19 @@
         <v>99</v>
       </c>
       <c r="AK69" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AO69" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP69" t="s" s="2">
         <v>77</v>
@@ -10577,14 +10581,14 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10606,10 +10610,10 @@
         <v>163</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10624,7 +10628,7 @@
         <v>77</v>
       </c>
       <c r="T70" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="U70" t="s" s="2">
         <v>77</v>
@@ -10660,7 +10664,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10675,19 +10679,19 @@
         <v>99</v>
       </c>
       <c r="AK70" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AP70" t="s" s="2">
         <v>77</v>
@@ -10695,10 +10699,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10724,13 +10728,13 @@
         <v>163</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10780,7 +10784,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10795,19 +10799,19 @@
         <v>99</v>
       </c>
       <c r="AK71" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AO71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AP71" t="s" s="2">
         <v>77</v>
@@ -10815,10 +10819,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10844,14 +10848,14 @@
         <v>224</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10864,7 +10868,7 @@
         <v>77</v>
       </c>
       <c r="T72" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="U72" t="s" s="2">
         <v>77</v>
@@ -10900,7 +10904,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10921,7 +10925,7 @@
         <v>77</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>341</v>
@@ -10935,10 +10939,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10964,14 +10968,14 @@
         <v>233</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -11020,7 +11024,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -11044,7 +11048,7 @@
         <v>254</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AO73" t="s" s="2">
         <v>167</v>
@@ -11055,10 +11059,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11081,19 +11085,19 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="O74" t="s" s="2">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>77</v>
@@ -11142,7 +11146,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -11166,7 +11170,7 @@
         <v>77</v>
       </c>
       <c r="AN74" t="s" s="2">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="AO74" t="s" s="2">
         <v>77</v>
@@ -11177,10 +11181,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11295,10 +11299,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11415,14 +11419,14 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" t="s" s="2">
@@ -11444,10 +11448,10 @@
         <v>133</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="N77" t="s" s="2">
         <v>136</v>
@@ -11502,7 +11506,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -11537,10 +11541,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11566,14 +11570,14 @@
         <v>187</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -11601,10 +11605,10 @@
         <v>192</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>77</v>
@@ -11622,7 +11626,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -11646,7 +11650,7 @@
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="AO78" t="s" s="2">
         <v>77</v>
@@ -11657,10 +11661,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11683,17 +11687,17 @@
         <v>77</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -11742,7 +11746,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -11763,10 +11767,10 @@
         <v>77</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="AO79" t="s" s="2">
         <v>77</v>
@@ -11777,10 +11781,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11895,10 +11899,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12015,10 +12019,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12044,16 +12048,16 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>77</v>
@@ -12081,10 +12085,10 @@
         <v>180</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -12102,7 +12106,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -12123,13 +12127,13 @@
         <v>77</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>329</v>
       </c>
       <c r="AO82" t="s" s="2">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="AP82" t="s" s="2">
         <v>77</v>
@@ -12137,10 +12141,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12166,16 +12170,16 @@
         <v>163</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="N83" t="s" s="2">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="O83" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>77</v>
@@ -12224,7 +12228,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -12239,16 +12243,16 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="AO83" t="s" s="2">
         <v>77</v>
@@ -12259,14 +12263,14 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="E84" s="2"/>
       <c r="F84" t="s" s="2">
@@ -12288,13 +12292,13 @@
         <v>163</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12344,7 +12348,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12365,13 +12369,13 @@
         <v>77</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="AO84" t="s" s="2">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="AP84" t="s" s="2">
         <v>77</v>
@@ -12379,14 +12383,14 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="E85" s="2"/>
       <c r="F85" t="s" s="2">
@@ -12408,13 +12412,13 @@
         <v>163</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12464,7 +12468,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12485,13 +12489,13 @@
         <v>77</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="AP85" t="s" s="2">
         <v>77</v>
@@ -12499,10 +12503,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12528,10 +12532,10 @@
         <v>163</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12582,7 +12586,7 @@
         <v>77</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12603,13 +12607,13 @@
         <v>77</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="AN86" t="s" s="2">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="AO86" t="s" s="2">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AP86" t="s" s="2">
         <v>77</v>
@@ -12617,10 +12621,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12646,10 +12650,10 @@
         <v>163</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12700,7 +12704,7 @@
         <v>77</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -12721,10 +12725,10 @@
         <v>77</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AO87" t="s" s="2">
         <v>77</v>
@@ -12735,10 +12739,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12764,14 +12768,14 @@
         <v>224</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" t="s" s="2">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="P88" t="s" s="2">
         <v>77</v>
@@ -12820,7 +12824,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -12841,7 +12845,7 @@
         <v>77</v>
       </c>
       <c r="AM88" t="s" s="2">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="AN88" t="s" s="2">
         <v>341</v>
@@ -12855,10 +12859,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12884,14 +12888,14 @@
         <v>289</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" t="s" s="2">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="P89" t="s" s="2">
         <v>77</v>
@@ -12940,7 +12944,7 @@
         <v>77</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -12961,10 +12965,10 @@
         <v>77</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="AN89" t="s" s="2">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="AO89" t="s" s="2">
         <v>77</v>
@@ -12975,10 +12979,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13093,10 +13097,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13213,10 +13217,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13257,7 +13261,7 @@
         <v>77</v>
       </c>
       <c r="S92" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="T92" t="s" s="2">
         <v>77</v>
@@ -13311,7 +13315,7 @@
         <v>99</v>
       </c>
       <c r="AK92" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="AL92" t="s" s="2">
         <v>77</v>
@@ -13331,10 +13335,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13433,7 +13437,7 @@
         <v>99</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>77</v>
@@ -13453,10 +13457,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13575,10 +13579,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13695,10 +13699,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13813,10 +13817,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13842,14 +13846,14 @@
         <v>343</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="P97" t="s" s="2">
         <v>77</v>
@@ -13898,7 +13902,7 @@
         <v>77</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -13919,10 +13923,10 @@
         <v>77</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="AN97" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="AO97" t="s" s="2">
         <v>77</v>
@@ -13933,10 +13937,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13959,17 +13963,17 @@
         <v>77</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -14018,7 +14022,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.467</t>
+    <t>1.1.468</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T09:38:39+00:00</t>
+    <t>2025-01-04T15:04:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.468</t>
+    <t>1.1.477</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-04T15:04:27+00:00</t>
+    <t>2025-01-07T16:27:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.477</t>
+    <t>1.1.478</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T16:27:08+00:00</t>
+    <t>2025-01-13T09:39:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.478</t>
+    <t>1.1.487</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-13T09:39:57+00:00</t>
+    <t>2025-01-17T12:09:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -692,7 +692,7 @@
     <t>Identifier.value</t>
   </si>
   <si>
-    <t>1252: source value from INSTITUTION - NPI (4-41.99)</t>
+    <t>1252: source value based on INSTITUTION - NPI (4-41.99)</t>
   </si>
   <si>
     <t>Dim.Institution.NPI,Dim.Institution.NPI,Dim.InstitutionTimeZone.NPI,NDim.MVIInstitution.NPI</t>
@@ -881,7 +881,7 @@
     <t>Need to use the name as the label of the organization.</t>
   </si>
   <si>
-    <t>1251: source value from INSTITUTION - NAME (4-.01)</t>
+    <t>1251: source value based on INSTITUTION - NAME (4-.01)</t>
   </si>
   <si>
     <t>Dim.AutoDiscontinuedRule.InstitutionName,Dim.Institution.InstitutionName,Dim.Institution.InstitutionName,Dim.InstitutionTimeZone.Institution,Dim.RequestService.IFCRoutingInstitution,NDim.MVIInstitution.InstitutionName</t>
@@ -912,7 +912,7 @@
 For searching knowing previous names that the organization was known by can be very useful.</t>
   </si>
   <si>
-    <t>1255: source value from INSTITUTION - SHORT NAME (4-.05)</t>
+    <t>1255: source value based on INSTITUTION - SHORT NAME (4-.05)</t>
   </si>
   <si>
     <t>Dim.Institution.InstitutionShortName,Dim.Institution.InstitutionShortName,Dim.InstitutionTimeZone.InstitutionShortName,NDim.MVIInstitution.InstitutionShortName</t>
@@ -1438,7 +1438,7 @@
     <t>Organization.address:va-physical.line</t>
   </si>
   <si>
-    <t>1259: source value from INSTITUTION - STREET ADDR. 2 (4-1.02)</t>
+    <t>1259: source value based on INSTITUTION - STREET ADDR. 2 (4-1.02)</t>
   </si>
   <si>
     <t>Dim.Institution.StreetAddress2,Dim.Institution.StreetAddress2,Dim.InstitutionTimeZone.StreetAddress2,NDim.MVIInstitution.StreetAddress2</t>
@@ -1447,7 +1447,7 @@
     <t>Organization.address:va-physical.city</t>
   </si>
   <si>
-    <t>1260: source value from INSTITUTION - CITY (4-1.03)</t>
+    <t>1260: source value based on INSTITUTION - CITY (4-1.03)</t>
   </si>
   <si>
     <t>Dim.Institution.City,Dim.Institution.City,Dim.InstitutionTimeZone.City,NDim.MVIInstitution.City</t>
@@ -1456,7 +1456,7 @@
     <t>Organization.address:va-physical.district</t>
   </si>
   <si>
-    <t>1261: source value from INSTITUTION - DISTRICT (4-.03)</t>
+    <t>1261: source value based on INSTITUTION - DISTRICT (4-.03)</t>
   </si>
   <si>
     <t>Dim.Institution.MedicalDistrict,Dim.Institution.MedicalDistrict,NDim.MVIInstitution.MedicalDistrict</t>
@@ -1465,7 +1465,7 @@
     <t>Organization.address:va-physical.state</t>
   </si>
   <si>
-    <t>1262: source value from INSTITUTION - STATE &gt; STATE - ABBREVIATION (4-.02 &gt; 5-1)</t>
+    <t>1262: source value based on INSTITUTION - STATE &gt; STATE - ABBREVIATION (4-.02 &gt; 5-1)</t>
   </si>
   <si>
     <t>Dim.Institution.StateIEN,Dim.InstitutionTimeZone.StateIEN,Dim.InstitutionTimeZone.StateSID,NDim.MVIInstitution.MVIStateIEN
@@ -1475,7 +1475,7 @@
     <t>Organization.address:va-physical.postalCode</t>
   </si>
   <si>
-    <t>1263: source value from INSTITUTION - ZIP (4-1.04)</t>
+    <t>1263: source value based on INSTITUTION - ZIP (4-1.04)</t>
   </si>
   <si>
     <t>Dim.Institution.Zip,Dim.Institution.Zip,Dim.InstitutionTimeZone.Zip,NDim.MVIInstitution.Zip</t>
@@ -1484,7 +1484,7 @@
     <t>Organization.address:va-physical.country</t>
   </si>
   <si>
-    <t>1264: source value from INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
+    <t>1264: source value based on INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>Dim.Country.CountryCode,NDim.MVICountryCode.CountryCode</t>
@@ -1523,7 +1523,7 @@
     <t>Organization.address:va-postal.line</t>
   </si>
   <si>
-    <t>1270: source value from INSTITUTION - ST. ADDR. 2 (MAILING) (4-4.02)</t>
+    <t>1270: source value based on INSTITUTION - ST. ADDR. 2 (MAILING) (4-4.02)</t>
   </si>
   <si>
     <t>Dim.InstitutionTimeZone.MailingStreetAddress2</t>
@@ -1532,7 +1532,7 @@
     <t>Organization.address:va-postal.city</t>
   </si>
   <si>
-    <t>1271: source value from INSTITUTION - CITY (MAILING) (4-4.03)</t>
+    <t>1271: source value based on INSTITUTION - CITY (MAILING) (4-4.03)</t>
   </si>
   <si>
     <t>Dim.InstitutionTimeZone.MailingCity</t>
@@ -1544,7 +1544,7 @@
     <t>Organization.address:va-postal.state</t>
   </si>
   <si>
-    <t>1272: source value from INSTITUTION - STATE (MAILING) (4-4.04)</t>
+    <t>1272: source value based on INSTITUTION - STATE (MAILING) (4-4.04)</t>
   </si>
   <si>
     <t>Dim.InstitutionTimeZone.MailingStateIEN,Dim.InstitutionTimeZone.MailingStateSID</t>
@@ -1553,7 +1553,7 @@
     <t>Organization.address:va-postal.postalCode</t>
   </si>
   <si>
-    <t>1273: source value from INSTITUTION - ZIP (MAILING) (4-4.05)</t>
+    <t>1273: source value based on INSTITUTION - ZIP (MAILING) (4-4.05)</t>
   </si>
   <si>
     <t>Dim.InstitutionTimeZone.MailingZip</t>
@@ -1562,7 +1562,7 @@
     <t>Organization.address:va-postal.country</t>
   </si>
   <si>
-    <t>1274: source value from INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
+    <t>1274: source value based on INSTITUTION - COUNTRY &gt; COUNTRY CODE - CODE (4-801 &gt; 779.004-.01)</t>
   </si>
   <si>
     <t>Organization.address:va-postal.period</t>
@@ -1722,7 +1722,7 @@
     <t>HumanName.text</t>
   </si>
   <si>
-    <t>1265: source value from INSTITUTION - CONTACT &gt; CONTACT - CONTACT (4-4 &gt; 4.03-.01)</t>
+    <t>1265: source value based on INSTITUTION - CONTACT &gt; CONTACT - CONTACT (4-4 &gt; 4.03-.01)</t>
   </si>
   <si>
     <t>implied by XPN.11</t>
@@ -1877,7 +1877,7 @@
     <t>Organization.contact.telecom.value</t>
   </si>
   <si>
-    <t>1266: source value from INSTITUTION - CONTACT &gt; CONTACT - PHONE # (4-4 &gt; 4.03-.03)</t>
+    <t>1266: source value based on INSTITUTION - CONTACT &gt; CONTACT - PHONE # (4-4 &gt; 4.03-.03)</t>
   </si>
   <si>
     <t>Organization.contact.telecom.use</t>
@@ -2275,7 +2275,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="92.3984375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="96.4921875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="206.203125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="107.3984375" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="102.6171875" customWidth="true" bestFit="true"/>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.487</t>
+    <t>1.1.491</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T12:09:20+00:00</t>
+    <t>2025-01-17T13:37:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -840,6 +840,7 @@
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
   &lt;coding&gt;
+    &lt;system value="http://terminology.hl7.org/CodeSystem/organization-type"/&gt;
     &lt;code value="prov"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
@@ -854,7 +855,7 @@
     <t>http://hl7.org/fhir/ValueSet/organization-type</t>
   </si>
   <si>
-    <t>1254: fixed value = #prov</t>
+    <t>1254: fixed value = http://terminology.hl7.org/CodeSystem/organization-type#prov</t>
   </si>
   <si>
     <t>No equivalent in v2</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.491</t>
+    <t>1.1.494</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T13:37:46+00:00</t>
+    <t>2025-01-25T09:28:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.494</t>
+    <t>1.1.500</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-25T09:28:03+00:00</t>
+    <t>2025-02-01T09:13:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.500</t>
+    <t>1.2.512</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-01T09:13:38+00:00</t>
+    <t>2025-02-05T16:47:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T16:47:13+00:00</t>
+    <t>2025-02-05T17:20:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.512</t>
+    <t>1.2.520</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T17:20:26+00:00</t>
+    <t>2025-02-08T12:00:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.520</t>
+    <t>1.2.529</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-08T12:00:09+00:00</t>
+    <t>2025-02-20T14:56:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.529</t>
+    <t>1.2.531</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-20T14:56:35+00:00</t>
+    <t>2025-02-22T09:54:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.531</t>
+    <t>1.2.537</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-22T09:54:59+00:00</t>
+    <t>2025-02-24T13:20:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:20:37+00:00</t>
+    <t>2025-02-25T20:49:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.537</t>
+    <t>1.2.540</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-25T20:49:13+00:00</t>
+    <t>2025-03-11T10:08:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.540</t>
+    <t>1.3.557</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T10:08:33+00:00</t>
+    <t>2025-03-15T09:48:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.557</t>
+    <t>1.3.574</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-15T09:48:09+00:00</t>
+    <t>2025-03-22T10:33:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.574</t>
+    <t>1.3.575</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:33:38+00:00</t>
+    <t>2025-03-22T10:56:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.575</t>
+    <t>1.3.578</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-22T10:56:07+00:00</t>
+    <t>2025-03-23T10:22:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.578</t>
+    <t>1.3.580</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T10:22:17+00:00</t>
+    <t>2025-03-23T13:19:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-Organization.xlsx
+++ b/docs/StructureDefinition-Organization.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.3.580</t>
+    <t>1.4.588</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-23T13:19:29+00:00</t>
+    <t>2025-04-01T14:43:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
